--- a/Results/Ammonia/ammonia resource use mineral and metals results.xlsx
+++ b/Results/Ammonia/ammonia resource use mineral and metals results.xlsx
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.329252649980159e-05</v>
+        <v>1.329252649979929e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.371768811308123e-05</v>
+        <v>1.371768811308124e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.353100692055026e-05</v>
+        <v>1.353100692054944e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.380569625680932e-05</v>
+        <v>1.380569625680878e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.355634005912649e-05</v>
+        <v>1.355634005912612e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.337598622686253e-05</v>
+        <v>1.337598622686165e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.344917506746007e-05</v>
+        <v>1.344917506746001e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.336447207614087e-05</v>
+        <v>1.336447207614045e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.422611800095009e-05</v>
+        <v>1.422611800095054e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.37311488825359e-05</v>
+        <v>1.373114888253613e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.346800452354244e-05</v>
+        <v>1.346800452354242e-05</v>
       </c>
     </row>
     <row r="3">
@@ -555,37 +555,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.346680070644005e-05</v>
+        <v>1.346680070644163e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.390209802914426e-05</v>
+        <v>1.39020980291443e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.374110259137457e-05</v>
+        <v>1.374110259137438e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.399079895546355e-05</v>
+        <v>1.399079895546341e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.374144275778066e-05</v>
+        <v>1.374144275778076e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.356279668119394e-05</v>
+        <v>1.356279668119346e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.364728672906485e-05</v>
+        <v>1.364728672906521e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.354673758804869e-05</v>
+        <v>1.354673758804861e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.444084554399096e-05</v>
+        <v>1.444084554399041e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.391122478794049e-05</v>
+        <v>1.391122478793918e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.36688940329174e-05</v>
+        <v>1.366889403291735e-05</v>
       </c>
     </row>
     <row r="4">
@@ -595,37 +595,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.739047344596439e-05</v>
+        <v>1.16148965585841e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.666129710270374e-05</v>
+        <v>1.152187350868458e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.753223995082772e-05</v>
+        <v>1.175666306344806e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6714373868992e-05</v>
+        <v>1.153121529190448e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.671437386899206e-05</v>
+        <v>1.15312152919045e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.737496732718889e-05</v>
+        <v>1.165304881725227e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.748422397504269e-05</v>
+        <v>1.170864708766317e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.716109584395397e-05</v>
+        <v>1.160983064447441e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.755057098084227e-05</v>
+        <v>1.177499409346276e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.741343416447438e-05</v>
+        <v>1.163785727709452e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.749608633169512e-05</v>
+        <v>1.172050944431564e-05</v>
       </c>
     </row>
     <row r="5">
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.000203954837189542</v>
+        <v>4.445022439951566e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>0.000214428199997707</v>
+        <v>4.632884822960057e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0002106030604584367</v>
+        <v>4.573712728865901e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0002144282003282913</v>
+        <v>4.632884856018775e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0002144282003282912</v>
+        <v>4.632884856018775e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0002037592243927649</v>
+        <v>4.445667788304267e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>0.000222789773215314</v>
+        <v>4.784242355815632e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0002144281909659184</v>
+        <v>4.632883919781238e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0002157273515916051</v>
+        <v>4.665410729196063e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0001984564714570898</v>
+        <v>4.350143166793474e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0002293981109258139</v>
+        <v>4.271148217296366e-05</v>
       </c>
     </row>
     <row r="6">
@@ -675,37 +675,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.418856866731618e-05</v>
+        <v>1.301706189975968e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>2.510759240492055e-05</v>
+        <v>1.300842147381975e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>2.554060533170062e-05</v>
+        <v>1.316614330322266e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>2.488563356281961e-05</v>
+        <v>1.296935699022543e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>2.513895302891118e-05</v>
+        <v>1.301394121601594e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>4.417306254854039e-05</v>
+        <v>1.63695135506535e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>4.437217626575717e-05</v>
+        <v>1.644092666518665e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>4.395919106530522e-05</v>
+        <v>1.301199598564976e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>2.603153781170211e-05</v>
+        <v>1.326764424760599e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>2.540944305510638e-05</v>
+        <v>1.304515483422008e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>2.547851715378884e-05</v>
+        <v>1.312541726139145e-05</v>
       </c>
     </row>
     <row r="7">
@@ -715,37 +715,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.909950817935901e-05</v>
+        <v>2.071568662234864e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>6.887013960913753e-05</v>
+        <v>2.071062974002672e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>6.924111565782255e-05</v>
+        <v>2.085742513856563e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>6.886936115490041e-05</v>
+        <v>2.07104930044855e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>6.886936115490041e-05</v>
+        <v>2.07104930044855e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>6.908400206058439e-05</v>
+        <v>2.075383888101634e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>6.919325870843837e-05</v>
+        <v>2.080943715142713e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>6.887013057734929e-05</v>
+        <v>2.071062070823835e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>6.92596057142378e-05</v>
+        <v>2.087578415722678e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>6.91224688978693e-05</v>
+        <v>2.073864734085844e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>6.920512106509062e-05</v>
+        <v>2.08212995080796e-05</v>
       </c>
     </row>
     <row r="8">
@@ -755,37 +755,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0002739970981108503</v>
+        <v>5.677766225488537e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0004380107616305867</v>
+        <v>8.567937886376179e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>0.000472400439370138</v>
+        <v>9.181346572745059e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0003930970709989663</v>
+        <v>7.777456962783338e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>0.000278972604577638</v>
+        <v>5.768866364651722e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0004381928853330588</v>
+        <v>8.571700198496228e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0004383021419809114</v>
+        <v>8.577260025537299e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0004379790138498241</v>
+        <v>8.567378381218407e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0004384007612410229</v>
+        <v>8.584462717790048e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0002709697497470185</v>
+        <v>5.626376857781196e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0006098464313847313</v>
+        <v>0.0001159741696087407</v>
       </c>
     </row>
     <row r="9">
@@ -795,37 +795,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0001822934323596053</v>
+        <v>4.063781717012213e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0002281764977606686</v>
+        <v>4.874854862276985e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0002285476341212802</v>
+        <v>4.889537223620793e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0002813892600413802</v>
+        <v>5.811399500583105e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0002281764898726351</v>
+        <v>4.874854750687965e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0002283903602121154</v>
+        <v>4.879175776375935e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0002284996168599699</v>
+        <v>4.884735603417025e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0002281764887288811</v>
+        <v>4.874853959098144e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.000228565963865769</v>
+        <v>4.891370303996984e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0001703650413060241</v>
+        <v>4.407424668432012e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0002285114792166215</v>
+        <v>4.885921839082269e-05</v>
       </c>
     </row>
   </sheetData>
@@ -911,37 +911,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.389487204336216e-05</v>
+        <v>1.389487204336212e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.436707621656943e-05</v>
+        <v>1.436707621656936e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.448687121383925e-05</v>
+        <v>1.448687121383923e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.446501040344699e-05</v>
+        <v>1.446501040344698e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.418662533366288e-05</v>
+        <v>1.418662533366283e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.397301806635478e-05</v>
+        <v>1.397301806635477e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.440846964865762e-05</v>
+        <v>1.44084696486576e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.39790060805508e-05</v>
+        <v>1.397900608055077e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.541940750325315e-05</v>
+        <v>1.541940750325309e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.424274342672271e-05</v>
+        <v>1.424274342672267e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.43597401168281e-05</v>
+        <v>1.435974011682809e-05</v>
       </c>
     </row>
     <row r="3">
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.415991912972289e-05</v>
+        <v>1.415991912972288e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.464408583290514e-05</v>
+        <v>1.464408583290508e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.484084080803028e-05</v>
+        <v>1.484084080803027e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.474271904940291e-05</v>
+        <v>1.474271904940284e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.446433397961873e-05</v>
+        <v>1.446433397961867e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.42498032440644e-05</v>
+        <v>1.424980324406431e-05</v>
       </c>
       <c r="H3" t="n">
         <v>1.475095183718401e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.42540084557595e-05</v>
+        <v>1.425400845575944e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.580199075107863e-05</v>
+        <v>1.580199075107854e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.449431570669285e-05</v>
+        <v>1.449431570669283e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.469485687244133e-05</v>
+        <v>1.469485687244131e-05</v>
       </c>
     </row>
     <row r="4">
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.810950685412478e-05</v>
+        <v>1.203405956094863e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.746069208039246e-05</v>
+        <v>1.196115784665596e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.846142527584068e-05</v>
+        <v>1.23859779826645e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.751879279147523e-05</v>
+        <v>1.197138387048227e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.751879279147528e-05</v>
+        <v>1.197138387048228e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.809085983543697e-05</v>
+        <v>1.206905619317883e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.841537423081875e-05</v>
+        <v>1.233992693764263e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.788758952076997e-05</v>
+        <v>1.203628563081935e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.857466625466875e-05</v>
+        <v>1.249921896149259e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.805617915663168e-05</v>
+        <v>1.198073186345553e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.838711453192062e-05</v>
+        <v>1.231166723874445e-05</v>
       </c>
     </row>
     <row r="5">
@@ -1031,37 +1031,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0002134258387830554</v>
+        <v>4.640973379417216e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0002349959844983406</v>
+        <v>5.024736910475703e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0002620819961206255</v>
+        <v>5.526319821901181e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0002349959848608782</v>
+        <v>5.024736946729483e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0002349959848608776</v>
+        <v>5.024736946729483e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0002277541460228897</v>
+        <v>4.896979436222e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0002719225189680994</v>
+        <v>5.695718416964068e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0002349959770166234</v>
+        <v>5.024736162303862e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0002532494041901425</v>
+        <v>5.380197261433254e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0002234561403908246</v>
+        <v>4.813112484478879e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0002574556308506934</v>
+        <v>5.46341682324381e-05</v>
       </c>
     </row>
     <row r="6">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.202473364490997e-05</v>
+        <v>1.624313945331948e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>2.498400509134684e-05</v>
+        <v>1.328526092940916e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>2.565363610236461e-05</v>
+        <v>1.663912980021292e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>2.478020288469562e-05</v>
+        <v>1.324939203996402e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>2.501601556716332e-05</v>
+        <v>1.329089507185345e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>4.200608662622213e-05</v>
+        <v>1.332107312273121e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>4.254411071770804e-05</v>
+        <v>1.658658453632418e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>2.50013221135913e-05</v>
+        <v>1.328830256037172e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>4.255168407336977e-05</v>
+        <v>1.671917407471768e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>2.518136568151066e-05</v>
+        <v>1.323476468503912e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>2.552263633877925e-05</v>
+        <v>1.356751906994661e-05</v>
       </c>
     </row>
     <row r="7">
@@ -1111,37 +1111,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.338298518233004e-05</v>
+        <v>2.000219170353653e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>6.316107533069355e-05</v>
+        <v>2.000442525512563e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>6.373472447279326e-05</v>
+        <v>2.035407859815213e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>6.316537635420797e-05</v>
+        <v>2.000518253399123e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>6.316537635420807e-05</v>
+        <v>2.000518253399123e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>6.336433816364212e-05</v>
+        <v>2.003718833576677e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>6.368885255902393e-05</v>
+        <v>2.030805908023054e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>6.316106784897525e-05</v>
+        <v>2.000441777340728e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>6.384814458287389e-05</v>
+        <v>2.046735110408049e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>6.33296574848369e-05</v>
+        <v>1.994886400604343e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>6.366059286012563e-05</v>
+        <v>2.027979938133238e-05</v>
       </c>
     </row>
     <row r="8">
@@ -1151,37 +1151,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0002423722100729541</v>
+        <v>5.150429511358883e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0003857690714813074</v>
+        <v>7.678343226997067e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0004160838508041943</v>
+        <v>8.236752449645227e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0003464960493309791</v>
+        <v>6.987138070769766e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0002467044335049915</v>
+        <v>5.230805641749257e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0003859397534138631</v>
+        <v>7.681046111217368e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0003862642678092437</v>
+        <v>7.708133185663724e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0003857364830991965</v>
+        <v>7.67776905498142e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0003864517786592269</v>
+        <v>7.72455903938598e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0002396516951701765</v>
+        <v>5.098154247050941e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0005362237904464914</v>
+        <v>0.0001034509217058612</v>
       </c>
     </row>
     <row r="9">
@@ -1191,37 +1191,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0001390493304976627</v>
+        <v>3.331946840687406e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0001727493525881406</v>
+        <v>3.92919619479248e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0001733231821634719</v>
+        <v>3.964164704719983e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0002118945346950608</v>
+        <v>4.618151426014206e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0001727493452445767</v>
+        <v>3.929196095418859e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0001729526154210893</v>
+        <v>3.932472502856592e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0001732771298164713</v>
+        <v>3.95955957730297e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0001727493451064226</v>
+        <v>3.929195446620642e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0001734364218403211</v>
+        <v>3.975488779687968e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0001532634347009206</v>
+        <v>3.577720871030659e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0001732488701175733</v>
+        <v>3.95673360741315e-05</v>
       </c>
     </row>
   </sheetData>
@@ -1307,37 +1307,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.390199506293319e-05</v>
+        <v>1.39019950629332e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.378408020208249e-05</v>
+        <v>1.378408020208251e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.448788447940698e-05</v>
+        <v>1.448788447940699e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.428378336778172e-05</v>
+        <v>1.428378336778173e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.428378336778172e-05</v>
+        <v>1.428378336778173e-05</v>
       </c>
       <c r="G2" t="n">
         <v>1.419297438692633e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.479664383700303e-05</v>
+        <v>1.479664383700305e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.428244284243146e-05</v>
+        <v>1.428244284243147e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.399347443624516e-05</v>
+        <v>1.399347443624517e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.417328841185567e-05</v>
+        <v>1.417328841185569e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.408295155578973e-05</v>
+        <v>1.408295155578974e-05</v>
       </c>
     </row>
     <row r="3">
@@ -1350,22 +1350,22 @@
         <v>1.414006889956239e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.403074274247409e-05</v>
+        <v>1.403074274247411e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.481396309513423e-05</v>
+        <v>1.481396309513422e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.45790260906858e-05</v>
+        <v>1.457902609068582e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.45790260906858e-05</v>
+        <v>1.457902609068582e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.447475539833986e-05</v>
+        <v>1.447475539833989e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.516937105762701e-05</v>
+        <v>1.516937105762703e-05</v>
       </c>
       <c r="I3" t="n">
         <v>1.45746613096579e-05</v>
@@ -1374,10 +1374,10 @@
         <v>1.422635253441042e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.443341540467151e-05</v>
+        <v>1.443341540467153e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.43484951392977e-05</v>
+        <v>1.434849513929769e-05</v>
       </c>
     </row>
     <row r="4">
@@ -1387,37 +1387,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.831809703149218e-05</v>
+        <v>1.191331561778153e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.729927689561903e-05</v>
+        <v>1.176400091926854e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.866638346334532e-05</v>
+        <v>1.226160204963465e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.778397686272116e-05</v>
+        <v>1.200574108810605e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.778397686272116e-05</v>
+        <v>1.200574108810606e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.842486582904692e-05</v>
+        <v>1.207463822591212e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.885046042904587e-05</v>
+        <v>1.244567901533524e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.826587563638746e-05</v>
+        <v>1.209055656274144e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.829753445263002e-05</v>
+        <v>1.189275303891944e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.840537428118327e-05</v>
+        <v>1.200059286747264e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.842705904575394e-05</v>
+        <v>1.202227763204326e-05</v>
       </c>
     </row>
     <row r="5">
@@ -1427,37 +1427,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.541904790899779e-05</v>
+        <v>2.020308292730352e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0001943198843685714</v>
+        <v>4.291962766568817e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0002212570150740589</v>
+        <v>4.791755301991493e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0002104377815511166</v>
+        <v>4.591281052953481e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0002104377815511166</v>
+        <v>4.591281052953481e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0002057501723062534</v>
+        <v>4.504389198725351e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0002599189481694555</v>
+        <v>5.487373262774658e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0002104377831177789</v>
+        <v>4.591281209619697e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0001909250111787636</v>
+        <v>4.227518877808852e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0001964249718923624</v>
+        <v>4.333204187726749e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0002166026231802349</v>
+        <v>4.690117673071697e-05</v>
       </c>
     </row>
     <row r="6">
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.351631435657681e-05</v>
+        <v>1.318286429626231e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>2.519082035590464e-05</v>
+        <v>1.315291256075284e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>2.592411659534298e-05</v>
+        <v>1.353896727841026e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>2.524531000822428e-05</v>
+        <v>1.331893571459901e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>2.549414927996702e-05</v>
+        <v>1.336273142618842e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>4.362308315413165e-05</v>
+        <v>1.650952445109612e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>4.525136177239519e-05</v>
+        <v>1.709223762658684e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>4.346409296147199e-05</v>
+        <v>1.652544278792543e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>4.380343881590059e-05</v>
+        <v>1.638179218253068e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>2.562949008134194e-05</v>
+        <v>1.327203724141108e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>2.565406947274654e-05</v>
+        <v>1.329423146030174e-05</v>
       </c>
     </row>
     <row r="7">
@@ -1507,37 +1507,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.667076312679327e-05</v>
+        <v>2.04233848044418e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>6.642076250914075e-05</v>
+        <v>2.040938234040247e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>6.701902082896182e-05</v>
+        <v>2.077166617987049e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>6.661877413927324e-05</v>
+        <v>2.06006653622068e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>6.661877413927324e-05</v>
+        <v>2.06006653622068e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>6.677753192434799e-05</v>
+        <v>2.058470741257242e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>6.720312652434692e-05</v>
+        <v>2.095574820199552e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>6.661854173168838e-05</v>
+        <v>2.060062574940174e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>6.665020054793115e-05</v>
+        <v>2.040282222557971e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>6.675804037648436e-05</v>
+        <v>2.051066205413291e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>6.677972514105497e-05</v>
+        <v>2.053234681870354e-05</v>
       </c>
     </row>
     <row r="8">
@@ -1547,37 +1547,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0002563288130556728</v>
+        <v>5.380320141105254e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0004087134075476889</v>
+        <v>8.065288754079335e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0004409248922687347</v>
+        <v>8.657909919668602e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0003671720567025405</v>
+        <v>7.349804280671188e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0002611140673892298</v>
+        <v>5.483183678871395e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0004090398794094613</v>
+        <v>8.082288024354553e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0004094654740095161</v>
+        <v>8.119392103297849e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0004088808892168013</v>
+        <v>8.083879858037483e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0004089425391773051</v>
+        <v>8.064627349791416e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0002535813871287775</v>
+        <v>5.339157090436785e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0005684500220130128</v>
+        <v>0.0001088263185897381</v>
       </c>
     </row>
     <row r="9">
@@ -1587,37 +1587,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000161019377474032</v>
+        <v>3.702874083957794e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0002008326300212546</v>
+        <v>4.406587089434935e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0002014309190058841</v>
+        <v>4.442816013082356e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0002472625445817791</v>
+        <v>5.239396878781251e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0002010304000621481</v>
+        <v>4.425711139644785e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.000201189399436462</v>
+        <v>4.42411959665193e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0002016149940364609</v>
+        <v>4.461223675594239e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0002010304092438022</v>
+        <v>4.425711430334861e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0002010620680600452</v>
+        <v>4.405931077952662e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0001507231203870838</v>
+        <v>4.008169687799339e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0002011915926531689</v>
+        <v>4.41888353726504e-05</v>
       </c>
     </row>
   </sheetData>
@@ -1703,13 +1703,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.411519007645427e-05</v>
+        <v>1.411519007645428e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.412227318755803e-05</v>
+        <v>1.4122273187558e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.475824966794973e-05</v>
+        <v>1.475824966794972e-05</v>
       </c>
       <c r="E2" t="n">
         <v>1.463119710964469e-05</v>
@@ -1718,22 +1718,22 @@
         <v>1.463119710964469e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.446147812701141e-05</v>
+        <v>1.446147812701139e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.510878269183653e-05</v>
+        <v>1.510878269183652e-05</v>
       </c>
       <c r="I2" t="n">
         <v>1.458799186304415e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.409363055653834e-05</v>
+        <v>1.409363055653835e-05</v>
       </c>
       <c r="K2" t="n">
         <v>1.443098942609685e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.432456676619066e-05</v>
+        <v>1.432456676619064e-05</v>
       </c>
     </row>
     <row r="3">
@@ -1746,19 +1746,19 @@
         <v>1.438886793268561e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.441818562265691e-05</v>
+        <v>1.44181856226569e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.512851967229844e-05</v>
+        <v>1.512851967229846e-05</v>
       </c>
       <c r="E3" t="n">
         <v>1.497591766598386e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.497591766598387e-05</v>
+        <v>1.497591766598386e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.478717092417987e-05</v>
+        <v>1.478717092417986e-05</v>
       </c>
       <c r="H3" t="n">
         <v>1.553195941430183e-05</v>
@@ -1767,13 +1767,13 @@
         <v>1.492981932594075e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.433660921942665e-05</v>
+        <v>1.433660921942664e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.472860544968235e-05</v>
+        <v>1.472860544968236e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.462999473561981e-05</v>
+        <v>1.462999473561982e-05</v>
       </c>
     </row>
     <row r="4">
@@ -1783,37 +1783,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.868136938273864e-05</v>
+        <v>1.209774308928702e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.76989668379816e-05</v>
+        <v>1.199960083449855e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.906364106113631e-05</v>
+        <v>1.248001476768476e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.823587437968313e-05</v>
+        <v>1.225100979485816e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.823587437968315e-05</v>
+        <v>1.225100979485816e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.882091582798446e-05</v>
+        <v>1.229192660752504e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.927254814080362e-05</v>
+        <v>1.268892184735201e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.868358052007179e-05</v>
+        <v>1.232981077209129e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.855987470233823e-05</v>
+        <v>1.197624840888666e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.877610672516858e-05</v>
+        <v>1.219248043171698e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.880725235192855e-05</v>
+        <v>1.2223626058477e-05</v>
       </c>
     </row>
     <row r="5">
@@ -1823,37 +1823,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.511013089006354e-05</v>
+        <v>2.202920506076157e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0002022793957448886</v>
+        <v>4.448575614608451e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0002254978362770992</v>
+        <v>4.881243292882324e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0002173207561716394</v>
+        <v>4.728994880038028e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0002173207561716394</v>
+        <v>4.728994880038028e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0002111338889792188</v>
+        <v>4.613900969873739e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0002666645173921029</v>
+        <v>5.622990819964935e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0002173207618718235</v>
+        <v>4.728995450056438e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0001844740862820739</v>
+        <v>4.1177149488692e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0001995775593726241</v>
+        <v>4.401353592524347e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0002215526794059491</v>
+        <v>4.790682102663151e-05</v>
       </c>
     </row>
     <row r="6">
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.286816842664112e-05</v>
+        <v>1.63546196979476e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>2.533944458626817e-05</v>
+        <v>1.334432491091045e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>2.605400254433531e-05</v>
+        <v>1.683465062796114e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>2.540675917146507e-05</v>
+        <v>1.351308551137308e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>2.565432980925853e-05</v>
+        <v>1.355665794338864e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>2.577445829653537e-05</v>
+        <v>1.351575007535863e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>4.508779372192174e-05</v>
+        <v>1.72324050450095e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>2.563712298862286e-05</v>
+        <v>1.355363423992489e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>2.597840597994549e-05</v>
+        <v>1.328190990667067e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>2.573161334189768e-05</v>
+        <v>1.341664958962803e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>2.577333176606879e-05</v>
+        <v>1.344965602872231e-05</v>
       </c>
     </row>
     <row r="7">
@@ -1903,37 +1903,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.454256989509526e-05</v>
+        <v>2.016931433572515e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>6.434634106305655e-05</v>
+        <v>2.020953865362534e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>6.492482842443709e-05</v>
+        <v>2.055158369988907e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>6.455073982901103e-05</v>
+        <v>2.040242606977058e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>6.455073982901103e-05</v>
+        <v>2.040242606977058e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>6.468211634034109e-05</v>
+        <v>2.036349785396318e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>6.513374865316023e-05</v>
+        <v>2.076049309379017e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>6.454478103242839e-05</v>
+        <v>2.040138201852944e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>6.442107521469486e-05</v>
+        <v>2.004781965532479e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>6.463730723752531e-05</v>
+        <v>2.026405167815513e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>6.466845286428523e-05</v>
+        <v>2.029519730491514e-05</v>
       </c>
     </row>
     <row r="8">
@@ -1943,37 +1943,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0002444898923354354</v>
+        <v>5.18400429136139e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0003891483984052009</v>
+        <v>7.737470043614014e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0004197221427439719</v>
+        <v>8.29959106817661e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0003497360838421426</v>
+        <v>7.059504634410778e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0002490862500673667</v>
+        <v>5.288067569573438e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0003894499426199419</v>
+        <v>7.752263496945025e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0003899015749329278</v>
+        <v>7.791963020930645e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0003893126073120294</v>
+        <v>7.756051913401646e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0003892173628979959</v>
+        <v>7.721196597783578e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0002418945144658561</v>
+        <v>5.146131998129563e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0005407134051215598</v>
+        <v>0.0001040791084482037</v>
       </c>
     </row>
     <row r="9">
@@ -1983,37 +1983,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0001465570249937244</v>
+        <v>3.460385835486879e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0001823106018208069</v>
+        <v>4.097124843448995e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0001828891044958875</v>
+        <v>4.131329617596485e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0002239943424165952</v>
+        <v>4.84644999731281e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0001825090288085563</v>
+        <v>4.116308481767675e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0001826463770980915</v>
+        <v>4.112520763482774e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0001830980094109103</v>
+        <v>4.152220287465475e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.000182509041790179</v>
+        <v>4.116309179939398e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0001823853359724454</v>
+        <v>4.080952943618933e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0001617721103210373</v>
+        <v>3.735977692821825e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0001826327136220357</v>
+        <v>4.105690708577975e-05</v>
       </c>
     </row>
   </sheetData>
@@ -2099,37 +2099,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.421720822955426e-05</v>
+        <v>1.421720822955447e-05</v>
       </c>
       <c r="C2" t="n">
         <v>1.434433581216319e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.490698862794825e-05</v>
+        <v>1.490698862794845e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.478701431336622e-05</v>
+        <v>1.478701431336637e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.478701431336622e-05</v>
+        <v>1.478701431336637e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.461435777322206e-05</v>
+        <v>1.461435777322214e-05</v>
       </c>
       <c r="H2" t="n">
         <v>1.520350492208706e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.470371137067655e-05</v>
+        <v>1.470371137067666e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.427271510189183e-05</v>
+        <v>1.427271510189192e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.456004395335672e-05</v>
+        <v>1.456004395335669e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.456550347289001e-05</v>
+        <v>1.456550347289002e-05</v>
       </c>
     </row>
     <row r="3">
@@ -2139,37 +2139,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.451369927870754e-05</v>
+        <v>1.451369927870756e-05</v>
       </c>
       <c r="C3" t="n">
         <v>1.467442776009315e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.53070896244397e-05</v>
+        <v>1.530708962443971e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.515660598801699e-05</v>
+        <v>1.515660598801707e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.515660598801699e-05</v>
+        <v>1.515660598801707e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.497050352320568e-05</v>
+        <v>1.497050352320554e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.564840563415786e-05</v>
+        <v>1.564840563415785e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.507043613079709e-05</v>
+        <v>1.507043613079681e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.453700337296197e-05</v>
+        <v>1.453700337296206e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.488167390823738e-05</v>
+        <v>1.488167390823754e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.49146130590964e-05</v>
+        <v>1.491461305909641e-05</v>
       </c>
     </row>
     <row r="4">
@@ -2179,37 +2179,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.924100658896257e-05</v>
+        <v>1.226784721462289e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.823263771995324e-05</v>
+        <v>1.2202426277094e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.965105180733287e-05</v>
+        <v>1.267789243299327e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.880404233998892e-05</v>
+        <v>1.242932633132194e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.880404233998892e-05</v>
+        <v>1.242932633132194e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.9410555116449e-05</v>
+        <v>1.24922247413707e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.982787010548939e-05</v>
+        <v>1.28547107311497e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.925005720339652e-05</v>
+        <v>1.250782471130138e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.911356134349656e-05</v>
+        <v>1.214040196915692e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.934049595608809e-05</v>
+        <v>1.236733658174845e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.944946796796891e-05</v>
+        <v>1.247630859362921e-05</v>
       </c>
     </row>
     <row r="5">
@@ -2219,37 +2219,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.148024285410675e-05</v>
+        <v>2.322195273793231e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0002129073030268783</v>
+        <v>4.646516718545661e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0002342482517760893</v>
+        <v>5.044699942283862e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0002243329844816739</v>
+        <v>4.86024199522504e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0002243329844816739</v>
+        <v>4.86024199522504e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0002203676088602766</v>
+        <v>4.786066600863558e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0002731856309280176</v>
+        <v>5.744567639429369e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.000224332984195819</v>
+        <v>4.860241966638274e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0001904040471529865</v>
+        <v>4.228752730827174e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0002062385548788409</v>
+        <v>4.526139477391314e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0002374207451404194</v>
+        <v>5.08392531681069e-05</v>
       </c>
     </row>
     <row r="6">
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.374837226377988e-05</v>
+        <v>1.349927338417739e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>2.597097266201993e-05</v>
+        <v>1.356437321951137e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>2.668235268344218e-05</v>
+        <v>1.39154013804826e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>2.599902791700214e-05</v>
+        <v>1.369564378601461e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>2.626476102254447e-05</v>
+        <v>1.374241281233659e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>2.640729475410307e-05</v>
+        <v>1.680552107676654e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>4.644285596287678e-05</v>
+        <v>1.753894821666785e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>2.624679684105063e-05</v>
+        <v>1.682112104669719e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>2.658546706282092e-05</v>
+        <v>1.652994606523834e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>2.633168832636485e-05</v>
+        <v>1.359778643224981e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>2.646020906819809e-05</v>
+        <v>1.371019902058357e-05</v>
       </c>
     </row>
     <row r="7">
@@ -2299,37 +2299,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.534580201894973e-05</v>
+        <v>2.038229116633167e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>6.519420416966593e-05</v>
+        <v>2.046766192745735e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>6.575583835643184e-05</v>
+        <v>2.079233482166569e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>6.536530526905765e-05</v>
+        <v>2.062410856243377e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>6.536530526905765e-05</v>
+        <v>2.062410856243377e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>6.551535054643617e-05</v>
+        <v>2.060666869307953e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>6.593266553547659e-05</v>
+        <v>2.096915468285848e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>6.535485263338379e-05</v>
+        <v>2.062226866301016e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>6.521835677348377e-05</v>
+        <v>2.025484592086569e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>6.544529138607526e-05</v>
+        <v>2.048178053345723e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>6.555426339795613e-05</v>
+        <v>2.059075254533798e-05</v>
       </c>
     </row>
     <row r="8">
@@ -2339,37 +2339,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0002456803653182532</v>
+        <v>5.21211741350286e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0003908869306381849</v>
+        <v>7.778958147523929e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0004215429001429592</v>
+        <v>8.341085735678952e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0003512998745815979</v>
+        <v>7.094859248875239e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0002503020617686184</v>
+        <v>5.317297752998699e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0003911694507950458</v>
+        <v>7.792179002626677e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0003915867657843428</v>
+        <v>7.828427601609095e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0003910089528819933</v>
+        <v>7.793738999619744e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0003909010164993299</v>
+        <v>7.757499372201948e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0002430804696770733</v>
+        <v>5.174557174326681e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0005430067714358748</v>
+        <v>0.0001046223935046775</v>
       </c>
     </row>
     <row r="9">
@@ -2379,37 +2379,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0001412989981229164</v>
+        <v>3.375005360819524e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0001755310461078518</v>
+        <v>3.988694600335269e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0001760926917296518</v>
+        <v>4.021162091012703e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0002153696863442317</v>
+        <v>4.702487948860907e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0001756916876064608</v>
+        <v>4.004155174860126e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0001758521924846222</v>
+        <v>4.002595276897478e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0001762695074736625</v>
+        <v>4.038843875875376e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0001756916945715696</v>
+        <v>4.004155273890549e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0001755551987116699</v>
+        <v>3.967412999676097e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0001550518534135311</v>
+        <v>3.228111856280734e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0001758911053361421</v>
+        <v>4.001003662123323e-05</v>
       </c>
     </row>
   </sheetData>
@@ -2495,37 +2495,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.417348561621307e-05</v>
+        <v>1.417348561621304e-05</v>
       </c>
       <c r="C2" t="n">
         <v>1.402835721459745e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.495637404052794e-05</v>
+        <v>1.49563740405279e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.454972208280034e-05</v>
+        <v>1.454972208280032e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.454972208280034e-05</v>
+        <v>1.454972208280032e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.449697785918278e-05</v>
+        <v>1.449697785918275e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.499655733299232e-05</v>
+        <v>1.499655733299225e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.456277492271762e-05</v>
+        <v>1.456277492271759e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.432520218117238e-05</v>
+        <v>1.432520218117236e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.434114793849999e-05</v>
+        <v>1.434114793849994e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.437094318196076e-05</v>
+        <v>1.437094318196072e-05</v>
       </c>
     </row>
     <row r="3">
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.445237872407809e-05</v>
+        <v>1.445237872407808e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.431444392796922e-05</v>
+        <v>1.431444392796921e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.53528625868887e-05</v>
+        <v>1.535286258688868e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.488711220311719e-05</v>
+        <v>1.488711220311717e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.488711220311719e-05</v>
+        <v>1.488711220311716e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.482446181470949e-05</v>
+        <v>1.482446181470946e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.539936374763034e-05</v>
+        <v>1.539936374763032e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.489734208170142e-05</v>
+        <v>1.489734208170139e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.461212271100502e-05</v>
+        <v>1.461212271100501e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.462719783129256e-05</v>
+        <v>1.462719783129252e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.467978866201853e-05</v>
+        <v>1.467978866201851e-05</v>
       </c>
     </row>
     <row r="4">
@@ -2575,37 +2575,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.847081133324438e-05</v>
+        <v>1.206251933723839e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.745230168641182e-05</v>
+        <v>1.190868375479126e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.893620532770299e-05</v>
+        <v>1.252791333169699e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.797383809897706e-05</v>
+        <v>1.216581375440228e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.797383809897701e-05</v>
+        <v>1.216581375440228e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.859672677548975e-05</v>
+        <v>1.224313765821198e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.896065023993723e-05</v>
+        <v>1.255235824393123e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.842262276829503e-05</v>
+        <v>1.224479833794878e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.850258054149352e-05</v>
+        <v>1.209428854548753e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.849913492102578e-05</v>
+        <v>1.209084292501979e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.858959754422437e-05</v>
+        <v>1.218130554821837e-05</v>
       </c>
     </row>
     <row r="5">
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.974106826200077e-05</v>
+        <v>2.284608449826761e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0002080385872993867</v>
+        <v>4.545186984091756e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0002464990249208507</v>
+        <v>5.257896936307016e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0002249787989801468</v>
+        <v>4.859868667207281e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0002249787989801468</v>
+        <v>4.859868667207281e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0002219809567113359</v>
+        <v>4.803876193295801e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0002709666914542901</v>
+        <v>5.690542125732558e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0002249787971381258</v>
+        <v>4.859868483005164e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0002108831888254656</v>
+        <v>4.5953275419998e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0002046290369463207</v>
+        <v>4.484970550396433e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0002337337901756926</v>
+        <v>5.004668324617927e-05</v>
       </c>
     </row>
     <row r="6">
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.379943270180977e-05</v>
+        <v>1.335093973417995e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>2.544307732199257e-05</v>
+        <v>1.331506025903286e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>2.63211020018061e-05</v>
+        <v>1.382765513929638e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>2.551164246290023e-05</v>
+        <v>1.349246731526416e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>2.57600694902052e-05</v>
+        <v>1.35361904718329e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>2.591729725232495e-05</v>
+        <v>1.353155805515353e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>4.548202721529941e-05</v>
+        <v>1.72201205663022e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>4.375124413686027e-05</v>
+        <v>1.353321873489032e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>4.414069741293991e-05</v>
+        <v>1.660659709041164e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>2.58151821379719e-05</v>
+        <v>1.337846722822517e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>2.592416111921951e-05</v>
+        <v>1.347218873042273e-05</v>
       </c>
     </row>
     <row r="7">
@@ -2695,37 +2695,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.673954357763462e-05</v>
+        <v>2.055781616621843e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>6.648385647412285e-05</v>
+        <v>2.053823735066826e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>6.720490753502895e-05</v>
+        <v>2.102320487415372e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>6.67007871936422e-05</v>
+        <v>2.07417567485937e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>6.67007871936422e-05</v>
+        <v>2.07417567485937e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>6.686545901988003e-05</v>
+        <v>2.0738434487192e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>6.722938248432744e-05</v>
+        <v>2.10476550729112e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>6.66913550126852e-05</v>
+        <v>2.074009516692881e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>6.67713127858838e-05</v>
+        <v>2.058958537446752e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>6.676786716541602e-05</v>
+        <v>2.05861397539998e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>6.685832978861462e-05</v>
+        <v>2.067660237719838e-05</v>
       </c>
     </row>
     <row r="8">
@@ -2735,37 +2735,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0002564233474277199</v>
+        <v>5.394216546293676e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0004087405465404028</v>
+        <v>8.077541447593201e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0004410514333779849</v>
+        <v>8.682019306598591e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0003672272686876564</v>
+        <v>7.363441720493573e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0002612158905843497</v>
+        <v>5.49764147598541e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.00040908307517649</v>
+        <v>8.09687346043911e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0004094469986409918</v>
+        <v>8.127795519011995e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.000408908971169295</v>
+        <v>8.097039528412795e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0004090189062344269</v>
+        <v>8.082516149501829e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0002536182771386131</v>
+        <v>5.347181173108801e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0005684102675949061</v>
+        <v>0.0001089497429527883</v>
       </c>
     </row>
     <row r="9">
@@ -2775,37 +2775,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0001615518056012039</v>
+        <v>3.724477419194659e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0002014497941795494</v>
+        <v>4.429224225810977e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0002021708774810372</v>
+        <v>4.47772154559375e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0002479937773033562</v>
+        <v>5.264932283500882e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0002016572868880462</v>
+        <v>4.44941005661043e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0002018313967253066</v>
+        <v>4.449243939463357e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>0.000202195320189754</v>
+        <v>4.480165998035272e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0002016572927181118</v>
+        <v>4.449410007437034e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0002017372504913104</v>
+        <v>4.434359028190909e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0001511731592105237</v>
+        <v>3.544147107344358e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0002018242674940413</v>
+        <v>4.443060728463987e-05</v>
       </c>
     </row>
   </sheetData>
@@ -2891,37 +2891,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.442455987000598e-05</v>
+        <v>1.44245598700062e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.44112727949932e-05</v>
+        <v>1.441127279499325e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.554033745102425e-05</v>
+        <v>1.554033745102468e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.488000557047451e-05</v>
+        <v>1.488000557047447e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.488000557047451e-05</v>
+        <v>1.488000557047447e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.491151584213686e-05</v>
+        <v>1.491151584213681e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.532759586907818e-05</v>
+        <v>1.532759586907821e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.485818004125656e-05</v>
+        <v>1.48581800412568e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.505347928678759e-05</v>
+        <v>1.505347928678777e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.466699142052898e-05</v>
+        <v>1.466699142052899e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.478388564296783e-05</v>
+        <v>1.478388564296786e-05</v>
       </c>
     </row>
     <row r="3">
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.474602659955373e-05</v>
+        <v>1.47460265995536e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.475669031250911e-05</v>
+        <v>1.475669031250913e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.602940195035431e-05</v>
+        <v>1.602940195035438e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.526662592400836e-05</v>
+        <v>1.526662592400839e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.526662592400836e-05</v>
+        <v>1.526662592400839e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.530612684012998e-05</v>
+        <v>1.530612684013013e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.578497724708483e-05</v>
+        <v>1.578497724708488e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.524195738321544e-05</v>
+        <v>1.524195738321571e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.544754376626699e-05</v>
+        <v>1.544754376626704e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.50010588811168e-05</v>
+        <v>1.500105888111706e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.515963237003833e-05</v>
+        <v>1.515963237003836e-05</v>
       </c>
     </row>
     <row r="4">
@@ -2971,37 +2971,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.888652540983834e-05</v>
+        <v>1.226721980075722e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.792402414666705e-05</v>
+        <v>1.217813674866554e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.954980790224699e-05</v>
+        <v>1.293050229316587e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.843140209476408e-05</v>
+        <v>1.239958734937326e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.843140209476415e-05</v>
+        <v>1.239958734937326e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.910912402394688e-05</v>
+        <v>1.254492430258221e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.942392822224235e-05</v>
+        <v>1.280462261316123e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.886171015704144e-05</v>
+        <v>1.247530612374933e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.917383720748621e-05</v>
+        <v>1.255453159840511e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.893639387945703e-05</v>
+        <v>1.231708827037597e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.910156168270538e-05</v>
+        <v>1.248225607362427e-05</v>
       </c>
     </row>
     <row r="5">
@@ -3011,37 +3011,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.967290178924367e-05</v>
+        <v>2.472562197602541e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0002174342957627553</v>
+        <v>4.729194436282929e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0002654498252983813</v>
+        <v>5.62089051203771e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0002294244581175215</v>
+        <v>4.953436500815988e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0002294244581175215</v>
+        <v>4.953436500815988e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0002335960237058865</v>
+        <v>5.029461844205395e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0002770534206427349</v>
+        <v>5.814741303347332e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0002294244393745912</v>
+        <v>4.953434626522968e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0002388916735077524</v>
+        <v>5.122487057771273e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0002096238871934282</v>
+        <v>4.587808691178119e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0002473191201928137</v>
+        <v>5.264854615375815e-05</v>
       </c>
     </row>
     <row r="6">
@@ -3051,37 +3051,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.596637899725423e-05</v>
+        <v>1.351327402539053e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>2.56707841310745e-05</v>
+        <v>1.354156649853339e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>4.448084047989953e-05</v>
+        <v>1.418954123372253e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>2.569701293800574e-05</v>
+        <v>1.367833485085477e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>2.595801272161158e-05</v>
+        <v>1.372427081252048e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>2.61889776113627e-05</v>
+        <v>1.683284208514973e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>4.54769350809052e-05</v>
+        <v>1.73899517954398e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>2.594156374445731e-05</v>
+        <v>1.676322390631684e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>2.673277812089658e-05</v>
+        <v>1.388490519195659e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>2.599298070689506e-05</v>
+        <v>1.355904754527537e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>2.619663278139694e-05</v>
+        <v>1.373098858022761e-05</v>
       </c>
     </row>
     <row r="7">
@@ -3091,37 +3091,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.467699200159183e-05</v>
+        <v>2.032634187723668e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>6.448704196685365e-05</v>
+        <v>2.037322784061248e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>6.534025691607611e-05</v>
+        <v>2.098962127593066e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>6.466463131414338e-05</v>
+        <v>2.053663564789258e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>6.466463131414338e-05</v>
+        <v>2.053663564789258e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>6.489959061570042e-05</v>
+        <v>2.060404637906165e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>6.521439481399591e-05</v>
+        <v>2.086374468964069e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>6.465217674879505e-05</v>
+        <v>2.053442820022878e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>6.496430379923978e-05</v>
+        <v>2.061365367488457e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>6.47268604712106e-05</v>
+        <v>2.037621034685542e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>6.489202827445889e-05</v>
+        <v>2.054137815010372e-05</v>
       </c>
     </row>
     <row r="8">
@@ -3131,37 +3131,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0002446885926995969</v>
+        <v>5.200838342841308e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0003893285600330542</v>
+        <v>7.754533471047076e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0004201644203616477</v>
+        <v>8.343867370396451e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0003498907870258441</v>
+        <v>7.073643878113913e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0002492608287897002</v>
+        <v>5.302556622754594e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0003897006905904955</v>
+        <v>7.776903966487113e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0003900154947889727</v>
+        <v>7.802873797548211e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0003894532767235898</v>
+        <v>7.769942148603825e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0003897938590843848</v>
+        <v>7.778365509528851e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0002420489218828847</v>
+        <v>5.158489298620253e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0005409378673688251</v>
+        <v>0.0001043254453767196</v>
       </c>
     </row>
     <row r="9">
@@ -3171,37 +3171,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000147215739210392</v>
+        <v>3.485316130727042e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0001830893186633976</v>
+        <v>4.124722842609634e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0001839425538467173</v>
+        <v>4.186362542261554e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0002248710137566068</v>
+        <v>4.873295880498149e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0001832544648352393</v>
+        <v>4.140844623450939e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0001835018673122442</v>
+        <v>4.14780469645455e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>0.00018381667151054</v>
+        <v>4.173774527512456e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0001832544534453389</v>
+        <v>4.140842878571259e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0001835665804957838</v>
+        <v>4.148765426036841e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0001624337876673196</v>
+        <v>3.325797676863652e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>0.000183494304971003</v>
+        <v>4.141537873558757e-05</v>
       </c>
     </row>
   </sheetData>
@@ -3287,37 +3287,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.452987754265209e-05</v>
+        <v>1.452987754265208e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.468726805347331e-05</v>
+        <v>1.468726805347332e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.560327975303828e-05</v>
+        <v>1.560327975303827e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.499870929775515e-05</v>
+        <v>1.499870929775514e-05</v>
       </c>
       <c r="F2" t="n">
         <v>1.499870929775515e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.505133098548001e-05</v>
+        <v>1.505133098547998e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.539594071908109e-05</v>
+        <v>1.539594071908108e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.491509038485223e-05</v>
+        <v>1.491509038485222e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.572882718118044e-05</v>
+        <v>1.572882718118042e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.479846179953044e-05</v>
+        <v>1.479846179953042e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.496312749338737e-05</v>
+        <v>1.496312749338736e-05</v>
       </c>
     </row>
     <row r="3">
@@ -3327,37 +3327,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.489279600984112e-05</v>
+        <v>1.48927960098411e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.50914339210976e-05</v>
+        <v>1.509143392109759e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.612743090638325e-05</v>
+        <v>1.612743090638322e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.541951681030437e-05</v>
+        <v>1.541951681030434e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.541951681030438e-05</v>
+        <v>1.541951681030434e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.54925754878485e-05</v>
+        <v>1.549257548784848e-05</v>
       </c>
       <c r="H3" t="n">
         <v>1.588927520604914e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.533340035840305e-05</v>
+        <v>1.533340035840303e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.622613767426643e-05</v>
+        <v>1.622613767426639e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.517040680726022e-05</v>
+        <v>1.517040680726021e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.539143418343507e-05</v>
+        <v>1.539143418343506e-05</v>
       </c>
     </row>
     <row r="4">
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.978307826486353e-05</v>
+        <v>1.249486095563656e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.883606552979276e-05</v>
+        <v>1.246515278826019e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>2.042117039502816e-05</v>
+        <v>1.313295308580122e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.933653040814987e-05</v>
+        <v>1.260504762787375e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.933653040814987e-05</v>
+        <v>1.260504762787375e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>2.002583608578817e-05</v>
+        <v>1.279301148032916e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>2.02985308996521e-05</v>
+        <v>1.301031359042513e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.972756114430937e-05</v>
+        <v>1.267384402711497e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>2.031494618895669e-05</v>
+        <v>1.302672887972973e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.981880157022429e-05</v>
+        <v>1.253058426099732e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>2.004207004573031e-05</v>
+        <v>1.275385273650337e-05</v>
       </c>
     </row>
     <row r="5">
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.500767508165461e-05</v>
+        <v>2.573438992365201e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0002292605140197683</v>
+        <v>4.949985552181975e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0002683455405918758</v>
+        <v>5.676764200400726e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0002320117387702197</v>
+        <v>5.0035884096775e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0002320117387702197</v>
+        <v>5.0035884096775e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0002408865195243028</v>
+        <v>5.166449155487786e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0002805983308458982</v>
+        <v>5.882307813272316e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0002320117084183388</v>
+        <v>5.00358537448938e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0002680080565492966</v>
+        <v>5.662071606693103e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0002135486839532996</v>
+        <v>4.662704337566335e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0002579203327322769</v>
+        <v>5.462042674247706e-05</v>
       </c>
     </row>
     <row r="6">
@@ -3447,37 +3447,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.481407205723082e-05</v>
+        <v>1.690031583922181e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>2.68182438018019e-05</v>
+        <v>1.387001615652139e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>2.77390805629819e-05</v>
+        <v>1.442090526838217e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>2.6707148491876e-05</v>
+        <v>1.390227640358038e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>2.701606997691277e-05</v>
+        <v>1.395664658465223e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>4.505682987815553e-05</v>
+        <v>1.719846636391392e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>4.761149430339479e-05</v>
+        <v>1.781739512343617e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>2.699777257504428e-05</v>
+        <v>1.395340123199071e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>4.582322121932683e-05</v>
+        <v>1.751618526074829e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>2.705880890061359e-05</v>
+        <v>1.380482554424129e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>2.732950581235787e-05</v>
+        <v>1.403644142447997e-05</v>
       </c>
     </row>
     <row r="7">
@@ -3487,37 +3487,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.591244523789843e-05</v>
+        <v>2.061362949889831e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>6.579044765751577e-05</v>
+        <v>2.072912399796025e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>6.655051619759074e-05</v>
+        <v>2.125171790305987e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>6.588631181915371e-05</v>
+        <v>2.07978091118171e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>6.588631181915371e-05</v>
+        <v>2.07978091118171e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>6.615520305882311e-05</v>
+        <v>2.091178002359044e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>6.6427897872687e-05</v>
+        <v>2.112908213368688e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>6.585692811734425e-05</v>
+        <v>2.079261257037653e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>6.644431316199157e-05</v>
+        <v>2.114549742299148e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>6.594816854325922e-05</v>
+        <v>2.064935280425906e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>6.617143701876524e-05</v>
+        <v>2.087262127976512e-05</v>
       </c>
     </row>
     <row r="8">
@@ -3527,37 +3527,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0002464833845163379</v>
+        <v>5.239411463969785e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0003920005684903844</v>
+        <v>7.814210495344705e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0004228913482676705</v>
+        <v>8.396770400756092e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0003522455489189545</v>
+        <v>7.119703456828869e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0002510601586784792</v>
+        <v>5.338840598246293e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0003923085527719952</v>
+        <v>7.831476926206473e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>0.000392581247586136</v>
+        <v>7.853207137220989e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0003920102778305167</v>
+        <v>7.819560180885087e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0003926262740115534</v>
+        <v>7.855352222144308e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0002438148398037489</v>
+        <v>5.195388677647841e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0005443977878550854</v>
+        <v>0.0001050404585708853</v>
       </c>
     </row>
     <row r="9">
@@ -3567,37 +3567,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0001423354925572954</v>
+        <v>3.406408575422949e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0001767761255940978</v>
+        <v>4.026260320895448e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>0.000177536218457026</v>
+        <v>4.078520139487626e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0002167271729433685</v>
+        <v>4.734580052582589e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0001768426290472483</v>
+        <v>4.032612083814558e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0001771408809954051</v>
+        <v>4.044525923458469e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>0.000177413575809269</v>
+        <v>4.06625613446811e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0001768426060539262</v>
+        <v>4.032609178137076e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0001774299910985737</v>
+        <v>4.067897663398573e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0001569081238881959</v>
+        <v>3.651531031680718e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0001771571149553471</v>
+        <v>4.040610049075934e-05</v>
       </c>
     </row>
   </sheetData>
@@ -3683,37 +3683,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.427190659205835e-05</v>
+        <v>1.427190659205823e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.419297201494529e-05</v>
+        <v>1.41929720149453e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.531872766789756e-05</v>
+        <v>1.531872766789762e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.466738641885176e-05</v>
+        <v>1.466738641885149e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.466738641885176e-05</v>
+        <v>1.466738641885153e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.467817363059852e-05</v>
+        <v>1.467817363059847e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.51094725313619e-05</v>
+        <v>1.510947253136186e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.469285213158282e-05</v>
+        <v>1.469285213158278e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.461743437590702e-05</v>
+        <v>1.461743437590688e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.447174863982066e-05</v>
+        <v>1.447174863982069e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.446086878235903e-05</v>
+        <v>1.446086878235902e-05</v>
       </c>
     </row>
     <row r="3">
@@ -3723,37 +3723,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.456500398895102e-05</v>
+        <v>1.45650039889506e-05</v>
       </c>
       <c r="C3" t="n">
         <v>1.449853865323121e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.57690650744987e-05</v>
+        <v>1.57690650744984e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.502373474747747e-05</v>
+        <v>1.502373474747758e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.502373474747747e-05</v>
+        <v>1.502373474747714e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.50322952412357e-05</v>
+        <v>1.503229524123528e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.552866573813951e-05</v>
+        <v>1.552866573813952e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.504637751086042e-05</v>
+        <v>1.504637751086007e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.495059853018775e-05</v>
+        <v>1.495059853018751e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.4775875245937e-05</v>
+        <v>1.477587524593698e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.47826487578362e-05</v>
+        <v>1.478264875783618e-05</v>
       </c>
     </row>
     <row r="4">
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.852987895542845e-05</v>
+        <v>1.211105199057113e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.752804161843514e-05</v>
+        <v>1.197737531434634e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.915216972744334e-05</v>
+        <v>1.273334276258578e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.805373215100761e-05</v>
+        <v>1.223351462974717e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.805373215100761e-05</v>
+        <v>1.223351462974717e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.870480642529207e-05</v>
+        <v>1.234084226181059e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.902835057064036e-05</v>
+        <v>1.260952360578285e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.849923790472049e-05</v>
+        <v>1.231191624473659e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.868844657084287e-05</v>
+        <v>1.226961960598504e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.857352799319772e-05</v>
+        <v>1.215470102833976e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.864364277339688e-05</v>
+        <v>1.222481580853988e-05</v>
       </c>
     </row>
     <row r="5">
@@ -3803,37 +3803,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.402631874933008e-05</v>
+        <v>2.36384253318356e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0002143959145779998</v>
+        <v>4.662612076748188e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0002658715837277972</v>
+        <v>5.615595939135825e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>0.000231021456733506</v>
+        <v>4.971583395316515e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>0.000231021456733506</v>
+        <v>4.971583395316515e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0002311775790290042</v>
+        <v>4.97360500374333e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>0.000276619944122823</v>
+        <v>5.794564382530817e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0002310214477562741</v>
+        <v>4.971582497593308e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0002282038569995792</v>
+        <v>4.914433164163321e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0002102975558123391</v>
+        <v>4.589812974166634e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0002379698731154724</v>
+        <v>5.082623213957908e-05</v>
       </c>
     </row>
     <row r="6">
@@ -3843,37 +3843,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.394125218637246e-05</v>
+        <v>1.34101774489872e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>2.558009243187353e-05</v>
+        <v>1.339453624983246e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>2.662104481003701e-05</v>
+        <v>1.404786476999945e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>2.564413805010914e-05</v>
+        <v>1.356942606075025e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>2.589798231256883e-05</v>
+        <v>1.361410265070109e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>4.411617965623601e-05</v>
+        <v>1.681324392622261e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>4.563502179048931e-05</v>
+        <v>1.729229771510229e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>2.588063259480965e-05</v>
+        <v>1.678431790914851e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>4.441230693345517e-05</v>
+        <v>1.679701900527281e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>2.594676747391314e-05</v>
+        <v>1.345239116991411e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>2.603879024167729e-05</v>
+        <v>1.35263617559047e-05</v>
       </c>
     </row>
     <row r="7">
@@ -3883,37 +3883,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.676981451566357e-05</v>
+        <v>2.060128060316728e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>6.653485085978669e-05</v>
+        <v>2.060257369408768e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>6.739207600643251e-05</v>
+        <v>2.1223566221683e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>6.67499682341959e-05</v>
+        <v>2.080405213394796e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>6.67499682341959e-05</v>
+        <v>2.080405213394796e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>6.694474198552718e-05</v>
+        <v>2.083107087440676e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>6.726828613087523e-05</v>
+        <v>2.109975221837888e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>6.673917346495553e-05</v>
+        <v>2.080214485733275e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>6.692838213107751e-05</v>
+        <v>2.075984821858133e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>6.681346355343229e-05</v>
+        <v>2.064492964093598e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>6.688357833363236e-05</v>
+        <v>2.071504442113608e-05</v>
       </c>
     </row>
     <row r="8">
@@ -3923,37 +3923,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000256467208057943</v>
+        <v>5.3988021685699e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0004087866163846117</v>
+        <v>8.083888410006001e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0004412282800708167</v>
+        <v>8.70187377804962e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0003672754505244308</v>
+        <v>7.369653673042597e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0002612774862445628</v>
+        <v>5.504089511825664e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.000409156143646704</v>
+        <v>8.106027724041586e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0004094796877921077</v>
+        <v>8.13289585843976e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0004089505751261322</v>
+        <v>8.103135122334181e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0004091697571920324</v>
+        <v>8.099432990292243e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0002536778310917817</v>
+        <v>5.353305814947792e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0005684086145144548</v>
+        <v>0.0001089834503106694</v>
       </c>
     </row>
     <row r="9">
@@ -3963,37 +3963,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0001618307475245147</v>
+        <v>3.733200472206776e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0002018058524294931</v>
+        <v>4.441026984135151e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>0.00020266310926383</v>
+        <v>4.503126794598011e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0002484117431064373</v>
+        <v>5.277652433821626e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0002020101763247961</v>
+        <v>4.460984862889947e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0002022157435552334</v>
+        <v>4.463876702167064e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0002025392877005815</v>
+        <v>4.490744836564287e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0002020101750346618</v>
+        <v>4.460984100459661e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0002021993837007837</v>
+        <v>4.456754436584512e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0001778413703553201</v>
+        <v>4.035220057968868e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0002021545799033388</v>
+        <v>4.452274056839988e-05</v>
       </c>
     </row>
   </sheetData>
@@ -4079,37 +4079,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.451257910616732e-05</v>
+        <v>1.451257910616707e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.456879290335822e-05</v>
+        <v>1.456879290335823e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.559341285129177e-05</v>
+        <v>1.559341285129163e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.495366552668906e-05</v>
+        <v>1.495366552668907e-05</v>
       </c>
       <c r="F2" t="n">
         <v>1.495366552668906e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.500492435282456e-05</v>
+        <v>1.500492435282435e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.541393101762936e-05</v>
+        <v>1.541393101762937e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.491501082192537e-05</v>
+        <v>1.491501082192564e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.547045707323158e-05</v>
+        <v>1.547045707323179e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.482429526504735e-05</v>
+        <v>1.482429526504726e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.48806295501251e-05</v>
+        <v>1.488062955012512e-05</v>
       </c>
     </row>
     <row r="3">
@@ -4119,34 +4119,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.485772431139287e-05</v>
+        <v>1.485772431139302e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.494071040250112e-05</v>
+        <v>1.494071040250114e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.61009070123222e-05</v>
+        <v>1.610090701232209e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.535927880411545e-05</v>
+        <v>1.53592788041152e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.535927880411545e-05</v>
+        <v>1.53592788041152e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.542402333405956e-05</v>
+        <v>1.542402333405952e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.589473081540812e-05</v>
+        <v>1.589473081540811e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.531794814162154e-05</v>
+        <v>1.531794814162134e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.594452433859294e-05</v>
+        <v>1.59445243385928e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.517959215464459e-05</v>
+        <v>1.517959215464439e-05</v>
       </c>
       <c r="L3" t="n">
         <v>1.528136622026054e-05</v>
@@ -4159,37 +4159,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.887516615973517e-05</v>
+        <v>1.228661843398266e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.79260053438021e-05</v>
+        <v>1.220907581277984e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9517676022401e-05</v>
+        <v>1.292912829664843e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.842442492705048e-05</v>
+        <v>1.240447740856417e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.842442492705047e-05</v>
+        <v>1.240447740856417e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.910046318387658e-05</v>
+        <v>1.25674377009366e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.941156908156829e-05</v>
+        <v>1.282302135581574e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.882842764461361e-05</v>
+        <v>1.247556185050788e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.938538622700672e-05</v>
+        <v>1.279683850125376e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.89153423179297e-05</v>
+        <v>1.232679459217739e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.909538968725263e-05</v>
+        <v>1.250684196150014e-05</v>
       </c>
     </row>
     <row r="5">
@@ -4199,37 +4199,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.218277657394326e-05</v>
+        <v>2.518875779697166e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0002209884862282682</v>
+        <v>4.79480722547904e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>0.000265972509543606</v>
+        <v>5.630517876134291e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0002301560805915591</v>
+        <v>4.966924860359425e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0002301560805915591</v>
+        <v>4.966924860359425e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0002364034107805233</v>
+        <v>5.08127562707106e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0002797038044751845</v>
+        <v>5.86344545368582e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0002301560562760707</v>
+        <v>4.966922428810616e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0002630169525145008</v>
+        <v>5.56759939355077e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0002111712641812364</v>
+        <v>4.616383665676966e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0002506793786606659</v>
+        <v>5.326562379996517e-05</v>
       </c>
     </row>
     <row r="6">
@@ -4239,37 +4239,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.326074225868202e-05</v>
+        <v>1.353950685042668e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>2.571058595263236e-05</v>
+        <v>1.357916199251001e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>2.670847543384366e-05</v>
+        <v>1.419471277399605e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>2.570191637924589e-05</v>
+        <v>1.368531589721021e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>2.596439155278348e-05</v>
+        <v>1.373151152750252e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>2.621914740679044e-05</v>
+        <v>1.382032611738057e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>4.548631640325934e-05</v>
+        <v>1.741217685956665e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>2.594711186752799e-05</v>
+        <v>1.676742322066667e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>2.699087197054296e-05</v>
+        <v>1.715281011640187e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>2.60127633021856e-05</v>
+        <v>1.357594067863784e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>2.623017200784456e-05</v>
+        <v>1.37625636431202e-05</v>
       </c>
     </row>
     <row r="7">
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.463428293398138e-05</v>
+        <v>2.03402229426108e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>6.445546914545829e-05</v>
+        <v>2.039826139749734e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>6.52767779949931e-05</v>
+        <v>2.098273020018545e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>6.460791075458888e-05</v>
+        <v>2.053277087016694e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>6.460791075458888e-05</v>
+        <v>2.053277087016694e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>6.485957995812271e-05</v>
+        <v>2.062104220956471e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>6.517068585581439e-05</v>
+        <v>2.0876625864444e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>6.458754441886041e-05</v>
+        <v>2.052916635913597e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>6.514450300125248e-05</v>
+        <v>2.085044300988192e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>6.467445909217619e-05</v>
+        <v>2.038039910080548e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>6.485450646149885e-05</v>
+        <v>2.056044647012832e-05</v>
       </c>
     </row>
     <row r="8">
@@ -4319,37 +4319,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.00024462343165878</v>
+        <v>5.201831294652429e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0003892275116028888</v>
+        <v>7.755814056027829e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0004200126078018022</v>
+        <v>8.341623590788119e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0003497708126940344</v>
+        <v>7.072144133955659e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0002491767352209229</v>
+        <v>5.301688380022304e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0003895836633894906</v>
+        <v>7.77724805838042e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0003898947692873679</v>
+        <v>7.802806423871589e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0003893116278502273</v>
+        <v>7.768060473337537e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0003898970310197124</v>
+        <v>7.800688763142264e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0002419750820955208</v>
+        <v>5.158530858030694e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0005407663317564706</v>
+        <v>0.0001043209272681782</v>
       </c>
     </row>
     <row r="9">
@@ -4359,37 +4359,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0001472520754785729</v>
+        <v>3.488095435166834e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0001831411113262493</v>
+        <v>4.128693430812903e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0001839624376579715</v>
+        <v>4.187140618768218e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>0.000224894737818937</v>
+        <v>4.874325228063067e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0001832732035250866</v>
+        <v>4.141786228460647e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0001835452221389136</v>
+        <v>4.150971512019638e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0001838563280366055</v>
+        <v>4.17652987750757e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0001832731865996513</v>
+        <v>4.141783926976768e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.000183830145182044</v>
+        <v>4.173911592051359e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0001379442397978681</v>
+        <v>3.759104997356079e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0001835401486422902</v>
+        <v>4.144911938075999e-05</v>
       </c>
     </row>
   </sheetData>
@@ -4475,37 +4475,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.461421709338015e-05</v>
+        <v>1.461421709338016e-05</v>
       </c>
       <c r="C2" t="n">
         <v>1.477120630863335e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.563030319101615e-05</v>
+        <v>1.563030319101616e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.499856687882798e-05</v>
+        <v>1.499856687882802e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.499856687882798e-05</v>
+        <v>1.499856687882802e-05</v>
       </c>
       <c r="G2" t="n">
         <v>1.512915825297719e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.550155459389702e-05</v>
+        <v>1.550155459389705e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.501245897636672e-05</v>
+        <v>1.501245897636674e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.575561309701608e-05</v>
+        <v>1.575561309701609e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.483534096746101e-05</v>
+        <v>1.483534096746103e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.503479276021896e-05</v>
+        <v>1.503479276021897e-05</v>
       </c>
     </row>
     <row r="3">
@@ -4515,28 +4515,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.502278707698206e-05</v>
+        <v>1.502278707698208e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.521896599562409e-05</v>
+        <v>1.521896599562411e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.619149657086446e-05</v>
+        <v>1.61914965708645e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.546698043877331e-05</v>
+        <v>1.546698043877332e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.546698043877331e-05</v>
+        <v>1.546698043877332e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.561507608025848e-05</v>
+        <v>1.561507608025852e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.604369850670679e-05</v>
+        <v>1.604369850670681e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.547885728464396e-05</v>
+        <v>1.547885728464398e-05</v>
       </c>
       <c r="J3" t="n">
         <v>1.631234832931932e-05</v>
@@ -4545,7 +4545,7 @@
         <v>1.525291397675624e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.550685078688903e-05</v>
+        <v>1.550685078688905e-05</v>
       </c>
     </row>
     <row r="4">
@@ -4555,37 +4555,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.957560799112108e-05</v>
+        <v>1.244562680315682e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.862203102339165e-05</v>
+        <v>1.240802210299195e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>2.017962812094547e-05</v>
+        <v>1.30496469329812e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.919743194100689e-05</v>
+        <v>1.257422073733719e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.919743194100691e-05</v>
+        <v>1.25742207373372e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.981284635311785e-05</v>
+        <v>1.273961597129932e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>2.010370148214657e-05</v>
+        <v>1.297372029418231e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.951671066043928e-05</v>
+        <v>1.263039030108178e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>2.016198462115979e-05</v>
+        <v>1.303200343319555e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.961123823446407e-05</v>
+        <v>1.248125704649982e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.982706119245237e-05</v>
+        <v>1.269708000448809e-05</v>
       </c>
     </row>
     <row r="5">
@@ -4595,37 +4595,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.424522958693914e-05</v>
+        <v>2.55874801328103e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0002277233401919275</v>
+        <v>4.920985231723963e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0002644657049169511</v>
+        <v>5.604399621610891e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0002319631111903661</v>
+        <v>5.002098008231377e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0002319631111903661</v>
+        <v>5.002098008231377e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0002397498960530959</v>
+        <v>5.14485365087467e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0002810763142672794</v>
+        <v>5.890489989548288e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0002319630826823915</v>
+        <v>5.002095157434162e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0002724973446267587</v>
+        <v>5.744302655353515e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0002127885367591591</v>
+        <v>4.648046140261788e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0002562673309356176</v>
+        <v>5.431056725379821e-05</v>
       </c>
     </row>
     <row r="6">
@@ -4635,37 +4635,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.442623435741373e-05</v>
+        <v>1.371609137207729e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>2.655012523692172e-05</v>
+        <v>1.380336667701243e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>2.74445617161901e-05</v>
+        <v>1.432827523881583e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>2.647220004401072e-05</v>
+        <v>1.385457991652809e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>2.67583477475986e-05</v>
+        <v>1.390494191208663e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>4.466347271941059e-05</v>
+        <v>1.711332618806744e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>4.716523621514282e-05</v>
+        <v>1.773655038138177e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>2.673525938660201e-05</v>
+        <v>1.700410051784985e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>4.547653472471949e-05</v>
+        <v>1.439082463992155e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>2.6798058544503e-05</v>
+        <v>1.374613741421277e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>2.706887546529671e-05</v>
+        <v>1.397163930960233e-05</v>
       </c>
     </row>
     <row r="7">
@@ -4675,37 +4675,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.559815397396408e-05</v>
+        <v>2.054559485224664e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>6.546807873604224e-05</v>
+        <v>2.065292645574264e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>6.62021562038656e-05</v>
+        <v>2.114961183168461e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>6.558898395372608e-05</v>
+        <v>2.073913384733331e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>6.558898395372608e-05</v>
+        <v>2.073913384733331e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>6.583539233596087e-05</v>
+        <v>2.083958402038916e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>6.612624746498959e-05</v>
+        <v>2.107368834327213e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>6.553925664328235e-05</v>
+        <v>2.073035835017162e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>6.618453060400278e-05</v>
+        <v>2.113197148228535e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>6.563378421730701e-05</v>
+        <v>2.058122509558963e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>6.584960717529542e-05</v>
+        <v>2.079704805357793e-05</v>
       </c>
     </row>
     <row r="8">
@@ -4715,37 +4715,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0002460510844070271</v>
+        <v>5.230531043637253e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0003913534008926833</v>
+        <v>7.800874284452293e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0004221518884827054</v>
+        <v>8.379676437330044e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0003516628884724069</v>
+        <v>7.108814076979985e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0002506294418521655</v>
+        <v>5.330625426099032e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0003916445467607498</v>
+        <v>7.81819948884363e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0003919354018900512</v>
+        <v>7.841609921136719e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0003913484110680713</v>
+        <v>7.807276921821868e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.000392022251714601</v>
+        <v>7.847941008700757e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0002433866481615674</v>
+        <v>5.186572898026104e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0005434954920715728</v>
+        <v>0.0001048627233398043</v>
       </c>
     </row>
     <row r="9">
@@ -4755,37 +4755,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0001420568567704666</v>
+        <v>3.400232647151434e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>0.000176433460446839</v>
+        <v>4.018283353101799e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>0.00017716755886459</v>
+        <v>4.067952259414721e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0002163246362545948</v>
+        <v>4.726860850853343e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0001765046595245301</v>
+        <v>4.026029264201745e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0001768007740467576</v>
+        <v>4.036949109566459e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0001770916291757861</v>
+        <v>4.060359541854749e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0001765046383540791</v>
+        <v>4.026026542544699e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0001771499123147994</v>
+        <v>4.066187855756068e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0001557947082075167</v>
+        <v>3.644954763188238e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0001768149888860918</v>
+        <v>4.032695512885327e-05</v>
       </c>
     </row>
   </sheetData>
@@ -4877,31 +4877,31 @@
         <v>1.373584570798723e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.362069835953594e-05</v>
+        <v>1.362069835953593e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.382498514159108e-05</v>
+        <v>1.382498514159109e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.357204975812956e-05</v>
+        <v>1.357204975812955e-05</v>
       </c>
       <c r="G2" t="n">
         <v>1.345279571693209e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.349317717035986e-05</v>
+        <v>1.349317717035989e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.338053917953708e-05</v>
+        <v>1.338053917953709e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.432329093625353e-05</v>
+        <v>1.43232909362535e-05</v>
       </c>
       <c r="K2" t="n">
         <v>1.382534598863613e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.355746288061404e-05</v>
+        <v>1.355746288061405e-05</v>
       </c>
     </row>
     <row r="3">
@@ -4911,16 +4911,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.357336931954303e-05</v>
+        <v>1.357336931954304e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.392279278034667e-05</v>
+        <v>1.392279278034666e-05</v>
       </c>
       <c r="D3" t="n">
         <v>1.384438772707456e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.401262086633025e-05</v>
+        <v>1.401262086633026e-05</v>
       </c>
       <c r="F3" t="n">
         <v>1.375968548286874e-05</v>
@@ -4929,19 +4929,19 @@
         <v>1.365126490715252e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.36980283286993e-05</v>
+        <v>1.369802832869932e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.356528644756939e-05</v>
+        <v>1.356528644756938e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.455149853173883e-05</v>
+        <v>1.455149853173886e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.401898491438673e-05</v>
+        <v>1.401898491438672e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.377191033210267e-05</v>
+        <v>1.377191033210268e-05</v>
       </c>
     </row>
     <row r="4">
@@ -4951,37 +4951,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.746302543811878e-05</v>
+        <v>1.167259465719146e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.67244706138635e-05</v>
+        <v>1.154045326275943e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.760309495458875e-05</v>
+        <v>1.181266417366146e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.677265700630573e-05</v>
+        <v>1.154893434924221e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.677265700630575e-05</v>
+        <v>1.154893434924221e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.743809013606017e-05</v>
+        <v>1.170137905639766e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.75279277336769e-05</v>
+        <v>1.173749695274959e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.718765714298647e-05</v>
+        <v>1.162195969748507e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.762097622769657e-05</v>
+        <v>1.183054544676923e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.748416776389261e-05</v>
+        <v>1.16937369829653e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.756680451483881e-05</v>
+        <v>1.17763737339114e-05</v>
       </c>
     </row>
     <row r="5">
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0001987943452715979</v>
+        <v>4.358690677495281e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0002182520816977607</v>
+        <v>4.70093126213336e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0002072528471816391</v>
+        <v>4.519102038475817e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0002182520820393369</v>
+        <v>4.700931296290991e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0002182520820393366</v>
+        <v>4.700931296290991e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0001992983239171475</v>
+        <v>4.370878002843358e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0002143706246938591</v>
+        <v>4.638181143001816e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0002182520642293649</v>
+        <v>4.700929515293757e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0002079908858335614</v>
+        <v>4.533564935585076e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0001938767610150373</v>
+        <v>4.273883322694556e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0002025901138152403</v>
+        <v>4.43404759943296e-05</v>
       </c>
     </row>
     <row r="6">
@@ -5031,37 +5031,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.263513250604344e-05</v>
+        <v>1.610288547714021e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>2.464052515272721e-05</v>
+        <v>1.293367885405012e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>2.512687455207799e-05</v>
+        <v>1.313684937564431e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>2.443100809033337e-05</v>
+        <v>1.289680413272749e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>2.467499603123379e-05</v>
+        <v>1.293974601009331e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>2.491626843287831e-05</v>
+        <v>1.61316698763464e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>2.502022620944041e-05</v>
+        <v>1.618178920262177e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>4.235976421091118e-05</v>
+        <v>1.605225051743382e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>4.286239736364188e-05</v>
+        <v>1.627303554262359e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>2.499070386723895e-05</v>
+        <v>1.301488732999546e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>2.506026817608527e-05</v>
+        <v>1.309522333114446e-05</v>
       </c>
     </row>
     <row r="7">
@@ -5071,37 +5071,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.585668380060181e-05</v>
+        <v>2.018987848283669e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>6.55813329738655e-05</v>
+        <v>2.013926099152626e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>6.599658283858111e-05</v>
+        <v>2.032991799509247e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>6.558015276107326e-05</v>
+        <v>2.013905355553483e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>6.558015276107326e-05</v>
+        <v>2.013905355553483e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>6.583174849854328e-05</v>
+        <v>2.021866288204288e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>6.592158609615992e-05</v>
+        <v>2.025478077839479e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>6.558131550546946e-05</v>
+        <v>2.013924352313027e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>6.601463459017962e-05</v>
+        <v>2.034782927241444e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>6.587782612637565e-05</v>
+        <v>2.021102080861051e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>6.596046287732178e-05</v>
+        <v>2.029365755955661e-05</v>
       </c>
     </row>
     <row r="8">
@@ -5111,37 +5111,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0002576515129399131</v>
+        <v>5.39457682284457e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0004111170326921858</v>
+        <v>8.095354381242215e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0004433762400293144</v>
+        <v>8.674873730076436e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0003690751746139218</v>
+        <v>7.355417711220086e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0002622479790968263</v>
+        <v>5.475259080307031e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0004113381411722432</v>
+        <v>8.102778766311343e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0004114279787698536</v>
+        <v>8.10639055594644e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0004110877081791697</v>
+        <v>8.094836830420087e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0004115512360183816</v>
+        <v>8.116227079424878e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0002548173840552047</v>
+        <v>5.346438282389771e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0005720314368402362</v>
+        <v>0.0001093621484944028</v>
       </c>
     </row>
     <row r="9">
@@ -5151,37 +5151,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0001611921280153828</v>
+        <v>3.696891657371917e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0002011439481743447</v>
+        <v>4.3998281137528e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0002015593697589026</v>
+        <v>4.418896836378628e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0002475652422447439</v>
+        <v>5.216842913110637e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0002011439407103121</v>
+        <v>4.399828010531719e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0002013943636990225</v>
+        <v>4.407768302804462e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>0.000201484201296639</v>
+        <v>4.411380092439654e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0002011439307059487</v>
+        <v>4.399826366913204e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0002015772497906587</v>
+        <v>4.420684941841622e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>0.000178132660995554</v>
+        <v>3.996787163853135e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0002015230780778008</v>
+        <v>4.415267770555838e-05</v>
       </c>
     </row>
   </sheetData>
@@ -5267,37 +5267,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.35257214313936e-05</v>
+        <v>1.352572143139362e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.385186953520002e-05</v>
+        <v>1.38518695352e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.369762915391409e-05</v>
+        <v>1.369762915391365e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.394601161897337e-05</v>
+        <v>1.394601161897335e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.367851458250128e-05</v>
+        <v>1.367851458250126e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.356129021371194e-05</v>
+        <v>1.356129021371175e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.363874573781547e-05</v>
+        <v>1.363874573781546e-05</v>
       </c>
       <c r="I2" t="n">
         <v>1.348143607894037e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.454025157573202e-05</v>
+        <v>1.454025157573197e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.39926905300635e-05</v>
+        <v>1.399269053006351e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.365347888462701e-05</v>
+        <v>1.365347888462681e-05</v>
       </c>
     </row>
     <row r="3">
@@ -5307,37 +5307,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.373483258496692e-05</v>
+        <v>1.373483258496709e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.405366120891682e-05</v>
+        <v>1.405366120891681e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.393256207644307e-05</v>
+        <v>1.393256207644175e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.414849122765166e-05</v>
+        <v>1.414849122765164e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.388099419117954e-05</v>
+        <v>1.388099419117952e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.377574405268433e-05</v>
+        <v>1.377574405268413e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.386514555187287e-05</v>
+        <v>1.386514555187284e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.368110452219129e-05</v>
+        <v>1.368110452219128e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.479521642398425e-05</v>
+        <v>1.479521642398421e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.420831277523352e-05</v>
+        <v>1.420831277523348e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.388203552793076e-05</v>
+        <v>1.388203552793085e-05</v>
       </c>
     </row>
     <row r="4">
@@ -5347,37 +5347,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.767923050795648e-05</v>
+        <v>1.177895207722743e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.695001264124966e-05</v>
+        <v>1.162898363555495e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.778142236464688e-05</v>
+        <v>1.188114393391735e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.700302386575934e-05</v>
+        <v>1.1638313906705e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.700302386575936e-05</v>
+        <v>1.1638313906705e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.763517644912941e-05</v>
+        <v>1.178862132927856e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.774705333767708e-05</v>
+        <v>1.184677490694782e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.738027555436347e-05</v>
+        <v>1.170469443895758e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.786070042209787e-05</v>
+        <v>1.196042199136879e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.770499870921629e-05</v>
+        <v>1.180472027848716e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.775648919588245e-05</v>
+        <v>1.185621076515339e-05</v>
       </c>
     </row>
     <row r="5">
@@ -5387,37 +5387,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0001875010881021394</v>
+        <v>4.166759885184881e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0002135936506143259</v>
+        <v>4.62382637312824e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0002039145162733771</v>
+        <v>4.464056828433903e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0002135936509731695</v>
+        <v>4.623826409012581e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0002135936509731695</v>
+        <v>4.623826409012581e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0001962516793195623</v>
+        <v>4.322512566413321e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0002079085730798831</v>
+        <v>4.531520220022395e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0002135936318413953</v>
+        <v>4.623824495835158e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0002041832528462645</v>
+        <v>4.475319104033109e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0002048814737314948</v>
+        <v>4.474777970390278e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0002113345040120725</v>
+        <v>4.470179056998559e-05</v>
       </c>
     </row>
     <row r="6">
@@ -5427,37 +5427,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.467470020708309e-05</v>
+        <v>1.59393524882759e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>2.434604336720866e-05</v>
+        <v>1.293068503627028e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>2.481219284416771e-05</v>
+        <v>1.311855953160225e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>2.414972708961046e-05</v>
+        <v>1.289613366728718e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>2.438332043960875e-05</v>
+        <v>1.293724609666412e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>2.463064614825581e-05</v>
+        <v>1.594902174032716e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>4.15430464293617e-05</v>
+        <v>1.603486966839061e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>2.437574525348992e-05</v>
+        <v>1.586509485000609e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>2.530994441127172e-05</v>
+        <v>1.613063223920151e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>2.47254277199488e-05</v>
+        <v>1.304031577768083e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>2.476410529803215e-05</v>
+        <v>1.308955119244873e-05</v>
       </c>
     </row>
     <row r="7">
@@ -5467,37 +5467,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.284114458651075e-05</v>
+        <v>1.972744891198327e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>6.254220840584855e-05</v>
+        <v>1.965321004664421e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>6.294316222057371e-05</v>
+        <v>1.982961010549081e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>6.254451073061412e-05</v>
+        <v>1.965361555148775e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>6.254451073061412e-05</v>
+        <v>1.965361555148775e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>6.27970905276837e-05</v>
+        <v>1.97371181640345e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>6.290896741623134e-05</v>
+        <v>1.979527174170366e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>6.254218963291778e-05</v>
+        <v>1.965319127371337e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>6.30226145006523e-05</v>
+        <v>1.990891882612459e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>6.286691278777069e-05</v>
+        <v>1.975321711324298e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>6.291840327443667e-05</v>
+        <v>1.980470759990919e-05</v>
       </c>
     </row>
     <row r="8">
@@ -5507,37 +5507,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0002417077694018725</v>
+        <v>5.120797470890629e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0003848442986821786</v>
+        <v>7.637837762793316e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0004149507300906421</v>
+        <v>8.178294171492224e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0003456210857629589</v>
+        <v>6.94750924872174e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0002459560227556977</v>
+        <v>5.193404149298749e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0003850685562214839</v>
+        <v>7.645689581880137e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0003851804331100279</v>
+        <v>7.651504939646975e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0003848136553267189</v>
+        <v>7.637296892848032e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0003853222633804578</v>
+        <v>7.663365672160132e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0002390697190575654</v>
+        <v>5.076491084868659e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0005349882166073048</v>
+        <v>0.000102888994296293</v>
       </c>
     </row>
     <row r="9">
@@ -5547,37 +5547,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0001441611430191696</v>
+        <v>3.403976855857834e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0001793026579592557</v>
+        <v>4.020304905669226e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0001797037872580175</v>
+        <v>4.037948000072962e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0002202001794065838</v>
+        <v>4.74010130881061e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0001793026509691503</v>
+        <v>4.020304812212077e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0001795575400810905</v>
+        <v>4.028695717408277e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0001796694169696382</v>
+        <v>4.034511075175177e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0001793026391863249</v>
+        <v>4.020303028376147e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0001797830640540592</v>
+        <v>4.045875783617265e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0001350015079550775</v>
+        <v>3.244890579389603e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0001796788528278433</v>
+        <v>4.035454660995738e-05</v>
       </c>
     </row>
   </sheetData>
@@ -5663,16 +5663,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.355697785188961e-05</v>
+        <v>1.35569778518897e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.395594357092887e-05</v>
+        <v>1.395594357092891e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.377258296603334e-05</v>
+        <v>1.377258296603342e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.405267443703741e-05</v>
+        <v>1.405267443703751e-05</v>
       </c>
       <c r="F2" t="n">
         <v>1.377784065677067e-05</v>
@@ -5681,19 +5681,19 @@
         <v>1.363169941099951e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.370095242199383e-05</v>
+        <v>1.370095242199375e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.357675786650583e-05</v>
+        <v>1.357675786650594e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.475194609078893e-05</v>
+        <v>1.475194609078912e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.405339450786807e-05</v>
+        <v>1.405339450786835e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.37474311637709e-05</v>
+        <v>1.374743116377127e-05</v>
       </c>
     </row>
     <row r="3">
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.377124935401527e-05</v>
+        <v>1.377124935401542e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.417252268275605e-05</v>
+        <v>1.417252268275618e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.401923989774542e-05</v>
+        <v>1.401923989774557e-05</v>
       </c>
       <c r="E3" t="n">
         <v>1.426993894782347e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.39951051675566e-05</v>
+        <v>1.399510516755673e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.385719462551582e-05</v>
+        <v>1.385719462551605e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.3937144179737e-05</v>
+        <v>1.393714417973689e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.379134197024885e-05</v>
+        <v>1.379134197024909e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.503623223017665e-05</v>
+        <v>1.503623223017636e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.427712589562968e-05</v>
+        <v>1.42771258956299e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.399056359947043e-05</v>
+        <v>1.399056359947023e-05</v>
       </c>
     </row>
     <row r="4">
@@ -5743,37 +5743,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.781491785711316e-05</v>
+        <v>1.181772667121064e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.713618283728084e-05</v>
+        <v>1.170802940944173e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.794308596150795e-05</v>
+        <v>1.194589477560539e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.71924166218729e-05</v>
+        <v>1.171792680649399e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.719241662187289e-05</v>
+        <v>1.171792680649397e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.779421474250337e-05</v>
+        <v>1.185068401485329e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.790114305177517e-05</v>
+        <v>1.190395186587262e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.755458499406928e-05</v>
+        <v>1.178165550759422e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.809200676568409e-05</v>
+        <v>1.209481557978152e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.785235616270986e-05</v>
+        <v>1.185516497680725e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.792944582109684e-05</v>
+        <v>1.193225463519407e-05</v>
       </c>
     </row>
     <row r="5">
@@ -5783,37 +5783,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0001980555043906807</v>
+        <v>4.354006972922723e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0002208907163653247</v>
+        <v>4.756882711606211e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>0.000220186093985391</v>
+        <v>4.754066399493474e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0002208907166699577</v>
+        <v>4.756882742069441e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0002208907166699577</v>
+        <v>4.756882742069441e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0002075251514097712</v>
+        <v>4.524332868734911e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0002275403054898841</v>
+        <v>4.880044425505206e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0002208907009757089</v>
+        <v>4.756881172644527e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0002140211162633534</v>
+        <v>4.657833866451868e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0002197363505271104</v>
+        <v>4.738674779241029e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0002196610802088953</v>
+        <v>4.743702209506444e-05</v>
       </c>
     </row>
     <row r="6">
@@ -5823,37 +5823,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.483509841746716e-05</v>
+        <v>1.305327844313791e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>2.454839256760163e-05</v>
+        <v>1.301257831490949e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>4.19129675909116e-05</v>
+        <v>1.616459391952096e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>2.435016075041082e-05</v>
+        <v>1.297768976629068e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>2.458431170292811e-05</v>
+        <v>1.301890033371044e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>2.481439530285731e-05</v>
+        <v>1.308623578678059e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>4.182834074274849e-05</v>
+        <v>1.611513863666511e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>4.128591685350853e-05</v>
+        <v>1.595836989222365e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>4.187779561352966e-05</v>
+        <v>1.341107289783028e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>2.489408523535481e-05</v>
+        <v>1.309450928687726e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>2.496223052411783e-05</v>
+        <v>1.31700247362189e-05</v>
       </c>
     </row>
     <row r="7">
@@ -5863,37 +5863,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.301524736720787e-05</v>
+        <v>1.977298462188088e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>6.275492989377952e-05</v>
+        <v>1.973692884788023e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>6.314323592418739e-05</v>
+        <v>1.990112112593075e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>6.276188745800665e-05</v>
+        <v>1.973815363019518e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>6.276188745800665e-05</v>
+        <v>1.973815363019518e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>6.299454425259799e-05</v>
+        <v>1.980594196552349e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>6.310147256186983e-05</v>
+        <v>1.985920981654282e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>6.275491450416397e-05</v>
+        <v>1.973691345826451e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>6.329233627577872e-05</v>
+        <v>2.00500735304518e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>6.305268567280442e-05</v>
+        <v>1.981042292747751e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>6.312977533119151e-05</v>
+        <v>1.988751258586472e-05</v>
       </c>
     </row>
     <row r="8">
@@ -5903,37 +5903,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0002419418931425954</v>
+        <v>5.126407410771122e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0003852014711940049</v>
+        <v>7.64875198092107e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0004153073610908707</v>
+        <v>8.188200681941703e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0003459559121178492</v>
+        <v>6.958030170025264e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0002462340798012458</v>
+        <v>5.202925930763265e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0003854059832739809</v>
+        <v>7.655035492581131e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0003855129115832503</v>
+        <v>7.660362277683013e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0003851663535255465</v>
+        <v>7.648132641855226e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0003857319741959272</v>
+        <v>7.679944949689535e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0002393140277463435</v>
+        <v>5.083241896432443e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0005354230789249395</v>
+        <v>0.0001030111335679498</v>
       </c>
     </row>
     <row r="9">
@@ -5943,37 +5943,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0001383217968970815</v>
+        <v>3.302693726732069e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0001718570810709676</v>
+        <v>3.893890735101726e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0001722455680121474</v>
+        <v>3.910313146936357e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0002108564811604873</v>
+        <v>4.580280198059777e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>0.000171857074042766</v>
+        <v>3.893890636507162e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0001720966954297856</v>
+        <v>3.900792046866068e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0001722036237390577</v>
+        <v>3.906118831967997e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0001718570656813519</v>
+        <v>3.893889196140161e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0001723944874529667</v>
+        <v>3.925205203358891e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0001525735331033885</v>
+        <v>3.556609198988663e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0001722319265083793</v>
+        <v>3.90894910890016e-05</v>
       </c>
     </row>
   </sheetData>
@@ -6059,37 +6059,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.364342746864129e-05</v>
+        <v>1.364342746864133e-05</v>
       </c>
       <c r="C2" t="n">
         <v>1.38350250143851e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.377926446517784e-05</v>
+        <v>1.377926446517785e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.39249647680593e-05</v>
+        <v>1.392496476805925e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.366971112724595e-05</v>
+        <v>1.366971112724588e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.352334536725882e-05</v>
+        <v>1.352334536725871e-05</v>
       </c>
       <c r="H2" t="n">
         <v>1.350588487130131e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.3475807184102e-05</v>
+        <v>1.347580718410194e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.444553203716782e-05</v>
+        <v>1.444553203716767e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.39307261644606e-05</v>
+        <v>1.393072616446059e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.360094044927281e-05</v>
+        <v>1.360094044927282e-05</v>
       </c>
     </row>
     <row r="3">
@@ -6099,34 +6099,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.387213405980556e-05</v>
+        <v>1.387213405980548e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.403790198945493e-05</v>
+        <v>1.403790198945491e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.402837474437166e-05</v>
+        <v>1.402837474437155e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.41285148191505e-05</v>
+        <v>1.412851481915043e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.387326117833713e-05</v>
+        <v>1.387326117833709e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.373401476828311e-05</v>
+        <v>1.37340147682831e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.37142255659495e-05</v>
+        <v>1.371422556594948e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.367656992162713e-05</v>
+        <v>1.367656992162705e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.469263803102806e-05</v>
+        <v>1.469263803102794e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.414076004411562e-05</v>
+        <v>1.414076004411551e-05</v>
       </c>
       <c r="L3" t="n">
         <v>1.382352244904636e-05</v>
@@ -6139,37 +6139,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.76699951119937e-05</v>
+        <v>1.183515064092603e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.684796449704363e-05</v>
+        <v>1.160843627650613e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.775074445053287e-05</v>
+        <v>1.191589997946517e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.689603003603978e-05</v>
+        <v>1.161689604320029e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.689603003603978e-05</v>
+        <v>1.16168960432003e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.753341485427084e-05</v>
+        <v>1.175229232955653e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.758888456542284e-05</v>
+        <v>1.175404009435517e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.729766952029025e-05</v>
+        <v>1.168757269755418e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.774281232009253e-05</v>
+        <v>1.190796784902486e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.759609626091742e-05</v>
+        <v>1.176125178984976e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.764604828326242e-05</v>
+        <v>1.181120381219472e-05</v>
       </c>
     </row>
     <row r="5">
@@ -6179,37 +6179,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.000216568799361974</v>
+        <v>4.68413399992378e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0002252470182499008</v>
+        <v>4.828666953826423e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0002566111761473472</v>
+        <v>5.395533573030934e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0002252470185313044</v>
+        <v>4.828666981966789e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0002252470185313044</v>
+        <v>4.828666981966789e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0002255242699284044</v>
+        <v>4.835868262424854e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0002589815188690087</v>
+        <v>5.423914350157632e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0002252470040962424</v>
+        <v>4.828665538460583e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0002148614604250711</v>
+        <v>4.660084972751405e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0002175138090389298</v>
+        <v>4.694676904812351e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0002425784900069306</v>
+        <v>4.974907265965191e-05</v>
       </c>
     </row>
     <row r="6">
@@ -6219,37 +6219,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.517715079029283e-05</v>
+        <v>1.315641003314725e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>2.478487148348377e-05</v>
+        <v>1.300533189855033e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>2.531422185025161e-05</v>
+        <v>1.640436434340661e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>2.457278388290695e-05</v>
+        <v>1.296800471292776e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>2.481658492181344e-05</v>
+        <v>1.301091369554279e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>4.276948161982385e-05</v>
+        <v>1.307355172177778e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>4.29012643700693e-05</v>
+        <v>1.620901891583319e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>4.253373628584323e-05</v>
+        <v>1.300883208977544e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>4.304588553742999e-05</v>
+        <v>1.636130871114534e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>2.513589519599708e-05</v>
+        <v>1.308825639523323e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>2.516879982973984e-05</v>
+        <v>1.313520807720049e-05</v>
       </c>
     </row>
     <row r="7">
@@ -6259,37 +6259,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.607990453617167e-05</v>
+        <v>2.035529465341408e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>6.570759309812655e-05</v>
+        <v>2.020773086370056e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>6.616047956122342e-05</v>
+        <v>2.043601331277961e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>6.571000487020478e-05</v>
+        <v>2.020815556746069e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>6.571000487020478e-05</v>
+        <v>2.020815556746069e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>6.594332427844884e-05</v>
+        <v>2.027243634204454e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>6.599879398960086e-05</v>
+        <v>2.027418410684323e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>6.570757894446823e-05</v>
+        <v>2.020771671004221e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>6.61527217442705e-05</v>
+        <v>2.042811186151285e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>6.60060056850954e-05</v>
+        <v>2.028139580233775e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>6.60559577074404e-05</v>
+        <v>2.033134782468285e-05</v>
       </c>
     </row>
     <row r="8">
@@ -6299,37 +6299,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0002578932245462705</v>
+        <v>5.411443879226398e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0004112945687116068</v>
+        <v>8.103103824207519e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0004435940542121251</v>
+        <v>8.686432209138976e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0003692443195000762</v>
+        <v>7.363019465284518e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>0.000262395805152957</v>
+        <v>5.482485622965092e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.000411497546923666</v>
+        <v>8.108997919805663e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0004115530166348123</v>
+        <v>8.109172696285436e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0004112618015896854</v>
+        <v>8.102525956605434e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0004117371589098324</v>
+        <v>8.125097247307686e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0002549635094958673</v>
+        <v>5.353791629282977e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0005722054087857534</v>
+        <v>0.0001094136507317643</v>
       </c>
     </row>
     <row r="9">
@@ -6339,37 +6339,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000161530422432204</v>
+        <v>3.715458571208702e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0002014247621706795</v>
+        <v>4.409395249103988e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0002018778244122964</v>
+        <v>4.432226587713821e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0002478916158606986</v>
+        <v>5.227211892804569e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0002014247547860717</v>
+        <v>4.409395142322552e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0002016604933510014</v>
+        <v>4.415865796938387e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0002017159630621534</v>
+        <v>4.416040573418248e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0002014247480170208</v>
+        <v>4.409393833738153e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0002018698908168229</v>
+        <v>4.431433348885212e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0001510202729748933</v>
+        <v>4.006142213411608e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0002017731267799931</v>
+        <v>4.421756945202205e-05</v>
       </c>
     </row>
   </sheetData>
@@ -6455,34 +6455,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.389684784958517e-05</v>
+        <v>1.389684784958534e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.415075580546761e-05</v>
+        <v>1.41507558054676e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.41475493585488e-05</v>
+        <v>1.414754935854906e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.42459989369342e-05</v>
+        <v>1.424599893693409e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.39750803168413e-05</v>
+        <v>1.397508031684127e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.386859017659108e-05</v>
+        <v>1.386859017659117e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.419630660569608e-05</v>
+        <v>1.419630660569605e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.377385640302918e-05</v>
+        <v>1.377385640302935e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.477516854408728e-05</v>
+        <v>1.477516854408739e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.427313870486953e-05</v>
+        <v>1.427313870486938e-05</v>
       </c>
       <c r="L2" t="n">
         <v>1.401891603449577e-05</v>
@@ -6495,37 +6495,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.416400274043846e-05</v>
+        <v>1.416400274043864e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.439876277273611e-05</v>
+        <v>1.43987627727361e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.445236140840775e-05</v>
+        <v>1.445236140840799e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.449470028621138e-05</v>
+        <v>1.449470028621166e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.422378166611849e-05</v>
+        <v>1.422378166611857e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.413150056293591e-05</v>
+        <v>1.41315005629363e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.450874926095744e-05</v>
+        <v>1.450874926095743e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.40197400971726e-05</v>
+        <v>1.401974009717268e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.506627731846397e-05</v>
+        <v>1.50662773184639e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.453163088785846e-05</v>
+        <v>1.453163088785842e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.430466123143106e-05</v>
+        <v>1.430466123143105e-05</v>
       </c>
     </row>
     <row r="4">
@@ -6535,37 +6535,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.801718995941275e-05</v>
+        <v>1.201890326519311e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.723858708449878e-05</v>
+        <v>1.1821690925843e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.816622138336753e-05</v>
+        <v>1.216793468914793e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.729367554177026e-05</v>
+        <v>1.183138679921907e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.729367554177026e-05</v>
+        <v>1.183138679921907e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.79350747718931e-05</v>
+        <v>1.199060944913807e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.819578369901514e-05</v>
+        <v>1.219749700479554e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.767070141248994e-05</v>
+        <v>1.189772571615242e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.811198949992519e-05</v>
+        <v>1.211370280570558e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.798290655295249e-05</v>
+        <v>1.19846198587329e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.809106627482992e-05</v>
+        <v>1.209277958061032e-05</v>
       </c>
     </row>
     <row r="5">
@@ -6575,37 +6575,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0002094868570468208</v>
+        <v>4.571756448997725e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0002333837976162987</v>
+        <v>4.986324777330764e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0002663457547851943</v>
+        <v>5.584753233118691e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0002333837979863823</v>
+        <v>4.986324814339115e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0002333837979863822</v>
+        <v>4.986324814339115e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0002358932422198332</v>
+        <v>5.035124671211353e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0002999087039182369</v>
+        <v>6.177897069471615e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.000233383776583526</v>
+        <v>4.986322674053471e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.00023864554528694</v>
+        <v>5.092760841390289e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0002209821535707139</v>
+        <v>4.771248714026379e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0002659226184003767</v>
+        <v>5.571113251835589e-05</v>
       </c>
     </row>
     <row r="6">
@@ -6615,37 +6615,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.509282125879775e-05</v>
+        <v>1.62109591390689e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>2.471659282324111e-05</v>
+        <v>1.313781992873007e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>2.529382960523106e-05</v>
+        <v>1.342240026704232e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>2.451527854225101e-05</v>
+        <v>1.310238892041662e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>2.475561518743591e-05</v>
+        <v>1.314468816973998e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>2.501070607127808e-05</v>
+        <v>1.323592055108205e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>4.219153560939019e-05</v>
+        <v>1.344630131829148e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>2.474633271187497e-05</v>
+        <v>1.314303681809632e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>2.564699076197784e-05</v>
+        <v>1.631647755478082e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>2.508519039483801e-05</v>
+        <v>1.323462180813146e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>2.518175102734587e-05</v>
+        <v>1.334074009029093e-05</v>
       </c>
     </row>
     <row r="7">
@@ -6655,37 +6655,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.324685591893948e-05</v>
+        <v>1.997932443093545e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>6.290038840478962e-05</v>
+        <v>1.985816791466772e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>6.339571190802676e-05</v>
+        <v>2.012832497835376e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>6.290281567984904e-05</v>
+        <v>1.985859542002468e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>6.290281567984901e-05</v>
+        <v>1.985859542002468e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>6.316474073141983e-05</v>
+        <v>1.995103061488046e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>6.342544965854187e-05</v>
+        <v>2.015791817053787e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>6.290036737201666e-05</v>
+        <v>1.985814688189473e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>6.334165545945188e-05</v>
+        <v>2.007412397144788e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>6.321257251247926e-05</v>
+        <v>1.994504102447523e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>6.332073223435665e-05</v>
+        <v>2.005320074635265e-05</v>
       </c>
     </row>
     <row r="8">
@@ -6695,37 +6695,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0002421716358616928</v>
+        <v>5.147008553022399e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0003853591885638564</v>
+        <v>7.661091643514267e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0004155802573327564</v>
+        <v>8.211280463723666e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0003461090449607556</v>
+        <v>6.970289150337761e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0002463755527319046</v>
+        <v>5.214979696621321e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0003855927759096207</v>
+        <v>7.669836449875245e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0003858534848367407</v>
+        <v>7.690525205440947e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0003853284025502174</v>
+        <v>7.660548076576658e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0003857978931647155</v>
+        <v>7.682642150005598e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>0.000239471705812476</v>
+        <v>5.096664831718082e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0005356499170766199</v>
+        <v>0.0001031831368281426</v>
       </c>
     </row>
     <row r="9">
@@ -6735,37 +6735,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0001449091757247273</v>
+        <v>3.435189263887482e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>0.000180124582020878</v>
+        <v>4.048962587930543e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0001806200823476864</v>
+        <v>4.075981406393989e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0002211622225194894</v>
+        <v>4.771225087287329e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0001801245748146566</v>
+        <v>4.048962491595933e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0001803889343475082</v>
+        <v>4.05824885795182e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0001806496432746305</v>
+        <v>4.078937613517565e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0001801245609881052</v>
+        <v>4.048960484653252e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0001805658490755403</v>
+        <v>4.07055819360857e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0001589961190575955</v>
+        <v>3.680294512506936e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0001805449258504451</v>
+        <v>4.068465871099046e-05</v>
       </c>
     </row>
   </sheetData>
@@ -6851,37 +6851,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.410561735815203e-05</v>
+        <v>1.410561735815206e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.439127138305864e-05</v>
+        <v>1.439127138305866e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.510630676320476e-05</v>
+        <v>1.510630676320477e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.449093366048497e-05</v>
+        <v>1.4490933660485e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.420782322624103e-05</v>
+        <v>1.420782322624104e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.413946170377179e-05</v>
+        <v>1.413946170377185e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.45359108887403e-05</v>
+        <v>1.453591088874033e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.400237620463165e-05</v>
+        <v>1.400237620463167e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.601387112024086e-05</v>
+        <v>1.601387112024089e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.439511198031438e-05</v>
+        <v>1.43951119803144e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.422302867815477e-05</v>
+        <v>1.422302867815479e-05</v>
       </c>
     </row>
     <row r="3">
@@ -6891,37 +6891,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.440373143745891e-05</v>
+        <v>1.440373143745894e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.467317335998168e-05</v>
+        <v>1.467317335998169e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.555473154545531e-05</v>
+        <v>1.555473154545534e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.477356056438299e-05</v>
+        <v>1.477356056438304e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.449045013013906e-05</v>
+        <v>1.449045013013909e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.444265944575656e-05</v>
+        <v>1.444265944575675e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.489895935962712e-05</v>
+        <v>1.489895935962714e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.428214360372126e-05</v>
+        <v>1.42821436037213e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.648563053946905e-05</v>
+        <v>1.64856305394691e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.46705007132066e-05</v>
+        <v>1.467050071320662e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.453903913084028e-05</v>
+        <v>1.453903913084029e-05</v>
       </c>
     </row>
     <row r="4">
@@ -6931,37 +6931,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.825415395231633e-05</v>
+        <v>1.216184031534621e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.747577463980268e-05</v>
+        <v>1.197434074745521e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.884902140081312e-05</v>
+        <v>1.2756707763843e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.753581533597398e-05</v>
+        <v>1.198490825997568e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.753581533597398e-05</v>
+        <v>1.19849082599757e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.820882747235829e-05</v>
+        <v>1.217044093513226e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.851051021365836e-05</v>
+        <v>1.241819657668817e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.791863055572548e-05</v>
+        <v>1.205226104456985e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.89413702202163e-05</v>
+        <v>1.284905658324615e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.816421645237036e-05</v>
+        <v>1.207190281540015e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.832529039096771e-05</v>
+        <v>1.223297675399754e-05</v>
       </c>
     </row>
     <row r="5">
@@ -6971,37 +6971,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0002218023615103551</v>
+        <v>4.798632465144235e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0002340847388026104</v>
+        <v>5.009751823353206e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0002935658909826371</v>
+        <v>6.110687654825369e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0002340847392274303</v>
+        <v>5.009751865835347e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0002340847392274303</v>
+        <v>5.009751865835347e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0002389118356188769</v>
+        <v>5.101417015844329e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0002866793456118353</v>
+        <v>5.961591135102165e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.000234084711686512</v>
+        <v>5.009749111743703e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0002961278254594655</v>
+        <v>6.163387244100849e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0002299897970077334</v>
+        <v>4.935320479113147e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0002575731863278832</v>
+        <v>5.346501215041706e-05</v>
       </c>
     </row>
     <row r="6">
@@ -7011,37 +7011,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.5410550606187e-05</v>
+        <v>1.342136611960259e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>2.503883982322223e-05</v>
+        <v>1.330544021252436e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>4.310232935700174e-05</v>
+        <v>1.403834191655439e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>2.483237625846455e-05</v>
+        <v>1.326910297537546e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>2.50828538466133e-05</v>
+        <v>1.33131870306508e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>2.536522412622873e-05</v>
+        <v>1.639328130235076e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>4.273133884331199e-05</v>
+        <v>1.668106239240846e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>2.507502720959618e-05</v>
+        <v>1.331178684882622e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>2.657984220150797e-05</v>
+        <v>1.708345043629524e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>2.533112568319363e-05</v>
+        <v>1.333327883319017e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>2.549527987470178e-05</v>
+        <v>1.349489489629689e-05</v>
       </c>
     </row>
     <row r="7">
@@ -7051,37 +7051,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.356362944473637e-05</v>
+        <v>2.013630795880166e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>6.322813316424429e-05</v>
+        <v>2.002675580412413e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>6.415831961029173e-05</v>
+        <v>2.073114420550096e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>6.32297768545074e-05</v>
+        <v>2.002704544366044e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>6.32297768545074e-05</v>
+        <v>2.002704544366044e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>6.35183029647784e-05</v>
+        <v>2.014490857858769e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>6.381998570607847e-05</v>
+        <v>2.039266422014366e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>6.32281060481455e-05</v>
+        <v>2.002672868802528e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>6.425084571263637e-05</v>
+        <v>2.082352422670157e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>6.347369194479013e-05</v>
+        <v>2.004637045885561e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>6.363476588338774e-05</v>
+        <v>2.020744439745298e-05</v>
       </c>
     </row>
     <row r="8">
@@ -7091,37 +7091,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0002425838907683801</v>
+        <v>5.164387378103595e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>0.000385917665535603</v>
+        <v>7.682011319377177e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0004166025103104211</v>
+        <v>8.276132143260672e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0003466304089131157</v>
+        <v>6.990555641570354e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0002468026225312916</v>
+        <v>5.233586610770586e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0003861777876861182</v>
+        <v>7.693297758183159e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0003864794704274195</v>
+        <v>7.71807332233877e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0003858875907694857</v>
+        <v>7.68147976912692e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0003869385596825215</v>
+        <v>7.761656157766254e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0002398257809472492</v>
+        <v>5.108433795510594e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0005363374303836243</v>
+        <v>0.0001034031128986905</v>
       </c>
     </row>
     <row r="9">
@@ -7131,37 +7131,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0001393690469902346</v>
+        <v>3.347806137451578e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0001730084430804207</v>
+        <v>3.934809024467661e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0001739388083494687</v>
+        <v>4.005251011890143e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0002122147406314563</v>
+        <v>4.624839892632038e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0001730084357631331</v>
+        <v>3.934808930688558e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0001732986128809546</v>
+        <v>3.946624301914016e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0001736002956222546</v>
+        <v>3.971399866069607e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0001730084159643222</v>
+        <v>3.934806312857778e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0001740311556288125</v>
+        <v>4.014485866725408e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0001535688164394378</v>
+        <v>3.576254937415248e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0001734150757995641</v>
+        <v>3.952877883800546e-05</v>
       </c>
     </row>
   </sheetData>
@@ -7247,22 +7247,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.34482716963939e-05</v>
+        <v>1.344827169639389e-05</v>
       </c>
       <c r="C2" t="n">
         <v>1.373334878354747e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.36370870116901e-05</v>
+        <v>1.363708701169009e-05</v>
       </c>
       <c r="E2" t="n">
         <v>1.382248741106427e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.356965151196105e-05</v>
+        <v>1.356965151196104e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.342443633012007e-05</v>
+        <v>1.342443633012005e-05</v>
       </c>
       <c r="H2" t="n">
         <v>1.347876953753448e-05</v>
@@ -7271,13 +7271,13 @@
         <v>1.33776361839803e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.431334964412498e-05</v>
+        <v>1.431334964412499e-05</v>
       </c>
       <c r="K2" t="n">
         <v>1.373569066007345e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.35441815526698e-05</v>
+        <v>1.354418155266978e-05</v>
       </c>
     </row>
     <row r="3">
@@ -7287,13 +7287,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.3646627386657e-05</v>
+        <v>1.364662738665701e-05</v>
       </c>
       <c r="C3" t="n">
         <v>1.392043681204202e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.386380411222236e-05</v>
+        <v>1.386380411222237e-05</v>
       </c>
       <c r="E3" t="n">
         <v>1.40102539238234e-05</v>
@@ -7305,19 +7305,19 @@
         <v>1.361921177796084e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.36820057662084e-05</v>
+        <v>1.368200576620841e-05</v>
       </c>
       <c r="I3" t="n">
         <v>1.356257275542399e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.454058548343323e-05</v>
+        <v>1.454058548343327e-05</v>
       </c>
       <c r="K3" t="n">
         <v>1.391674706413761e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.375719855690829e-05</v>
+        <v>1.375719855690828e-05</v>
       </c>
     </row>
     <row r="4">
@@ -7327,37 +7327,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.750839029834912e-05</v>
+        <v>1.171165935613764e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.673806558013377e-05</v>
+        <v>1.154155010869267e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.762063300250912e-05</v>
+        <v>1.182390206029763e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.678582530662235e-05</v>
+        <v>1.154995607673577e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.678582530662234e-05</v>
+        <v>1.154995607673577e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.742906063979603e-05</v>
+        <v>1.168602198532047e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.752715538883941e-05</v>
+        <v>1.17304244466279e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.719394320809015e-05</v>
+        <v>1.162177305124716e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.762268595553285e-05</v>
+        <v>1.182595501332135e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.743992689527494e-05</v>
+        <v>1.164319595306342e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.756670054605595e-05</v>
+        <v>1.176996960384444e-05</v>
       </c>
     </row>
     <row r="5">
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0002046474938277548</v>
+        <v>4.464814139884329e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0002199649452498585</v>
+        <v>4.730948073675188e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0002277170860350337</v>
+        <v>4.880087759365841e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>0.000219964945560813</v>
+        <v>4.730948104770661e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>0.000219964945560813</v>
+        <v>4.730948104770661e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0002089339260799696</v>
+        <v>4.53908781201582e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0002490350428114732</v>
+        <v>5.24758124122284e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.000219964931269845</v>
+        <v>4.730946675673852e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0002076244140825072</v>
+        <v>4.526625898246915e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0001964733692162716</v>
+        <v>4.315308163081926e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0002212715984964647</v>
+        <v>4.762203144884836e-05</v>
       </c>
     </row>
     <row r="6">
@@ -7407,37 +7407,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.498556960712155e-05</v>
+        <v>1.302764290735079e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>2.464952100062077e-05</v>
+        <v>1.293396625515342e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>2.514812240428154e-05</v>
+        <v>1.31487401878308e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>2.443970985919911e-05</v>
+        <v>1.289703975068998e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>2.468091911096359e-05</v>
+        <v>1.293949257877048e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>4.259413925259527e-05</v>
+        <v>1.611507579717387e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>4.277452055273194e-05</v>
+        <v>1.617396069139522e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>2.46711225168626e-05</v>
+        <v>1.605082686310056e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>4.285781455003898e-05</v>
+        <v>1.626733762188834e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>2.49382505176201e-05</v>
+        <v>1.296290090344523e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>2.505894506080779e-05</v>
+        <v>1.308860463129561e-05</v>
       </c>
     </row>
     <row r="7">
@@ -7447,37 +7447,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.589086108437279e-05</v>
+        <v>2.022697416833668e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>6.557642797412727e-05</v>
+        <v>2.013710184345963e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>6.600293179059725e-05</v>
+        <v>2.033918660086017e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>6.557697851281563e-05</v>
+        <v>2.013719899449492e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>6.557697851281571e-05</v>
+        <v>2.013719899449492e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>6.581153142581972e-05</v>
+        <v>2.020133679751952e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>6.590962617486312e-05</v>
+        <v>2.024573925882693e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>6.557641399411382e-05</v>
+        <v>2.013708786344622e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>6.600515674155656e-05</v>
+        <v>2.034126982552039e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>6.582239768129861e-05</v>
+        <v>2.015851076526247e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>6.59491713320796e-05</v>
+        <v>2.028528441604349e-05</v>
       </c>
     </row>
     <row r="8">
@@ -7487,37 +7487,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0002576792685154419</v>
+        <v>5.398173369330115e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0004110949817789379</v>
+        <v>8.094836698361424e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0004433612229801584</v>
+        <v>8.675424549034607e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0003690563330035857</v>
+        <v>7.354956509545002e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>0.000262237293366427</v>
+        <v>5.474941422118057e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0004112991234359347</v>
+        <v>8.10071526618171e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0004113972181849735</v>
+        <v>8.105155512312366e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0004110640060042289</v>
+        <v>8.094290372774386e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0004115229550733294</v>
+        <v>8.115240200240098e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0002547557638473389</v>
+        <v>5.341078303030469e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0005719884137774187</v>
+        <v>0.0001093481906038266</v>
       </c>
     </row>
     <row r="9">
@@ -7527,37 +7527,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0001612036937742521</v>
+        <v>3.700203263085803e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0002011065662741415</v>
+        <v>4.39904060550105e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0002015332433451222</v>
+        <v>4.419252130520483e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0002475164759632814</v>
+        <v>5.215855037226589e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0002011065588353433</v>
+        <v>4.399040500200879e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0002013416697258337</v>
+        <v>4.405464100907042e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0002014397644748772</v>
+        <v>4.409904347037785e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0002011065522941279</v>
+        <v>4.399039207499709e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0002015352950415707</v>
+        <v>4.419457403707129e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0001771050774597213</v>
+        <v>3.991065168442678e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0002014793096320937</v>
+        <v>4.413858862759438e-05</v>
       </c>
     </row>
   </sheetData>
@@ -7643,37 +7643,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.379920439478744e-05</v>
+        <v>1.379920439478742e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.406772622942727e-05</v>
+        <v>1.406772622942725e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.365782413966649e-05</v>
+        <v>1.365782413966651e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.416207228696949e-05</v>
+        <v>1.416207228696948e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.389385606385883e-05</v>
+        <v>1.389385606385882e-05</v>
       </c>
       <c r="G2" t="n">
         <v>1.373349332995569e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.39620546917954e-05</v>
+        <v>1.396205469179539e-05</v>
       </c>
       <c r="I2" t="n">
         <v>1.369309164787696e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.459977880121054e-05</v>
+        <v>1.459977880121053e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.410034403841108e-05</v>
+        <v>1.410034403841106e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.376108492704232e-05</v>
+        <v>1.37610849270423e-05</v>
       </c>
     </row>
     <row r="3">
@@ -7683,37 +7683,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.405039590836151e-05</v>
+        <v>1.405039590836149e-05</v>
       </c>
       <c r="C3" t="n">
         <v>1.430231634325706e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.388777932814081e-05</v>
+        <v>1.38877793281408e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.439734688413735e-05</v>
+        <v>1.439734688413733e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.412913066102671e-05</v>
+        <v>1.412913066102667e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.397481457179894e-05</v>
+        <v>1.397481457179896e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.423801375425714e-05</v>
+        <v>1.423801375425713e-05</v>
       </c>
       <c r="I3" t="n">
         <v>1.392558607357594e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.486416072524318e-05</v>
+        <v>1.486416072524319e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.433257672924198e-05</v>
+        <v>1.433257672924197e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.400681051397515e-05</v>
+        <v>1.400681051397514e-05</v>
       </c>
     </row>
     <row r="4">
@@ -7723,37 +7723,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.790845937803662e-05</v>
+        <v>1.195264506510808e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.71437194879331e-05</v>
+        <v>1.176614468035831e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.782441480715676e-05</v>
+        <v>1.18686004942283e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.719760888701276e-05</v>
+        <v>1.177562951273444e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.719760888701277e-05</v>
+        <v>1.177562951273446e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.780423718712913e-05</v>
+        <v>1.190211450602068e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.800586744300678e-05</v>
+        <v>1.205005313007829e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.757301920688573e-05</v>
+        <v>1.184169031559323e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.796066155433172e-05</v>
+        <v>1.200484724140322e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.783342821730839e-05</v>
+        <v>1.18776139043799e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.788713321502589e-05</v>
+        <v>1.193131890209734e-05</v>
       </c>
     </row>
     <row r="5">
@@ -7763,37 +7763,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0002046453079864807</v>
+        <v>4.481833024210804e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>0.000225857694464217</v>
+        <v>4.849980407713917e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0002282596921688026</v>
+        <v>4.890520910919114e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0002258576948260973</v>
+        <v>4.849980443901975e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0002258576948260973</v>
+        <v>4.849980443901975e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0002201475200734938</v>
+        <v>4.751453210105138e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0002653268695698021</v>
+        <v>5.557854926853043e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0002258576809752712</v>
+        <v>4.849979058819341e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0002067101422084879</v>
+        <v>4.522475565652922e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0002123774368181357</v>
+        <v>4.611735923259378e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>0.000223811911534156</v>
+        <v>5.118231006957147e-05</v>
       </c>
     </row>
     <row r="6">
@@ -7803,37 +7803,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.494883810498286e-05</v>
+        <v>1.613017561371934e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>2.45890707028262e-05</v>
+        <v>1.307652648707908e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>2.487824911124211e-05</v>
+        <v>1.311007532502002e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>2.439025937795846e-05</v>
+        <v>1.304153599228153e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>2.462340969926533e-05</v>
+        <v>1.308257044860916e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>4.154020634194535e-05</v>
+        <v>1.314122115524897e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>4.19078844069506e-05</v>
+        <v>1.625680809293765e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>4.130898836170189e-05</v>
+        <v>1.601922086420447e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>4.17549189834494e-05</v>
+        <v>1.332416552491939e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>2.489380015487161e-05</v>
+        <v>1.312023935865772e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>2.493974557453686e-05</v>
+        <v>1.317257867064539e-05</v>
       </c>
     </row>
     <row r="7">
@@ -7843,37 +7843,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.310446729667733e-05</v>
+        <v>1.990714241568658e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>6.276904061447219e-05</v>
+        <v>1.979620115511747e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>6.302024762851119e-05</v>
+        <v>1.982306702768455e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>6.277143690358158e-05</v>
+        <v>1.979662320018802e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>6.27714369035816e-05</v>
+        <v>1.979662320018802e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>6.300024510576987e-05</v>
+        <v>1.985661185659916e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>6.320187536164745e-05</v>
+        <v>2.000455048065678e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>6.276902712552639e-05</v>
+        <v>1.97961876661717e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>6.315666947297248e-05</v>
+        <v>1.995934459198172e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>6.302943613594916e-05</v>
+        <v>1.98321112549584e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>6.308314113366661e-05</v>
+        <v>1.988581625267584e-05</v>
       </c>
     </row>
     <row r="8">
@@ -7883,37 +7883,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0002420022434000949</v>
+        <v>5.139315083927786e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>0.000385152263700963</v>
+        <v>7.653564811091772e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0004151191915660705</v>
+        <v>8.179248082490728e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0003459153979488841</v>
+        <v>6.962996007413417e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0002462156439739479</v>
+        <v>5.208280346962644e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0003853527428842801</v>
+        <v>7.659065115819755e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0003855543731401542</v>
+        <v>7.673858978225465e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.000385121524904036</v>
+        <v>7.653022696777018e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0003855373602404193</v>
+        <v>7.669834585960603e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0002392624671324001</v>
+        <v>5.084912454226485e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0005352860912142425</v>
+        <v>0.0001029935350165292</v>
       </c>
     </row>
     <row r="9">
@@ -7923,37 +7923,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0001446236935583036</v>
+        <v>3.425452615999e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>0.000179796911145093</v>
+        <v>4.039310625690025e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0001800482945844226</v>
+        <v>4.042000318031827e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0002207731259788539</v>
+        <v>4.760492032675378e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0001797969040588621</v>
+        <v>4.039310530791314e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0001800281156363908</v>
+        <v>4.045351695838184e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0001802297458922683</v>
+        <v>4.060145558243956e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0001797968976561472</v>
+        <v>4.039309276795447e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0001801845400035934</v>
+        <v>4.055624969376449e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0001594834592824581</v>
+        <v>3.255975337148082e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0001801110116642875</v>
+        <v>4.04827213544586e-05</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Ammonia/ammonia resource use mineral and metals results.xlsx
+++ b/Results/Ammonia/ammonia resource use mineral and metals results.xlsx
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.329252649979929e-05</v>
+        <v>1.339185046789549e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.371768811308124e-05</v>
+        <v>1.368617434489113e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.353100692054944e-05</v>
+        <v>1.340440121877934e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.380569625680878e-05</v>
+        <v>1.376282308511024e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.355634005912612e-05</v>
+        <v>1.355526323846732e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.337598622686165e-05</v>
+        <v>1.339624278756645e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.344917506746001e-05</v>
+        <v>1.339721711264679e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.336447207614045e-05</v>
+        <v>1.339564444194992e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.422611800095054e-05</v>
+        <v>1.395894591533589e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.373114888253613e-05</v>
+        <v>1.372682910720864e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.346800452354242e-05</v>
+        <v>1.339741112047875e-05</v>
       </c>
     </row>
     <row r="3">
@@ -555,37 +555,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.346680070644163e-05</v>
+        <v>1.342385095165073e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.39020980291443e-05</v>
+        <v>1.393565492487959e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.374110259137438e-05</v>
+        <v>1.351078816011193e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.399079895546341e-05</v>
+        <v>1.40587892178542e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.374144275778076e-05</v>
+        <v>1.371617587927313e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.356279668119346e-05</v>
+        <v>1.345354829289506e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.364728672906521e-05</v>
+        <v>1.348268508097658e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.354673758804861e-05</v>
+        <v>1.345271814185358e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.444084554399041e-05</v>
+        <v>1.443599108047507e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.391122478793918e-05</v>
+        <v>1.398557255740188e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.366889403291735e-05</v>
+        <v>1.349089554249179e-05</v>
       </c>
     </row>
     <row r="4">
@@ -595,37 +595,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.16148965585841e-05</v>
+        <v>1.161489655858471e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.152187350868458e-05</v>
+        <v>1.152187350868455e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.175666306344806e-05</v>
+        <v>1.175666306344815e-05</v>
       </c>
       <c r="E4" t="n">
+        <v>1.153121529190447e-05</v>
+      </c>
+      <c r="F4" t="n">
         <v>1.153121529190448e-05</v>
       </c>
-      <c r="F4" t="n">
-        <v>1.15312152919045e-05</v>
-      </c>
       <c r="G4" t="n">
-        <v>1.165304881725227e-05</v>
+        <v>1.165304881725249e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.170864708766317e-05</v>
+        <v>1.170864708766316e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.160983064447441e-05</v>
+        <v>1.160983064447437e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.177499409346276e-05</v>
+        <v>1.177499409346278e-05</v>
       </c>
       <c r="K4" t="n">
         <v>1.163785727709452e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.172050944431564e-05</v>
+        <v>1.172050944431561e-05</v>
       </c>
     </row>
     <row r="5">
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.445022439951566e-05</v>
+        <v>4.44502243995218e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.632884822960057e-05</v>
+        <v>4.632884822960042e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>4.573712728865901e-05</v>
+        <v>4.573712728866047e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>4.632884856018775e-05</v>
+        <v>4.632884856018761e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.632884856018775e-05</v>
+        <v>4.632884856018761e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>4.445667788304267e-05</v>
+        <v>4.445667788304146e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>4.784242355815632e-05</v>
+        <v>4.784242355815499e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>4.632883919781238e-05</v>
+        <v>4.632883919781209e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>4.665410729196063e-05</v>
+        <v>4.665410729196225e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>4.350143166793474e-05</v>
+        <v>4.350143166793674e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>4.271148217296366e-05</v>
+        <v>4.901526557079489e-05</v>
       </c>
     </row>
     <row r="6">
@@ -675,37 +675,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.301706189975968e-05</v>
+        <v>1.301706189976003e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.300842147381975e-05</v>
+        <v>1.30084214738197e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.316614330322266e-05</v>
+        <v>1.31661353628444e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.296935699022543e-05</v>
+        <v>1.296935699022542e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.301394121601594e-05</v>
+        <v>1.301394121601593e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.63695135506535e-05</v>
+        <v>1.636951355065355e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.644092666518665e-05</v>
+        <v>1.644092666518658e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.301199598564976e-05</v>
+        <v>1.632629537787551e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.326764424760599e-05</v>
+        <v>1.650633894518229e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.304515483422008e-05</v>
+        <v>1.304515483422016e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.312541726139145e-05</v>
+        <v>1.312541726139144e-05</v>
       </c>
     </row>
     <row r="7">
@@ -715,37 +715,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.071568662234864e-05</v>
+        <v>2.071568662234861e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>2.071062974002672e-05</v>
+        <v>2.071062974002671e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.085742513856563e-05</v>
+        <v>2.085742513856571e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.07104930044855e-05</v>
+        <v>2.071049300448548e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.07104930044855e-05</v>
+        <v>2.071049300448547e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.075383888101634e-05</v>
+        <v>2.075383888101637e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.080943715142713e-05</v>
+        <v>2.080943715142712e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.071062070823835e-05</v>
+        <v>2.071062070823832e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.087578415722678e-05</v>
+        <v>2.087578415722673e-05</v>
       </c>
       <c r="K7" t="n">
         <v>2.073864734085844e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>2.08212995080796e-05</v>
+        <v>2.082129950807957e-05</v>
       </c>
     </row>
     <row r="8">
@@ -755,37 +755,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.677766225488537e-05</v>
+        <v>5.677766225488535e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>8.567937886376179e-05</v>
+        <v>8.567937886377816e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>9.181346572745059e-05</v>
+        <v>9.18134657274505e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>7.777456962783338e-05</v>
+        <v>7.777456962783331e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>5.768866364651722e-05</v>
+        <v>5.768866364651716e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>8.571700198496228e-05</v>
+        <v>8.571700198496209e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>8.577260025537299e-05</v>
+        <v>8.577260025537276e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>8.567378381218407e-05</v>
+        <v>8.567378381218412e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>8.584462717790048e-05</v>
+        <v>8.584462717790038e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>5.626376857781196e-05</v>
+        <v>5.626376857781195e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001159741696087407</v>
+        <v>0.0001159741696087403</v>
       </c>
     </row>
     <row r="9">
@@ -795,37 +795,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.063781717012213e-05</v>
+        <v>4.063781717012183e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>4.874854862276985e-05</v>
+        <v>4.874854862276973e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.889537223620793e-05</v>
+        <v>4.889537223620778e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>5.811399500583105e-05</v>
+        <v>5.811399500583087e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>4.874854750687965e-05</v>
+        <v>4.874854750687964e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.879175776375935e-05</v>
+        <v>4.879175776375942e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>4.884735603417025e-05</v>
+        <v>4.884735603417015e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.874853959098144e-05</v>
+        <v>4.87485395909814e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.891370303996984e-05</v>
+        <v>4.891370303996976e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>4.407424668432012e-05</v>
+        <v>3.855733998814117e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>4.885921839082269e-05</v>
+        <v>4.885921839082263e-05</v>
       </c>
     </row>
   </sheetData>
@@ -911,37 +911,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.389487204336212e-05</v>
+        <v>1.351703907055126e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.436707621656936e-05</v>
+        <v>1.384057497197967e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.448687121383923e-05</v>
+        <v>1.354819481108842e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.446501040344698e-05</v>
+        <v>1.39259350358632e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.418662533366283e-05</v>
+        <v>1.36942131489897e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.397301806635477e-05</v>
+        <v>1.352115174053088e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.44084696486576e-05</v>
+        <v>1.35412118577926e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.397900608055077e-05</v>
+        <v>1.352147529570017e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.541940750325309e-05</v>
+        <v>1.417587299838811e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.424274342672267e-05</v>
+        <v>1.387654575871276e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.435974011682809e-05</v>
+        <v>1.35379128379324e-05</v>
       </c>
     </row>
     <row r="3">
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.415991912972288e-05</v>
+        <v>1.37004422883095e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.464408583290508e-05</v>
+        <v>1.426827121885225e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.484084080803027e-05</v>
+        <v>1.392787584919753e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.474271904940284e-05</v>
+        <v>1.440548868075552e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.446433397961867e-05</v>
+        <v>1.402299101157877e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.424980324406431e-05</v>
+        <v>1.373317132802562e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.475095183718401e-05</v>
+        <v>1.390071295569764e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.425400845575944e-05</v>
+        <v>1.373789139018377e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.580199075107854e-05</v>
+        <v>1.501229186020417e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.449431570669283e-05</v>
+        <v>1.42731136106727e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.469485687244131e-05</v>
+        <v>1.387854171649923e-05</v>
       </c>
     </row>
     <row r="4">
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.203405956094863e-05</v>
+        <v>1.20340595609487e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.196115784665596e-05</v>
+        <v>1.196115784665599e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.23859779826645e-05</v>
+        <v>1.238597798266455e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.197138387048227e-05</v>
+        <v>1.197138387048235e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.197138387048228e-05</v>
+        <v>1.197138387048231e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.206905619317883e-05</v>
+        <v>1.20690561931789e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.233992693764263e-05</v>
+        <v>1.233992693764269e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.203628563081935e-05</v>
+        <v>1.203628563081943e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.249921896149259e-05</v>
+        <v>1.249921896149265e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.198073186345553e-05</v>
+        <v>1.198073186345557e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.231166723874445e-05</v>
+        <v>1.23116672387445e-05</v>
       </c>
     </row>
     <row r="5">
@@ -1031,37 +1031,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.640973379417216e-05</v>
+        <v>4.64097337941722e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>5.024736910475703e-05</v>
+        <v>5.02473691047571e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.526319821901181e-05</v>
+        <v>5.52631982190119e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>5.024736946729483e-05</v>
+        <v>5.02473694672949e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>5.024736946729483e-05</v>
+        <v>5.02473694672949e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>4.896979436222e-05</v>
+        <v>4.896979436222046e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>5.695718416964068e-05</v>
+        <v>5.695718416964081e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>5.024736162303862e-05</v>
+        <v>5.02473616230387e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>5.380197261433254e-05</v>
+        <v>5.380197261433267e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>4.813112484478879e-05</v>
+        <v>4.813112484478881e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.46341682324381e-05</v>
+        <v>5.463416823243825e-05</v>
       </c>
     </row>
     <row r="6">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.624313945331948e-05</v>
+        <v>1.328607649050101e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.328526092940916e-05</v>
+        <v>1.328526092940919e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.663912980021292e-05</v>
+        <v>1.663912980021294e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.324939203996402e-05</v>
+        <v>1.324939203996406e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.329089507185345e-05</v>
+        <v>1.329089507185348e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.332107312273121e-05</v>
+        <v>1.627813608554972e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.658658453632418e-05</v>
+        <v>1.658658453632423e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.328830256037172e-05</v>
+        <v>1.328830256037175e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.671917407471768e-05</v>
+        <v>1.383470879267309e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.323476468503912e-05</v>
+        <v>1.323476468503915e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.356751906994661e-05</v>
+        <v>1.356751906994662e-05</v>
       </c>
     </row>
     <row r="7">
@@ -1111,37 +1111,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.000219170353653e-05</v>
+        <v>2.000219170353658e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>2.000442525512563e-05</v>
+        <v>2.000442525512566e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.035407859815213e-05</v>
+        <v>2.035407859815215e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.000518253399123e-05</v>
+        <v>2.000518253399125e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.000518253399123e-05</v>
+        <v>2.000518253399125e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.003718833576677e-05</v>
+        <v>2.003718833576678e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.030805908023054e-05</v>
+        <v>2.030805908023058e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.000441777340728e-05</v>
+        <v>2.000441777340732e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.046735110408049e-05</v>
+        <v>2.046735110408054e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>1.994886400604343e-05</v>
+        <v>1.994886400604347e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>2.027979938133238e-05</v>
+        <v>2.02797993813324e-05</v>
       </c>
     </row>
     <row r="8">
@@ -1151,37 +1151,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.150429511358883e-05</v>
+        <v>5.1504295113589e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>7.678343226997067e-05</v>
+        <v>7.678343226999997e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>8.236752449645227e-05</v>
+        <v>8.236752449645242e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>6.987138070769766e-05</v>
+        <v>6.987138070769784e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>5.230805641749257e-05</v>
+        <v>5.230805641749265e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>7.681046111217368e-05</v>
+        <v>7.681046111217385e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>7.708133185663724e-05</v>
+        <v>7.708133185663731e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>7.67776905498142e-05</v>
+        <v>7.677769054981431e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>7.72455903938598e-05</v>
+        <v>7.724559039385995e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>5.098154247050941e-05</v>
+        <v>5.098154247050947e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001034509217058612</v>
+        <v>0.0001034509217058613</v>
       </c>
     </row>
     <row r="9">
@@ -1194,34 +1194,34 @@
         <v>3.331946840687406e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>3.92919619479248e-05</v>
+        <v>3.929196194792479e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>3.964164704719983e-05</v>
+        <v>3.964164704719988e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>4.618151426014206e-05</v>
+        <v>4.618151426014217e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>3.929196095418859e-05</v>
+        <v>3.929196095418863e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>3.932472502856592e-05</v>
+        <v>3.932472502856584e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>3.95955957730297e-05</v>
+        <v>3.959559577302972e-05</v>
       </c>
       <c r="I9" t="n">
         <v>3.929195446620642e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>3.975488779687968e-05</v>
+        <v>3.975488779687971e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>3.577720871030659e-05</v>
+        <v>3.577720871030666e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>3.95673360741315e-05</v>
+        <v>3.956733607413149e-05</v>
       </c>
     </row>
   </sheetData>
@@ -1307,37 +1307,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.39019950629332e-05</v>
+        <v>1.391776340519942e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.378408020208251e-05</v>
+        <v>1.376818043494141e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.448788447940699e-05</v>
+        <v>1.394859760151833e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.428378336778173e-05</v>
+        <v>1.393884706270342e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.428378336778173e-05</v>
+        <v>1.393884402550683e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.419297438692633e-05</v>
+        <v>1.393307706908986e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.479664383700305e-05</v>
+        <v>1.396213401442926e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.428244284243147e-05</v>
+        <v>1.393779364311155e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.399347443624517e-05</v>
+        <v>1.402087967974375e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.417328841185569e-05</v>
+        <v>1.402909940256885e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.408295155578974e-05</v>
+        <v>1.392335343845929e-05</v>
       </c>
     </row>
     <row r="3">
@@ -1347,37 +1347,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.414006889956239e-05</v>
+        <v>1.403152526847521e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.403074274247411e-05</v>
+        <v>1.384645776265103e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.481396309513422e-05</v>
+        <v>1.429039386175278e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.457902609068582e-05</v>
+        <v>1.42155603233209e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.457902609068582e-05</v>
+        <v>1.421555728612452e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.447475539833989e-05</v>
+        <v>1.418035745066161e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.516937105762703e-05</v>
+        <v>1.441039336747602e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.45746613096579e-05</v>
+        <v>1.421386347049967e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.422635253441042e-05</v>
+        <v>1.423279164024785e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.443341540467153e-05</v>
+        <v>1.429700128693477e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.434849513929769e-05</v>
+        <v>1.414140586242129e-05</v>
       </c>
     </row>
     <row r="4">
@@ -1387,37 +1387,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.191331561778153e-05</v>
+        <v>1.191331561778155e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.176400091926854e-05</v>
+        <v>1.176400091926855e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.226160204963465e-05</v>
+        <v>1.226160204963469e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.200574108810605e-05</v>
+        <v>1.200574108810618e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.200574108810606e-05</v>
+        <v>1.200574108810619e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.207463822591212e-05</v>
+        <v>1.207463822591219e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.244567901533524e-05</v>
+        <v>1.244567901533531e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.209055656274144e-05</v>
+        <v>1.209055656274147e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.189275303891944e-05</v>
+        <v>1.18927530389195e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.200059286747264e-05</v>
+        <v>1.200059286747269e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.202227763204326e-05</v>
+        <v>1.202227763204331e-05</v>
       </c>
     </row>
     <row r="5">
@@ -1427,37 +1427,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.020308292730352e-05</v>
+        <v>2.020308292730354e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.291962766568817e-05</v>
+        <v>4.29196276656882e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>4.791755301991493e-05</v>
+        <v>4.791755301991499e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>4.591281052953481e-05</v>
+        <v>4.591281052953465e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.591281052953481e-05</v>
+        <v>4.591281052953465e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>4.504389198725351e-05</v>
+        <v>4.504389198725525e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>5.487373262774658e-05</v>
+        <v>5.48737326277465e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>4.591281209619697e-05</v>
+        <v>4.591281209619625e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>4.227518877808852e-05</v>
+        <v>4.227518877808848e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>4.333204187726749e-05</v>
+        <v>4.333204187726746e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>4.690117673071697e-05</v>
+        <v>4.690117673071695e-05</v>
       </c>
     </row>
     <row r="6">
@@ -1467,34 +1467,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.318286429626231e-05</v>
+        <v>1.634820184296554e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.315291256075284e-05</v>
+        <v>1.315291256075285e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.353896727841026e-05</v>
+        <v>1.353896307394473e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.331893571459901e-05</v>
+        <v>1.331893571459898e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.336273142618842e-05</v>
+        <v>1.336273142618843e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.650952445109612e-05</v>
+        <v>1.334418690439289e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.709223762658684e-05</v>
+        <v>1.709223762658689e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.652544278792543e-05</v>
+        <v>1.336010524122223e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.638179218253068e-05</v>
+        <v>1.638179218253072e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.327203724141108e-05</v>
+        <v>1.327203724141109e-05</v>
       </c>
       <c r="L6" t="n">
         <v>1.329423146030174e-05</v>
@@ -1507,37 +1507,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.04233848044418e-05</v>
+        <v>2.042338480444183e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>2.040938234040247e-05</v>
+        <v>2.040938234040248e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.077166617987049e-05</v>
+        <v>2.077166617987054e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.06006653622068e-05</v>
+        <v>2.060066536220677e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.06006653622068e-05</v>
+        <v>2.060066536220677e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.058470741257242e-05</v>
+        <v>2.058470741257249e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.095574820199552e-05</v>
+        <v>2.095574820199554e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.060062574940174e-05</v>
+        <v>2.060062574940171e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.040282222557971e-05</v>
+        <v>2.040282222557975e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>2.051066205413291e-05</v>
+        <v>2.051066205413293e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>2.053234681870354e-05</v>
+        <v>2.053234681870355e-05</v>
       </c>
     </row>
     <row r="8">
@@ -1547,37 +1547,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.380320141105254e-05</v>
+        <v>5.380320141105266e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>8.065288754079335e-05</v>
+        <v>8.065288754079338e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>8.657909919668602e-05</v>
+        <v>8.65790991966861e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>7.349804280671188e-05</v>
+        <v>7.349804280671197e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>5.483183678871395e-05</v>
+        <v>5.483183678871397e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>8.082288024354553e-05</v>
+        <v>8.082288024354554e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>8.119392103297849e-05</v>
+        <v>8.119392103297846e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>8.083879858037483e-05</v>
+        <v>8.083879858037484e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>8.064627349791416e-05</v>
+        <v>8.064627349791415e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>5.339157090436785e-05</v>
+        <v>5.3391570904368e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001088263185897381</v>
+        <v>0.0001088263185897384</v>
       </c>
     </row>
     <row r="9">
@@ -1587,37 +1587,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.702874083957794e-05</v>
+        <v>3.702874083957803e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>4.406587089434935e-05</v>
+        <v>4.406587089434934e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.442816013082356e-05</v>
+        <v>4.442816013082364e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>5.239396878781251e-05</v>
+        <v>5.239396878781258e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>4.425711139644785e-05</v>
+        <v>4.425711139644788e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.42411959665193e-05</v>
+        <v>4.424119596651929e-05</v>
       </c>
       <c r="H9" t="n">
         <v>4.461223675594239e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.425711430334861e-05</v>
+        <v>4.425711430334873e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.405931077952662e-05</v>
+        <v>4.405931077952667e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>4.008169687799339e-05</v>
+        <v>4.008169687799341e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>4.41888353726504e-05</v>
+        <v>4.418883537265051e-05</v>
       </c>
     </row>
   </sheetData>
@@ -1703,37 +1703,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.411519007645428e-05</v>
+        <v>1.393830117240029e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.4122273187558e-05</v>
+        <v>1.38212815649132e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.475824966794972e-05</v>
+        <v>1.397214412148148e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.463119710964469e-05</v>
+        <v>1.399909543878514e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.463119710964469e-05</v>
+        <v>1.399909285071932e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.446147812701139e-05</v>
+        <v>1.395652562471763e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.510878269183652e-05</v>
+        <v>1.398782189119695e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.458799186304415e-05</v>
+        <v>1.396319237245327e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.409363055653835e-05</v>
+        <v>1.407971849872587e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.443098942609685e-05</v>
+        <v>1.407689731050637e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.432456676619064e-05</v>
+        <v>1.394529877118527e-05</v>
       </c>
     </row>
     <row r="3">
@@ -1743,37 +1743,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.438886793268561e-05</v>
+        <v>1.41037330519754e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.44181856226569e-05</v>
+        <v>1.399893599928512e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.512851967229846e-05</v>
+        <v>1.43839078547058e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.497591766598386e-05</v>
+        <v>1.437984167911394e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.497591766598386e-05</v>
+        <v>1.437983909104812e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.478717092417986e-05</v>
+        <v>1.427332260090168e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.553195941430183e-05</v>
+        <v>1.452027241624995e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.492981932594075e-05</v>
+        <v>1.432062658449858e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.433660921942664e-05</v>
+        <v>1.431925217803194e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.472860544968236e-05</v>
+        <v>1.441771570820412e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.462999473561982e-05</v>
+        <v>1.422476422120535e-05</v>
       </c>
     </row>
     <row r="4">
@@ -1783,37 +1783,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.209774308928702e-05</v>
+        <v>1.209774308928707e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.199960083449855e-05</v>
+        <v>1.199960083449857e-05</v>
       </c>
       <c r="D4" t="n">
         <v>1.248001476768476e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.225100979485816e-05</v>
+        <v>1.225100979485817e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.225100979485816e-05</v>
+        <v>1.225100979485818e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.229192660752504e-05</v>
+        <v>1.229192660752509e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.268892184735201e-05</v>
+        <v>1.268892184735205e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.232981077209129e-05</v>
+        <v>1.232981077209135e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.197624840888666e-05</v>
+        <v>1.19762484088867e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.219248043171698e-05</v>
+        <v>1.219248043171701e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2223626058477e-05</v>
+        <v>1.222362605847705e-05</v>
       </c>
     </row>
     <row r="5">
@@ -1823,37 +1823,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.202920506076157e-05</v>
+        <v>2.202920506076161e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.448575614608451e-05</v>
+        <v>4.448575614608462e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>4.881243292882324e-05</v>
+        <v>4.881243292882322e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>4.728994880038028e-05</v>
+        <v>4.728994880038032e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.728994880038028e-05</v>
+        <v>4.728994880038032e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>4.613900969873739e-05</v>
+        <v>4.613900969873981e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>5.622990819964935e-05</v>
+        <v>5.622990819964938e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>4.728995450056438e-05</v>
+        <v>4.728995450056442e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>4.1177149488692e-05</v>
+        <v>4.117714948869203e-05</v>
       </c>
       <c r="K5" t="n">
         <v>4.401353592524347e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>4.790682102663151e-05</v>
+        <v>4.790682102663155e-05</v>
       </c>
     </row>
     <row r="6">
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.63546196979476e-05</v>
+        <v>1.635461969794761e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.334432491091045e-05</v>
+        <v>1.334432491091047e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.683465062796114e-05</v>
+        <v>1.683465062796117e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.351308551137308e-05</v>
+        <v>1.351308551137309e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.355665794338864e-05</v>
+        <v>1.355665794338865e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.351575007535863e-05</v>
+        <v>1.654880321618557e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.72324050450095e-05</v>
+        <v>1.723240504500956e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.355363423992489e-05</v>
+        <v>1.355363423992491e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.328190990667067e-05</v>
+        <v>1.32819099066707e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.341664958962803e-05</v>
+        <v>1.341664958962801e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.344965602872231e-05</v>
+        <v>1.344965602872236e-05</v>
       </c>
     </row>
     <row r="7">
@@ -1903,37 +1903,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.016931433572515e-05</v>
+        <v>2.016931433572519e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>2.020953865362534e-05</v>
+        <v>2.020953865362538e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.055158369988907e-05</v>
+        <v>2.05515836998891e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.040242606977058e-05</v>
+        <v>2.040242606977063e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.040242606977058e-05</v>
+        <v>2.040242606977063e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.036349785396318e-05</v>
+        <v>2.036349785396327e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.076049309379017e-05</v>
+        <v>2.076049309379019e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.040138201852944e-05</v>
+        <v>2.040138201852948e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.004781965532479e-05</v>
+        <v>2.004781965532485e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>2.026405167815513e-05</v>
+        <v>2.026405167815515e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>2.029519730491514e-05</v>
+        <v>2.029519730491516e-05</v>
       </c>
     </row>
     <row r="8">
@@ -1943,34 +1943,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.18400429136139e-05</v>
+        <v>5.184004291361394e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>7.737470043614014e-05</v>
+        <v>7.737470043608735e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>8.29959106817661e-05</v>
+        <v>8.299591068176619e-05</v>
       </c>
       <c r="E8" t="n">
         <v>7.059504634410778e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>5.288067569573438e-05</v>
+        <v>5.288067569573443e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>7.752263496945025e-05</v>
+        <v>7.75226349694503e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>7.791963020930645e-05</v>
+        <v>7.791963020930659e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>7.756051913401646e-05</v>
+        <v>7.756051913401649e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>7.721196597783578e-05</v>
+        <v>7.721196597783588e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>5.146131998129563e-05</v>
+        <v>5.146131998129573e-05</v>
       </c>
       <c r="L8" t="n">
         <v>0.0001040791084482037</v>
@@ -1983,37 +1983,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.460385835486879e-05</v>
+        <v>3.460385835486891e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>4.097124843448995e-05</v>
+        <v>4.097124843448996e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.131329617596485e-05</v>
+        <v>4.131329617596492e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>4.84644999731281e-05</v>
+        <v>4.846449997312817e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>4.116308481767675e-05</v>
+        <v>4.11630848176768e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.112520763482774e-05</v>
+        <v>4.112520763482786e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>4.152220287465475e-05</v>
+        <v>4.152220287465482e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.116309179939398e-05</v>
+        <v>4.116309179939415e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.080952943618933e-05</v>
+        <v>4.080952943618942e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>3.735977692821825e-05</v>
+        <v>3.735977692821827e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>4.105690708577975e-05</v>
+        <v>4.105690708577991e-05</v>
       </c>
     </row>
   </sheetData>
@@ -2099,37 +2099,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.421720822955447e-05</v>
+        <v>1.394775228289149e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.434433581216319e-05</v>
+        <v>1.387112406745809e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.490698862794845e-05</v>
+        <v>1.398405405524472e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.478701431336637e-05</v>
+        <v>1.404265898821278e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.478701431336637e-05</v>
+        <v>1.404265681438251e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.461435777322214e-05</v>
+        <v>1.396865347457209e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.520350492208706e-05</v>
+        <v>1.399679654693295e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.470371137067666e-05</v>
+        <v>1.397336451737154e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.427271510189192e-05</v>
+        <v>1.416112259147008e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.456004395335669e-05</v>
+        <v>1.410261951152301e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.456550347289002e-05</v>
+        <v>1.39620759914168e-05</v>
       </c>
     </row>
     <row r="3">
@@ -2139,37 +2139,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.451369927870756e-05</v>
+        <v>1.412812193770061e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.467442776009315e-05</v>
+        <v>1.411209682820425e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.530708962443971e-05</v>
+        <v>1.44257501552625e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.515660598801707e-05</v>
+        <v>1.4464439212395e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.515660598801707e-05</v>
+        <v>1.446443703856481e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.497050352320554e-05</v>
+        <v>1.431680430472153e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.564840563415785e-05</v>
+        <v>1.454203198808912e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.507043613079681e-05</v>
+        <v>1.43501150329426e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.453700337296206e-05</v>
+        <v>1.445956650112834e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.488167390823754e-05</v>
+        <v>1.447121529685241e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.491461305909641e-05</v>
+        <v>1.430188438612257e-05</v>
       </c>
     </row>
     <row r="4">
@@ -2179,37 +2179,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.226784721462289e-05</v>
+        <v>1.22678472146229e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.2202426277094e-05</v>
+        <v>1.220242627709397e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.267789243299327e-05</v>
+        <v>1.267789243299323e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.242932633132194e-05</v>
+        <v>1.242932633132193e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.242932633132194e-05</v>
+        <v>1.242932633132195e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.24922247413707e-05</v>
+        <v>1.249222474137079e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.28547107311497e-05</v>
+        <v>1.285471073114969e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.250782471130138e-05</v>
+        <v>1.250782471130137e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.214040196915692e-05</v>
+        <v>1.214040196915688e-05</v>
       </c>
       <c r="K4" t="n">
         <v>1.236733658174845e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.247630859362921e-05</v>
+        <v>1.247630859362918e-05</v>
       </c>
     </row>
     <row r="5">
@@ -2219,13 +2219,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.322195273793231e-05</v>
+        <v>2.322195273793228e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.646516718545661e-05</v>
+        <v>4.646516718545658e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.044699942283862e-05</v>
+        <v>5.044699942283843e-05</v>
       </c>
       <c r="E5" t="n">
         <v>4.86024199522504e-05</v>
@@ -2234,22 +2234,22 @@
         <v>4.86024199522504e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>4.786066600863558e-05</v>
+        <v>4.786066600863638e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>5.744567639429369e-05</v>
+        <v>5.744567639429383e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>4.860241966638274e-05</v>
+        <v>4.86024196663828e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>4.228752730827174e-05</v>
+        <v>4.22875273082717e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>4.526139477391314e-05</v>
+        <v>4.526139477391305e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.08392531681069e-05</v>
+        <v>5.083925316810693e-05</v>
       </c>
     </row>
     <row r="6">
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.349927338417739e-05</v>
+        <v>1.349927338417737e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.356437321951137e-05</v>
+        <v>1.356437321951135e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.39154013804826e-05</v>
+        <v>1.391540461684299e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.369564378601461e-05</v>
+        <v>1.369564378601456e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.374241281233659e-05</v>
+        <v>1.374241281233658e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.680552107676654e-05</v>
+        <v>1.680552107676658e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.753894821666785e-05</v>
+        <v>1.753894821666787e-05</v>
       </c>
       <c r="I6" t="n">
         <v>1.682112104669719e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.652994606523834e-05</v>
+        <v>1.65299460652383e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.359778643224981e-05</v>
+        <v>1.359778643224977e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.371019902058357e-05</v>
+        <v>1.371019902058353e-05</v>
       </c>
     </row>
     <row r="7">
@@ -2299,37 +2299,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.038229116633167e-05</v>
+        <v>2.038229116633165e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>2.046766192745735e-05</v>
+        <v>2.046766192745737e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.079233482166569e-05</v>
+        <v>2.079233482166567e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.062410856243377e-05</v>
+        <v>2.062410856243376e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.062410856243377e-05</v>
+        <v>2.062410856243376e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.060666869307953e-05</v>
+        <v>2.060666869307952e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.096915468285848e-05</v>
+        <v>2.096915468285851e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.062226866301016e-05</v>
+        <v>2.062226866301013e-05</v>
       </c>
       <c r="J7" t="n">
         <v>2.025484592086569e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>2.048178053345723e-05</v>
+        <v>2.04817805334572e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>2.059075254533798e-05</v>
+        <v>2.059075254533797e-05</v>
       </c>
     </row>
     <row r="8">
@@ -2339,34 +2339,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.21211741350286e-05</v>
+        <v>5.212117413502861e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>7.778958147523929e-05</v>
+        <v>7.778958147531179e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>8.341085735678952e-05</v>
+        <v>8.341085735678949e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>7.094859248875239e-05</v>
+        <v>7.094859248875223e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>5.317297752998699e-05</v>
+        <v>5.317297752998703e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>7.792179002626677e-05</v>
+        <v>7.792179002626671e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>7.828427601609095e-05</v>
+        <v>7.828427601609089e-05</v>
       </c>
       <c r="I8" t="n">
         <v>7.793738999619744e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>7.757499372201948e-05</v>
+        <v>7.757499372201941e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>5.174557174326681e-05</v>
+        <v>5.174557174326675e-05</v>
       </c>
       <c r="L8" t="n">
         <v>0.0001046223935046775</v>
@@ -2379,37 +2379,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.375005360819524e-05</v>
+        <v>3.375005360819522e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>3.988694600335269e-05</v>
+        <v>3.988694600335265e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.021162091012703e-05</v>
+        <v>4.021162091012696e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>4.702487948860907e-05</v>
+        <v>4.702487948860906e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>4.004155174860126e-05</v>
+        <v>4.004155174860125e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.002595276897478e-05</v>
+        <v>4.002595276897485e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>4.038843875875376e-05</v>
+        <v>4.038843875875382e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.004155273890549e-05</v>
+        <v>4.004155273890543e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>3.967412999676097e-05</v>
+        <v>3.9674129996761e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>3.228111856280734e-05</v>
+        <v>3.625253536483394e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>4.001003662123323e-05</v>
+        <v>4.001003662123327e-05</v>
       </c>
     </row>
   </sheetData>
@@ -2495,37 +2495,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.417348561621304e-05</v>
+        <v>1.398654619207236e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.402835721459745e-05</v>
+        <v>1.382142316524827e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.49563740405279e-05</v>
+        <v>1.402774805490239e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.454972208280032e-05</v>
+        <v>1.399611617359372e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.454972208280032e-05</v>
+        <v>1.399611324245315e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.449697785918275e-05</v>
+        <v>1.400357094631251e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.499655733299225e-05</v>
+        <v>1.402700987122823e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.456277492271759e-05</v>
+        <v>1.400704176497752e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.432520218117236e-05</v>
+        <v>1.407115921886096e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.434114793849994e-05</v>
+        <v>1.408895155093241e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.437094318196072e-05</v>
+        <v>1.399293980695165e-05</v>
       </c>
     </row>
     <row r="3">
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.445237872407808e-05</v>
+        <v>1.416214622527263e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.431444392796921e-05</v>
+        <v>1.394883704791351e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.535286258688868e-05</v>
+        <v>1.449471363272607e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.488711220311717e-05</v>
+        <v>1.432962748137771e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.488711220311716e-05</v>
+        <v>1.432962455023708e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.482446181470946e-05</v>
+        <v>1.432317605853494e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.539936374763032e-05</v>
+        <v>1.451433266554292e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.489734208170139e-05</v>
+        <v>1.434770544829247e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.461212271100501e-05</v>
+        <v>1.435839904446101e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.462719783129252e-05</v>
+        <v>1.438419517205833e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.467978866201851e-05</v>
+        <v>1.427875223741401e-05</v>
       </c>
     </row>
     <row r="4">
@@ -2575,37 +2575,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.206251933723839e-05</v>
+        <v>1.206251933723842e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.190868375479126e-05</v>
+        <v>1.190868375479129e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.252791333169699e-05</v>
+        <v>1.2527913331697e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.216581375440228e-05</v>
+        <v>1.216581375440226e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.216581375440228e-05</v>
+        <v>1.216581375440226e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.224313765821198e-05</v>
+        <v>1.2243137658212e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.255235824393123e-05</v>
+        <v>1.255235824393124e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.224479833794878e-05</v>
+        <v>1.224479833794876e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.209428854548753e-05</v>
+        <v>1.209428854548755e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.209084292501979e-05</v>
+        <v>1.209084292501982e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.218130554821837e-05</v>
+        <v>1.218130554821838e-05</v>
       </c>
     </row>
     <row r="5">
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.284608449826761e-05</v>
+        <v>2.284608449826766e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.545186984091756e-05</v>
+        <v>4.545186984091766e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.257896936307016e-05</v>
+        <v>5.257896936307022e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>4.859868667207281e-05</v>
+        <v>4.85986866720723e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.859868667207281e-05</v>
+        <v>4.85986866720723e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>4.803876193295801e-05</v>
+        <v>4.803876193295826e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>5.690542125732558e-05</v>
+        <v>5.690542125732567e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>4.859868483005164e-05</v>
+        <v>4.859868483005136e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>4.5953275419998e-05</v>
+        <v>4.595327541999807e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>4.484970550396433e-05</v>
+        <v>4.484970550396436e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.004668324617927e-05</v>
+        <v>5.004668324617929e-05</v>
       </c>
     </row>
     <row r="6">
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.335093973417995e-05</v>
+        <v>1.335093973417998e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.331506025903286e-05</v>
+        <v>1.33150602590329e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.382765513929638e-05</v>
+        <v>1.382765943508974e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.349246731526416e-05</v>
+        <v>1.349246731526411e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.35361904718329e-05</v>
+        <v>1.353619047183288e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.353155805515353e-05</v>
+        <v>1.353155805515355e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.72201205663022e-05</v>
+        <v>1.722012056630222e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.353321873489032e-05</v>
+        <v>1.670263567466098e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.660659709041164e-05</v>
+        <v>1.346842459016716e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.337846722822517e-05</v>
+        <v>1.337846722822521e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.347218873042273e-05</v>
+        <v>1.347218873042275e-05</v>
       </c>
     </row>
     <row r="7">
@@ -2698,10 +2698,10 @@
         <v>2.055781616621843e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>2.053823735066826e-05</v>
+        <v>2.053823735066828e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.102320487415372e-05</v>
+        <v>2.102320487415377e-05</v>
       </c>
       <c r="E7" t="n">
         <v>2.07417567485937e-05</v>
@@ -2710,22 +2710,22 @@
         <v>2.07417567485937e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.0738434487192e-05</v>
+        <v>2.073843448719203e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.10476550729112e-05</v>
+        <v>2.104765507291127e-05</v>
       </c>
       <c r="I7" t="n">
         <v>2.074009516692881e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.058958537446752e-05</v>
+        <v>2.058958537446758e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>2.05861397539998e-05</v>
+        <v>2.058613975399984e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>2.067660237719838e-05</v>
+        <v>2.06766023771984e-05</v>
       </c>
     </row>
     <row r="8">
@@ -2735,37 +2735,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.394216546293676e-05</v>
+        <v>5.394216546293692e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>8.077541447593201e-05</v>
+        <v>8.077541447597431e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>8.682019306598591e-05</v>
+        <v>8.682019306598624e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>7.363441720493573e-05</v>
+        <v>7.363441720493589e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>5.49764147598541e-05</v>
+        <v>5.497641475985414e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>8.09687346043911e-05</v>
+        <v>8.09687346043913e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>8.127795519011995e-05</v>
+        <v>8.127795519012022e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>8.097039528412795e-05</v>
+        <v>8.097039528412807e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>8.082516149501829e-05</v>
+        <v>8.082516149501846e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>5.347181173108801e-05</v>
+        <v>5.3471811731088e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001089497429527883</v>
+        <v>0.0001089497429527886</v>
       </c>
     </row>
     <row r="9">
@@ -2775,37 +2775,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.724477419194659e-05</v>
+        <v>3.724477419194657e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>4.429224225810977e-05</v>
+        <v>4.429224225810981e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.47772154559375e-05</v>
+        <v>4.477721545593748e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>5.264932283500882e-05</v>
+        <v>5.264932283500892e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>4.44941005661043e-05</v>
+        <v>4.449410056610419e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.449243939463357e-05</v>
+        <v>4.449243939463351e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>4.480165998035272e-05</v>
+        <v>4.480165998035281e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.449410007437034e-05</v>
+        <v>4.449410007437031e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.434359028190909e-05</v>
+        <v>4.434359028190908e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>3.544147107344358e-05</v>
+        <v>4.024547010685644e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>4.443060728463987e-05</v>
+        <v>4.443060728463997e-05</v>
       </c>
     </row>
   </sheetData>
@@ -2891,37 +2891,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.44245598700062e-05</v>
+        <v>1.404372222484132e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.441127279499325e-05</v>
+        <v>1.390065539960051e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.554033745102468e-05</v>
+        <v>1.410244338281785e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.488000557047447e-05</v>
+        <v>1.408468021429715e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.488000557047447e-05</v>
+        <v>1.408467789460108e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.491151584213681e-05</v>
+        <v>1.406934975048214e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.532759586907821e-05</v>
+        <v>1.408822720432267e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.48581800412568e-05</v>
+        <v>1.40665500718454e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.505347928678777e-05</v>
+        <v>1.419035282432942e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.466699142052899e-05</v>
+        <v>1.418010309729796e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.478388564296786e-05</v>
+        <v>1.405853973112417e-05</v>
       </c>
     </row>
     <row r="3">
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.47460265995536e-05</v>
+        <v>1.426815234598989e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.475669031250913e-05</v>
+        <v>1.412381444199876e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.602940195035438e-05</v>
+        <v>1.472536299290084e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.526662592400839e-05</v>
+        <v>1.450012023874146e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.526662592400839e-05</v>
+        <v>1.4500117919045e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.530612684013013e-05</v>
+        <v>1.449054001184814e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.578497724708488e-05</v>
+        <v>1.465079071822879e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.524195738321571e-05</v>
+        <v>1.447024410554433e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.544754376626704e-05</v>
+        <v>1.469107336929213e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.500105888111706e-05</v>
+        <v>1.455661096737136e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.515963237003836e-05</v>
+        <v>1.444634621865133e-05</v>
       </c>
     </row>
     <row r="4">
@@ -2971,37 +2971,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.226721980075722e-05</v>
+        <v>1.226721980075721e-05</v>
       </c>
       <c r="C4" t="n">
         <v>1.217813674866554e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.293050229316587e-05</v>
+        <v>1.293050229316585e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.239958734937326e-05</v>
+        <v>1.239958734937327e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.239958734937326e-05</v>
+        <v>1.239958734937327e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.254492430258221e-05</v>
+        <v>1.254492430258223e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.280462261316123e-05</v>
+        <v>1.280462261316124e-05</v>
       </c>
       <c r="I4" t="n">
         <v>1.247530612374933e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.255453159840511e-05</v>
+        <v>1.255453159840512e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.231708827037597e-05</v>
+        <v>1.231708827037593e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.248225607362427e-05</v>
+        <v>1.248225607362426e-05</v>
       </c>
     </row>
     <row r="5">
@@ -3011,13 +3011,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.472562197602541e-05</v>
+        <v>2.472562197602545e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.729194436282929e-05</v>
+        <v>4.729194436282927e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.62089051203771e-05</v>
+        <v>5.620890512037713e-05</v>
       </c>
       <c r="E5" t="n">
         <v>4.953436500815988e-05</v>
@@ -3026,22 +3026,22 @@
         <v>4.953436500815988e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>5.029461844205395e-05</v>
+        <v>5.029461844205299e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>5.814741303347332e-05</v>
+        <v>5.814741303347314e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>4.953434626522968e-05</v>
+        <v>4.95343462652299e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>5.122487057771273e-05</v>
+        <v>5.122487057771269e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>4.587808691178119e-05</v>
+        <v>4.587808691178112e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.264854615375815e-05</v>
+        <v>5.264854615375818e-05</v>
       </c>
     </row>
     <row r="6">
@@ -3051,37 +3051,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.351327402539053e-05</v>
+        <v>1.351327402539055e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.354156649853339e-05</v>
+        <v>1.354156649853338e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.418954123372253e-05</v>
+        <v>1.731836400305665e-05</v>
       </c>
       <c r="E6" t="n">
         <v>1.367833485085477e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.372427081252048e-05</v>
+        <v>1.37242708125205e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.683284208514973e-05</v>
+        <v>1.379097852721551e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.73899517954398e-05</v>
+        <v>1.738995179543982e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.676322390631684e-05</v>
+        <v>1.676322390631686e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.388490519195659e-05</v>
+        <v>1.690727290236138e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.355904754527537e-05</v>
+        <v>1.355904754527538e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.373098858022761e-05</v>
+        <v>1.37309885802276e-05</v>
       </c>
     </row>
     <row r="7">
@@ -3091,34 +3091,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.032634187723668e-05</v>
+        <v>2.032634187723669e-05</v>
       </c>
       <c r="C7" t="n">
         <v>2.037322784061248e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.098962127593066e-05</v>
+        <v>2.098962127593065e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.053663564789258e-05</v>
+        <v>2.053663564789262e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.053663564789258e-05</v>
+        <v>2.053663564789262e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.060404637906165e-05</v>
+        <v>2.06040463790617e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.086374468964069e-05</v>
+        <v>2.086374468964068e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.053442820022878e-05</v>
+        <v>2.05344282002288e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.061365367488457e-05</v>
+        <v>2.061365367488461e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>2.037621034685542e-05</v>
+        <v>2.03762103468554e-05</v>
       </c>
       <c r="L7" t="n">
         <v>2.054137815010372e-05</v>
@@ -3131,34 +3131,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.200838342841308e-05</v>
+        <v>5.200838342841306e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>7.754533471047076e-05</v>
+        <v>7.754533471041656e-05</v>
       </c>
       <c r="D8" t="n">
         <v>8.343867370396451e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>7.073643878113913e-05</v>
+        <v>7.07364387811389e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>5.302556622754594e-05</v>
+        <v>5.302556622754587e-05</v>
       </c>
       <c r="G8" t="n">
         <v>7.776903966487113e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>7.802873797548211e-05</v>
+        <v>7.802873797548203e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>7.769942148603825e-05</v>
+        <v>7.769942148603835e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>7.778365509528851e-05</v>
+        <v>7.778365509528852e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>5.158489298620253e-05</v>
+        <v>5.158489298620245e-05</v>
       </c>
       <c r="L8" t="n">
         <v>0.0001043254453767196</v>
@@ -3171,37 +3171,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.485316130727042e-05</v>
+        <v>3.485316130727044e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>4.124722842609634e-05</v>
+        <v>4.12472284260963e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.186362542261554e-05</v>
+        <v>4.186362542261559e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>4.873295880498149e-05</v>
+        <v>4.87329588049815e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>4.140844623450939e-05</v>
+        <v>4.140844623450948e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.14780469645455e-05</v>
+        <v>4.147804696454557e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>4.173774527512456e-05</v>
+        <v>4.173774527512454e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.140842878571259e-05</v>
+        <v>4.140842878571269e-05</v>
       </c>
       <c r="J9" t="n">
         <v>4.148765426036841e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>3.325797676863652e-05</v>
+        <v>3.757262944019003e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>4.141537873558757e-05</v>
+        <v>4.141537873558752e-05</v>
       </c>
     </row>
   </sheetData>
@@ -3287,37 +3287,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.452987754265208e-05</v>
+        <v>1.41080874132815e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.468726805347332e-05</v>
+        <v>1.401668272987898e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.560327975303827e-05</v>
+        <v>1.416457843966561e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.499870929775514e-05</v>
+        <v>1.419791972628827e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.499870929775515e-05</v>
+        <v>1.419791905960949e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.505133098547998e-05</v>
+        <v>1.413553047228757e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.539594071908108e-05</v>
+        <v>1.415051116844051e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.491509038485222e-05</v>
+        <v>1.412836997302023e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.572882718118042e-05</v>
+        <v>1.440841303870639e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.479846179953042e-05</v>
+        <v>1.42847910072011e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.496312749338736e-05</v>
+        <v>1.412675810662197e-05</v>
       </c>
     </row>
     <row r="3">
@@ -3327,37 +3327,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.48927960098411e-05</v>
+        <v>1.431597310275427e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.509143392109759e-05</v>
+        <v>1.42904515747993e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.612743090638322e-05</v>
+        <v>1.475725850979835e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.541951681030434e-05</v>
+        <v>1.46146420511314e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.541951681030434e-05</v>
+        <v>1.461464138445263e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.549257548784848e-05</v>
+        <v>1.455131535149585e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.588927520604914e-05</v>
+        <v>1.468471064667325e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.533340035840303e-05</v>
+        <v>1.449990208288113e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.622613767426639e-05</v>
+        <v>1.511149937629058e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.517040680726021e-05</v>
+        <v>1.466410266439559e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.539143418343506e-05</v>
+        <v>1.452226038467364e-05</v>
       </c>
     </row>
     <row r="4">
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.249486095563656e-05</v>
+        <v>1.249486095563659e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.246515278826019e-05</v>
+        <v>1.246515278826021e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.313295308580122e-05</v>
+        <v>1.313295308580126e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.260504762787375e-05</v>
+        <v>1.260504762787378e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.260504762787375e-05</v>
+        <v>1.260504762787378e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.279301148032916e-05</v>
+        <v>1.279301148032968e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.301031359042513e-05</v>
+        <v>1.301031359042515e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.267384402711497e-05</v>
+        <v>1.267384402711465e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.302672887972973e-05</v>
+        <v>1.302672887972985e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.253058426099732e-05</v>
+        <v>1.253058426099737e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.275385273650337e-05</v>
+        <v>1.275385273650343e-05</v>
       </c>
     </row>
     <row r="5">
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.573438992365201e-05</v>
+        <v>2.573438992365215e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.949985552181975e-05</v>
+        <v>4.949985552181978e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.676764200400726e-05</v>
+        <v>5.676764200400728e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>5.0035884096775e-05</v>
+        <v>5.003588409677516e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>5.0035884096775e-05</v>
+        <v>5.003588409677516e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>5.166449155487786e-05</v>
+        <v>5.166449155487821e-05</v>
       </c>
       <c r="H5" t="n">
         <v>5.882307813272316e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>5.00358537448938e-05</v>
+        <v>5.003585374489399e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>5.662071606693103e-05</v>
+        <v>5.662071606693105e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>4.662704337566335e-05</v>
+        <v>4.662704337566347e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.462042674247706e-05</v>
+        <v>5.462042674247719e-05</v>
       </c>
     </row>
     <row r="6">
@@ -3447,37 +3447,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.690031583922181e-05</v>
+        <v>1.690031583922191e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.387001615652139e-05</v>
+        <v>1.387001615652144e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.442090526838217e-05</v>
+        <v>1.442090526838223e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.390227640358038e-05</v>
+        <v>1.390227640358041e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.395664658465223e-05</v>
+        <v>1.395664658465227e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.719846636391392e-05</v>
+        <v>1.719846636391398e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.781739512343617e-05</v>
+        <v>1.429490609096801e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.395340123199071e-05</v>
+        <v>1.707929891070003e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.751618526074829e-05</v>
+        <v>1.439779855578526e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.380482554424129e-05</v>
+        <v>1.380482554424126e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.403644142447997e-05</v>
+        <v>1.403644142448e-05</v>
       </c>
     </row>
     <row r="7">
@@ -3487,37 +3487,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.061362949889831e-05</v>
+        <v>2.061362949889839e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>2.072912399796025e-05</v>
+        <v>2.072912399796026e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.125171790305987e-05</v>
+        <v>2.125171790305995e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.07978091118171e-05</v>
+        <v>2.079780911181715e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.07978091118171e-05</v>
+        <v>2.079780911181715e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.091178002359044e-05</v>
+        <v>2.091178002359053e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.112908213368688e-05</v>
+        <v>2.112908213368692e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.079261257037653e-05</v>
+        <v>2.079261257037654e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.114549742299148e-05</v>
+        <v>2.114549742299155e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>2.064935280425906e-05</v>
+        <v>2.064935280425914e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>2.087262127976512e-05</v>
+        <v>2.087262127976513e-05</v>
       </c>
     </row>
     <row r="8">
@@ -3530,31 +3530,31 @@
         <v>5.239411463969785e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>7.814210495344705e-05</v>
+        <v>7.814210495352661e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>8.396770400756092e-05</v>
+        <v>8.39677040075608e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>7.119703456828869e-05</v>
+        <v>7.11970345682887e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>5.338840598246293e-05</v>
+        <v>5.338840598246289e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>7.831476926206473e-05</v>
+        <v>7.831476926206484e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>7.853207137220989e-05</v>
+        <v>7.853207137220997e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>7.819560180885087e-05</v>
+        <v>7.819560180885082e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>7.855352222144308e-05</v>
+        <v>7.855352222144316e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>5.195388677647841e-05</v>
+        <v>5.195388677647857e-05</v>
       </c>
       <c r="L8" t="n">
         <v>0.0001050404585708853</v>
@@ -3567,37 +3567,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.406408575422949e-05</v>
+        <v>3.406408575422951e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>4.026260320895448e-05</v>
+        <v>4.026260320895454e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.078520139487626e-05</v>
+        <v>4.078520139487634e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>4.734580052582589e-05</v>
+        <v>4.734580052582591e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>4.032612083814558e-05</v>
+        <v>4.032612083814564e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.044525923458469e-05</v>
+        <v>4.044525923458482e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>4.06625613446811e-05</v>
+        <v>4.066256134468128e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.032609178137076e-05</v>
+        <v>4.032609178137082e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.067897663398573e-05</v>
+        <v>4.067897663398577e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>3.651531031680718e-05</v>
+        <v>3.665830485822178e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>4.040610049075934e-05</v>
+        <v>4.040610049075945e-05</v>
       </c>
     </row>
   </sheetData>
@@ -3683,37 +3683,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.427190659205823e-05</v>
+        <v>1.403147758799296e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.41929720149453e-05</v>
+        <v>1.389393735809818e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.531872766789762e-05</v>
+        <v>1.408656970206036e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.466738641885149e-05</v>
+        <v>1.403238753865743e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.466738641885153e-05</v>
+        <v>1.403238472605402e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.467817363059847e-05</v>
+        <v>1.405285861532008e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.510947253136186e-05</v>
+        <v>1.40726183897753e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.469285213158278e-05</v>
+        <v>1.405363878953685e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.461743437590688e-05</v>
+        <v>1.411109352264016e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.447174863982069e-05</v>
+        <v>1.414056619718997e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.446086878235902e-05</v>
+        <v>1.40373256109756e-05</v>
       </c>
     </row>
     <row r="3">
@@ -3723,37 +3723,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.45650039889506e-05</v>
+        <v>1.422420420710207e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.449853865323121e-05</v>
+        <v>1.406664240749473e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.57690650744984e-05</v>
+        <v>1.465565784136075e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.502373474747758e-05</v>
+        <v>1.438648230028262e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.502373474747714e-05</v>
+        <v>1.438647948767923e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.503229524123528e-05</v>
+        <v>1.441630468877186e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.552866573813952e-05</v>
+        <v>1.458191740694923e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.504637751086007e-05</v>
+        <v>1.442160497706048e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.495059853018751e-05</v>
+        <v>1.447386580976694e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.477587524593698e-05</v>
+        <v>1.44646754401165e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.478264875783618e-05</v>
+        <v>1.433768337915171e-05</v>
       </c>
     </row>
     <row r="4">
@@ -3763,13 +3763,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.211105199057113e-05</v>
+        <v>1.211105199057131e-05</v>
       </c>
       <c r="C4" t="n">
         <v>1.197737531434634e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.273334276258578e-05</v>
+        <v>1.2733342762586e-05</v>
       </c>
       <c r="E4" t="n">
         <v>1.223351462974717e-05</v>
@@ -3778,22 +3778,22 @@
         <v>1.223351462974717e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.234084226181059e-05</v>
+        <v>1.234084226181072e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.260952360578285e-05</v>
+        <v>1.260952360578294e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.231191624473659e-05</v>
+        <v>1.23119162447366e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.226961960598504e-05</v>
+        <v>1.226961960598521e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.215470102833976e-05</v>
+        <v>1.215470102833994e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.222481580853988e-05</v>
+        <v>1.222481580853996e-05</v>
       </c>
     </row>
     <row r="5">
@@ -3803,37 +3803,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.36384253318356e-05</v>
+        <v>2.363842533183564e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.662612076748188e-05</v>
+        <v>4.662612076748181e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.615595939135825e-05</v>
+        <v>5.615595939135834e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>4.971583395316515e-05</v>
+        <v>4.971583395316511e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.971583395316515e-05</v>
+        <v>4.971583395316512e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>4.97360500374333e-05</v>
+        <v>4.973605003743406e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>5.794564382530817e-05</v>
+        <v>5.794564382530863e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>4.971582497593308e-05</v>
+        <v>4.971582497593312e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>4.914433164163321e-05</v>
+        <v>4.914433164163337e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>4.589812974166634e-05</v>
+        <v>4.589812974166662e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.082623213957908e-05</v>
+        <v>5.082623213957948e-05</v>
       </c>
     </row>
     <row r="6">
@@ -3843,37 +3843,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.34101774489872e-05</v>
+        <v>1.34101774489875e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.339453624983246e-05</v>
+        <v>1.339453624983245e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.404786476999945e-05</v>
+        <v>1.404786476999956e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.356942606075025e-05</v>
+        <v>1.356942606075026e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.361410265070109e-05</v>
+        <v>1.36141026507011e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.681324392622261e-05</v>
+        <v>1.36399677202269e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.729229771510229e-05</v>
+        <v>1.729229771510228e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.678431790914851e-05</v>
+        <v>1.361104170315283e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.679701900527281e-05</v>
+        <v>1.36555686441194e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.345239116991411e-05</v>
+        <v>1.345239116991431e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.35263617559047e-05</v>
+        <v>1.352636175590472e-05</v>
       </c>
     </row>
     <row r="7">
@@ -3883,37 +3883,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.060128060316728e-05</v>
+        <v>2.060128060316742e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>2.060257369408768e-05</v>
+        <v>2.060257369408766e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.1223566221683e-05</v>
+        <v>2.122356622168287e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.080405213394796e-05</v>
+        <v>2.080405213394794e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.080405213394796e-05</v>
+        <v>2.080405213394794e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.083107087440676e-05</v>
+        <v>2.083107087440691e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.109975221837888e-05</v>
+        <v>2.109975221837907e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.080214485733275e-05</v>
+        <v>2.080214485733272e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.075984821858133e-05</v>
+        <v>2.075984821858147e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>2.064492964093598e-05</v>
+        <v>2.064492964093608e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>2.071504442113608e-05</v>
+        <v>2.071504442113622e-05</v>
       </c>
     </row>
     <row r="8">
@@ -3923,34 +3923,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.3988021685699e-05</v>
+        <v>5.398802168569892e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>8.083888410006001e-05</v>
+        <v>8.08388841000177e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>8.70187377804962e-05</v>
+        <v>8.701873778049636e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>7.369653673042597e-05</v>
+        <v>7.369653673042582e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>5.504089511825664e-05</v>
+        <v>5.504089511825654e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>8.106027724041586e-05</v>
+        <v>8.106027724041578e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>8.13289585843976e-05</v>
+        <v>8.132895858439753e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>8.103135122334181e-05</v>
+        <v>8.103135122334171e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>8.099432990292243e-05</v>
+        <v>8.099432990292281e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>5.353305814947792e-05</v>
+        <v>5.353305814947783e-05</v>
       </c>
       <c r="L8" t="n">
         <v>0.0001089834503106694</v>
@@ -3963,37 +3963,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.733200472206776e-05</v>
+        <v>3.733200472206803e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>4.441026984135151e-05</v>
+        <v>4.441026984135149e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.503126794598011e-05</v>
+        <v>4.503126794598029e-05</v>
       </c>
       <c r="E9" t="n">
         <v>5.277652433821626e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>4.460984862889947e-05</v>
+        <v>4.46098486288994e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.463876702167064e-05</v>
+        <v>4.463876702167073e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>4.490744836564287e-05</v>
+        <v>4.490744836564291e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.460984100459661e-05</v>
+        <v>4.460984100459658e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.456754436584512e-05</v>
+        <v>4.456754436584527e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>4.035220057968868e-05</v>
+        <v>4.035220057968887e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>4.452274056839988e-05</v>
+        <v>4.452274056840003e-05</v>
       </c>
     </row>
   </sheetData>
@@ -4079,37 +4079,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.451257910616707e-05</v>
+        <v>1.416856107440696e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.456879290335823e-05</v>
+        <v>1.406869447577936e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.559341285129163e-05</v>
+        <v>1.422544320770412e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.495366552668907e-05</v>
+        <v>1.422189077627245e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.495366552668906e-05</v>
+        <v>1.422188832545958e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.500492435282435e-05</v>
+        <v>1.419447222686213e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.541393101762937e-05</v>
+        <v>1.421296498870213e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.491501082192564e-05</v>
+        <v>1.418974724666206e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.547045707323179e-05</v>
+        <v>1.429662118013509e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.482429526504726e-05</v>
+        <v>1.437532560426451e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.488062955012512e-05</v>
+        <v>1.418383303637869e-05</v>
       </c>
     </row>
     <row r="3">
@@ -4119,37 +4119,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.485772431139302e-05</v>
+        <v>1.434480708210294e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.494071040250114e-05</v>
+        <v>1.427719922661558e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.610090701232209e-05</v>
+        <v>1.478889355260657e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.53592788041152e-05</v>
+        <v>1.45881900475637e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.53592788041152e-05</v>
+        <v>1.458818759675079e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.542402333405952e-05</v>
+        <v>1.456921597381888e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.589473081540811e-05</v>
+        <v>1.472688138409739e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.531794814162134e-05</v>
+        <v>1.453518273214042e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.59445243385928e-05</v>
+        <v>1.484543162088313e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.517959215464439e-05</v>
+        <v>1.474472761682136e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.528136622026054e-05</v>
+        <v>1.452639376861433e-05</v>
       </c>
     </row>
     <row r="4">
@@ -4159,13 +4159,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.228661843398266e-05</v>
+        <v>1.228661843398269e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.220907581277984e-05</v>
+        <v>1.220907581277982e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.292912829664843e-05</v>
+        <v>1.292912829664845e-05</v>
       </c>
       <c r="E4" t="n">
         <v>1.240447740856417e-05</v>
@@ -4174,22 +4174,22 @@
         <v>1.240447740856417e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.25674377009366e-05</v>
+        <v>1.256743770093656e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.282302135581574e-05</v>
+        <v>1.282302135581588e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.247556185050788e-05</v>
+        <v>1.247556185050785e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.279683850125376e-05</v>
+        <v>1.27968385012538e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.232679459217739e-05</v>
+        <v>1.232679459217736e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.250684196150014e-05</v>
+        <v>1.250684196150021e-05</v>
       </c>
     </row>
     <row r="5">
@@ -4199,37 +4199,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.518875779697166e-05</v>
+        <v>2.518875779697165e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.79480722547904e-05</v>
+        <v>4.794807225479044e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.630517876134291e-05</v>
+        <v>5.630517876134283e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>4.966924860359425e-05</v>
+        <v>4.966924860359429e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.966924860359425e-05</v>
+        <v>4.966924860359429e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>5.08127562707106e-05</v>
+        <v>5.081275627070956e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>5.86344545368582e-05</v>
+        <v>5.863445453685823e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>4.966922428810616e-05</v>
+        <v>4.966922428810622e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>5.56759939355077e-05</v>
+        <v>5.567599393550783e-05</v>
       </c>
       <c r="K5" t="n">
         <v>4.616383665676966e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.326562379996517e-05</v>
+        <v>5.326562379996521e-05</v>
       </c>
     </row>
     <row r="6">
@@ -4239,34 +4239,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.353950685042668e-05</v>
+        <v>1.65784798041415e-05</v>
       </c>
       <c r="C6" t="n">
         <v>1.357916199251001e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.419471277399605e-05</v>
+        <v>1.419470898620477e-05</v>
       </c>
       <c r="E6" t="n">
         <v>1.368531589721021e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.373151152750252e-05</v>
+        <v>1.37315115275025e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.382032611738057e-05</v>
+        <v>1.382032611738053e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.741217685956665e-05</v>
+        <v>1.74121768595667e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.676742322066667e-05</v>
+        <v>1.676742322066665e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.715281011640187e-05</v>
+        <v>1.413540398486312e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.357594067863784e-05</v>
+        <v>1.35759406786378e-05</v>
       </c>
       <c r="L6" t="n">
         <v>1.37625636431202e-05</v>
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.03402229426108e-05</v>
+        <v>2.034022294261082e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>2.039826139749734e-05</v>
+        <v>2.039826139749736e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.098273020018545e-05</v>
+        <v>2.098273020018544e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.053277087016694e-05</v>
+        <v>2.053277087016693e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.053277087016694e-05</v>
+        <v>2.053277087016693e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.062104220956471e-05</v>
+        <v>2.062104220956467e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.0876625864444e-05</v>
+        <v>2.087662586444397e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.052916635913597e-05</v>
+        <v>2.052916635913599e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.085044300988192e-05</v>
+        <v>2.085044300988193e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>2.038039910080548e-05</v>
+        <v>2.038039910080547e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>2.056044647012832e-05</v>
+        <v>2.056044647012833e-05</v>
       </c>
     </row>
     <row r="8">
@@ -4319,37 +4319,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.201831294652429e-05</v>
+        <v>5.201831294652431e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>7.755814056027829e-05</v>
+        <v>7.75581405602782e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>8.341623590788119e-05</v>
+        <v>8.3416235907881e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>7.072144133955659e-05</v>
+        <v>7.072144133955651e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>5.301688380022304e-05</v>
+        <v>5.301688380022309e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>7.77724805838042e-05</v>
+        <v>7.777248058380398e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>7.802806423871589e-05</v>
+        <v>7.80280642387159e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>7.768060473337537e-05</v>
+        <v>7.768060473337542e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>7.800688763142264e-05</v>
+        <v>7.800688763142263e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>5.158530858030694e-05</v>
+        <v>5.158530858030692e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001043209272681782</v>
+        <v>0.0001043209272681781</v>
       </c>
     </row>
     <row r="9">
@@ -4359,37 +4359,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.488095435166834e-05</v>
+        <v>3.488095435166837e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>4.128693430812903e-05</v>
+        <v>4.128693430812904e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.187140618768218e-05</v>
+        <v>4.187140618768212e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>4.874325228063067e-05</v>
+        <v>4.874325228063064e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>4.141786228460647e-05</v>
+        <v>4.141786228460643e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.150971512019638e-05</v>
+        <v>4.150971512019633e-05</v>
       </c>
       <c r="H9" t="n">
         <v>4.17652987750757e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.141783926976768e-05</v>
+        <v>4.141783926976763e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.173911592051359e-05</v>
+        <v>4.173911592051358e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>3.759104997356079e-05</v>
+        <v>3.327588043513166e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>4.144911938075999e-05</v>
+        <v>4.144911938076002e-05</v>
       </c>
     </row>
   </sheetData>
@@ -4475,37 +4475,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.461421709338016e-05</v>
+        <v>1.444359624974212e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.477120630863335e-05</v>
+        <v>1.43626522166187e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.563030319101616e-05</v>
+        <v>1.449707084295116e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.499856687882802e-05</v>
+        <v>1.445296248455829e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.499856687882802e-05</v>
+        <v>1.445296100752458e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.512915825297719e-05</v>
+        <v>1.447069658021619e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.550155459389705e-05</v>
+        <v>1.448717812721466e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.501245897636674e-05</v>
+        <v>1.44645636176545e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.575561309701609e-05</v>
+        <v>1.462451770638922e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.483534096746103e-05</v>
+        <v>1.45809173379826e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.503479276021897e-05</v>
+        <v>1.446162050165742e-05</v>
       </c>
     </row>
     <row r="3">
@@ -4515,37 +4515,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.502278707698208e-05</v>
+        <v>1.44467634988624e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.521896599562411e-05</v>
+        <v>1.443449474075198e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.61914965708645e-05</v>
+        <v>1.486657041854455e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.546698043877332e-05</v>
+        <v>1.461635986304047e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.546698043877332e-05</v>
+        <v>1.461635838600678e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.561507608025852e-05</v>
+        <v>1.467965912652267e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.604369850670681e-05</v>
+        <v>1.482353714725448e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.547885728464398e-05</v>
+        <v>1.463557449381881e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.631234832931932e-05</v>
+        <v>1.507167691796232e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.525291397675624e-05</v>
+        <v>1.472984363229004e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.550685078688905e-05</v>
+        <v>1.46482513261699e-05</v>
       </c>
     </row>
     <row r="4">
@@ -4555,37 +4555,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.244562680315682e-05</v>
+        <v>1.244562680315678e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.240802210299195e-05</v>
+        <v>1.240802210299193e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.30496469329812e-05</v>
+        <v>1.304964693298115e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.257422073733719e-05</v>
+        <v>1.257422073733715e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.25742207373372e-05</v>
+        <v>1.257422073733714e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.273961597129932e-05</v>
+        <v>1.27396159712993e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.297372029418231e-05</v>
+        <v>1.297372029418227e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.263039030108178e-05</v>
+        <v>1.263039030108175e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.303200343319555e-05</v>
+        <v>1.303200343319549e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.248125704649982e-05</v>
+        <v>1.248125704649977e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.269708000448809e-05</v>
+        <v>1.269708000448805e-05</v>
       </c>
     </row>
     <row r="5">
@@ -4595,37 +4595,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.55874801328103e-05</v>
+        <v>2.558748013281025e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.920985231723963e-05</v>
+        <v>4.920985231723962e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.604399621610891e-05</v>
+        <v>5.604399621610868e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>5.002098008231377e-05</v>
+        <v>5.002098008231519e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>5.002098008231377e-05</v>
+        <v>5.002098008231519e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>5.14485365087467e-05</v>
+        <v>5.144853650874668e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>5.890489989548288e-05</v>
+        <v>5.89048998954827e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>5.002095157434162e-05</v>
+        <v>5.00209515743407e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>5.744302655353515e-05</v>
+        <v>5.744302655353513e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>4.648046140261788e-05</v>
+        <v>4.648046140261786e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.431056725379821e-05</v>
+        <v>5.431056725379807e-05</v>
       </c>
     </row>
     <row r="6">
@@ -4635,37 +4635,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.371609137207729e-05</v>
+        <v>1.681933701992488e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.380336667701243e-05</v>
+        <v>1.380336667701242e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.432827523881583e-05</v>
+        <v>1.432827857577114e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.385457991652809e-05</v>
+        <v>1.385457991652805e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.390494191208663e-05</v>
+        <v>1.390494191208662e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.711332618806744e-05</v>
+        <v>1.401008054021977e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.773655038138177e-05</v>
+        <v>1.773655038138172e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.700410051784985e-05</v>
+        <v>1.390085487000223e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.439082463992155e-05</v>
+        <v>1.748736422728016e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.374613741421277e-05</v>
+        <v>1.374613741421273e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.397163930960233e-05</v>
+        <v>1.397163930960231e-05</v>
       </c>
     </row>
     <row r="7">
@@ -4675,37 +4675,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.054559485224664e-05</v>
+        <v>2.054559485224661e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>2.065292645574264e-05</v>
+        <v>2.065292645574258e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.114961183168461e-05</v>
+        <v>2.114961183168459e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.073913384733331e-05</v>
+        <v>2.073913384733328e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.073913384733331e-05</v>
+        <v>2.073913384733328e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.083958402038916e-05</v>
+        <v>2.083958402038914e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.107368834327213e-05</v>
+        <v>2.107368834327208e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.073035835017162e-05</v>
+        <v>2.073035835017158e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.113197148228535e-05</v>
+        <v>2.113197148228533e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>2.058122509558963e-05</v>
+        <v>2.05812250955896e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>2.079704805357793e-05</v>
+        <v>2.079704805357789e-05</v>
       </c>
     </row>
     <row r="8">
@@ -4715,37 +4715,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.230531043637253e-05</v>
+        <v>5.230531043637238e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>7.800874284452293e-05</v>
+        <v>7.800874284444569e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>8.379676437330044e-05</v>
+        <v>8.379676437330025e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>7.108814076979985e-05</v>
+        <v>7.10881407697997e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>5.330625426099032e-05</v>
+        <v>5.330625426099026e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>7.81819948884363e-05</v>
+        <v>7.818199488843612e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>7.841609921136719e-05</v>
+        <v>7.84160992113671e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>7.807276921821868e-05</v>
+        <v>7.80727692182186e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>7.847941008700757e-05</v>
+        <v>7.84794100870076e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>5.186572898026104e-05</v>
+        <v>5.186572898026107e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001048627233398043</v>
+        <v>0.0001048627233398041</v>
       </c>
     </row>
     <row r="9">
@@ -4758,34 +4758,34 @@
         <v>3.400232647151434e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>4.018283353101799e-05</v>
+        <v>4.018283353101793e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.067952259414721e-05</v>
+        <v>4.067952259414712e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>4.726860850853343e-05</v>
+        <v>4.726860850853339e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>4.026029264201745e-05</v>
+        <v>4.026029264201732e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.036949109566459e-05</v>
+        <v>4.036949109566451e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>4.060359541854749e-05</v>
+        <v>4.060359541854742e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.026026542544699e-05</v>
+        <v>4.02602654254469e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.066187855756068e-05</v>
+        <v>4.066187855756061e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>3.644954763188238e-05</v>
+        <v>3.644954763188232e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>4.032695512885327e-05</v>
+        <v>4.032695512885319e-05</v>
       </c>
     </row>
   </sheetData>
@@ -4871,37 +4871,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.338507262231237e-05</v>
+        <v>1.340809496977704e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.373584570798723e-05</v>
+        <v>1.37000719688475e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.362069835953593e-05</v>
+        <v>1.342049548433669e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.382498514159109e-05</v>
+        <v>1.377773983078341e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.357204975812955e-05</v>
+        <v>1.356720089096345e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.345279571693209e-05</v>
+        <v>1.341165910173797e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.349317717035989e-05</v>
+        <v>1.341086001557462e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.338053917953709e-05</v>
+        <v>1.340786338513155e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.43232909362535e-05</v>
+        <v>1.398185748965487e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.382534598863613e-05</v>
+        <v>1.374683299684121e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.355746288061405e-05</v>
+        <v>1.341348375212394e-05</v>
       </c>
     </row>
     <row r="3">
@@ -4911,37 +4911,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.357336931954304e-05</v>
+        <v>1.346482434893004e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.392279278034666e-05</v>
+        <v>1.395526283060961e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.384438772707456e-05</v>
+        <v>1.355144970294389e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.401262086633026e-05</v>
+        <v>1.408002068435684e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.375968548286874e-05</v>
+        <v>1.373248973435774e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.365126490715252e-05</v>
+        <v>1.348913280688489e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.369802832869932e-05</v>
+        <v>1.350567101409166e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.356528644756938e-05</v>
+        <v>1.34695004821965e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.455149853173886e-05</v>
+        <v>1.448641778228256e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.401898491438672e-05</v>
+        <v>1.403199892065558e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.377191033210268e-05</v>
+        <v>1.353028462808845e-05</v>
       </c>
     </row>
     <row r="4">
@@ -4951,13 +4951,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.167259465719146e-05</v>
+        <v>1.167259465719147e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.154045326275943e-05</v>
+        <v>1.154045326275942e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.181266417366146e-05</v>
+        <v>1.181266417366145e-05</v>
       </c>
       <c r="E4" t="n">
         <v>1.154893434924221e-05</v>
@@ -4966,7 +4966,7 @@
         <v>1.154893434924221e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.170137905639766e-05</v>
+        <v>1.170137905639777e-05</v>
       </c>
       <c r="H4" t="n">
         <v>1.173749695274959e-05</v>
@@ -4975,13 +4975,13 @@
         <v>1.162195969748507e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.183054544676923e-05</v>
+        <v>1.183054544676925e-05</v>
       </c>
       <c r="K4" t="n">
         <v>1.16937369829653e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.17763737339114e-05</v>
+        <v>1.177637373391141e-05</v>
       </c>
     </row>
     <row r="5">
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.358690677495281e-05</v>
+        <v>4.358690677495288e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.70093126213336e-05</v>
+        <v>4.700931262133352e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>4.519102038475817e-05</v>
+        <v>4.519102038475808e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>4.700931296290991e-05</v>
+        <v>4.700931296290982e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.700931296290991e-05</v>
+        <v>4.700931296290982e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>4.370878002843358e-05</v>
+        <v>4.370878002843272e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>4.638181143001816e-05</v>
+        <v>4.638181143001845e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>4.700929515293757e-05</v>
+        <v>4.700929515293758e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>4.533564935585076e-05</v>
+        <v>4.53356493558505e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>4.273883322694556e-05</v>
+        <v>4.273883322694571e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>4.43404759943296e-05</v>
+        <v>4.434047599432954e-05</v>
       </c>
     </row>
     <row r="6">
@@ -5031,34 +5031,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.610288547714021e-05</v>
+        <v>1.29887540302997e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.293367885405012e-05</v>
+        <v>1.293367885405009e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.313684937564431e-05</v>
+        <v>1.313684213266226e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.289680413272749e-05</v>
+        <v>1.289680413272748e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.293974601009331e-05</v>
+        <v>1.29397460100933e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.61316698763464e-05</v>
+        <v>1.301753842950582e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.618178920262177e-05</v>
+        <v>1.618178920262179e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.605225051743382e-05</v>
+        <v>1.605225051743379e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.627303554262359e-05</v>
+        <v>1.323178165959342e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.301488732999546e-05</v>
+        <v>1.301488732999545e-05</v>
       </c>
       <c r="L6" t="n">
         <v>1.309522333114446e-05</v>
@@ -5071,34 +5071,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.018987848283669e-05</v>
+        <v>2.018987848283668e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>2.013926099152626e-05</v>
+        <v>2.013926099152625e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.032991799509247e-05</v>
+        <v>2.032991799509244e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.013905355553483e-05</v>
+        <v>2.013905355553481e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.013905355553483e-05</v>
+        <v>2.013905355553481e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.021866288204288e-05</v>
+        <v>2.021866288204292e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.025478077839479e-05</v>
+        <v>2.025478077839481e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.013924352313027e-05</v>
+        <v>2.013924352313029e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.034782927241444e-05</v>
+        <v>2.034782927241449e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>2.021102080861051e-05</v>
+        <v>2.021102080861052e-05</v>
       </c>
       <c r="L7" t="n">
         <v>2.029365755955661e-05</v>
@@ -5111,31 +5111,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.39457682284457e-05</v>
+        <v>5.394576822844576e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>8.095354381242215e-05</v>
+        <v>8.0953543812442e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>8.674873730076436e-05</v>
+        <v>8.674873730076447e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>7.355417711220086e-05</v>
+        <v>7.355417711220088e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>5.475259080307031e-05</v>
+        <v>5.475259080307028e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>8.102778766311343e-05</v>
+        <v>8.102778766311348e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>8.10639055594644e-05</v>
+        <v>8.10639055594645e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>8.094836830420087e-05</v>
+        <v>8.094836830420096e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>8.116227079424878e-05</v>
+        <v>8.116227079424877e-05</v>
       </c>
       <c r="K8" t="n">
         <v>5.346438282389771e-05</v>
@@ -5151,34 +5151,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.696891657371917e-05</v>
+        <v>3.696891657371908e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>4.3998281137528e-05</v>
+        <v>4.399828113752794e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.418896836378628e-05</v>
+        <v>4.418896836378638e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>5.216842913110637e-05</v>
+        <v>5.216842913110641e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>4.399828010531719e-05</v>
+        <v>4.399828010531713e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.407768302804462e-05</v>
+        <v>4.40776830280446e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>4.411380092439654e-05</v>
+        <v>4.411380092439664e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.399826366913204e-05</v>
+        <v>4.399826366913205e-05</v>
       </c>
       <c r="J9" t="n">
         <v>4.420684941841622e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>3.996787163853135e-05</v>
+        <v>3.996787163853142e-05</v>
       </c>
       <c r="L9" t="n">
         <v>4.415267770555838e-05</v>
@@ -5267,37 +5267,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.352572143139362e-05</v>
+        <v>1.344329406688571e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.38518695352e-05</v>
+        <v>1.374566656205533e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.369762915391365e-05</v>
+        <v>1.345234122888572e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.394601161897335e-05</v>
+        <v>1.382760979700979e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.367851458250126e-05</v>
+        <v>1.360495037647834e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.356129021371175e-05</v>
+        <v>1.344516598125385e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.363874573781546e-05</v>
+        <v>1.344629871906959e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.348143607894037e-05</v>
+        <v>1.344097057537432e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.454025157573197e-05</v>
+        <v>1.4049726529718e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.399269053006351e-05</v>
+        <v>1.379818511271987e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.365347888462681e-05</v>
+        <v>1.344629566188551e-05</v>
       </c>
     </row>
     <row r="3">
@@ -5307,37 +5307,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.373483258496709e-05</v>
+        <v>1.353051890729523e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.405366120891681e-05</v>
+        <v>1.403019417905579e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.393256207644175e-05</v>
+        <v>1.359733805098774e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.414849122765164e-05</v>
+        <v>1.416192793265961e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.388099419117952e-05</v>
+        <v>1.379438978364911e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.377574405268413e-05</v>
+        <v>1.354618486636492e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.386514555187284e-05</v>
+        <v>1.357509696844373e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.368110452219128e-05</v>
+        <v>1.352374421712999e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.479521642398421e-05</v>
+        <v>1.461944996066752e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.420831277523348e-05</v>
+        <v>1.413391179907228e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.388203552793085e-05</v>
+        <v>1.35810770844702e-05</v>
       </c>
     </row>
     <row r="4">
@@ -5347,34 +5347,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.177895207722743e-05</v>
+        <v>1.177895207722745e-05</v>
       </c>
       <c r="C4" t="n">
         <v>1.162898363555495e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.188114393391735e-05</v>
+        <v>1.188114393391759e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1638313906705e-05</v>
+        <v>1.163831390670501e-05</v>
       </c>
       <c r="F4" t="n">
         <v>1.1638313906705e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.178862132927856e-05</v>
+        <v>1.178862132927875e-05</v>
       </c>
       <c r="H4" t="n">
         <v>1.184677490694782e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.170469443895758e-05</v>
+        <v>1.170469443895761e-05</v>
       </c>
       <c r="J4" t="n">
         <v>1.196042199136879e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.180472027848716e-05</v>
+        <v>1.180472027848717e-05</v>
       </c>
       <c r="L4" t="n">
         <v>1.185621076515339e-05</v>
@@ -5387,37 +5387,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.166759885184881e-05</v>
+        <v>4.166759885184889e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.62382637312824e-05</v>
+        <v>4.623826373128247e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>4.464056828433903e-05</v>
+        <v>4.464056828434178e-05</v>
       </c>
       <c r="E5" t="n">
         <v>4.623826409012581e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.623826409012581e-05</v>
+        <v>4.623826409012583e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>4.322512566413321e-05</v>
+        <v>4.322512566413424e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>4.531520220022395e-05</v>
+        <v>4.531520220022389e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>4.623824495835158e-05</v>
+        <v>4.623824495835164e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>4.475319104033109e-05</v>
+        <v>4.47531910403311e-05</v>
       </c>
       <c r="K5" t="n">
         <v>4.474777970390278e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>4.470179056998559e-05</v>
+        <v>4.470179056998568e-05</v>
       </c>
     </row>
     <row r="6">
@@ -5427,37 +5427,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.59393524882759e-05</v>
+        <v>1.301015473760229e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.293068503627028e-05</v>
+        <v>1.293068503627033e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.311855953160225e-05</v>
+        <v>1.311855953160823e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.289613366728718e-05</v>
+        <v>1.289613366728721e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.293724609666412e-05</v>
+        <v>1.293724609666414e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.594902174032716e-05</v>
+        <v>1.301982398965367e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.603486966839061e-05</v>
+        <v>1.603486966839064e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.586509485000609e-05</v>
+        <v>1.586509485000602e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.613063223920151e-05</v>
+        <v>1.327148892635924e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.304031577768083e-05</v>
+        <v>1.304031577768085e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.308955119244873e-05</v>
+        <v>1.308955119244874e-05</v>
       </c>
     </row>
     <row r="7">
@@ -5467,13 +5467,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.972744891198327e-05</v>
+        <v>1.972744891198326e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>1.965321004664421e-05</v>
+        <v>1.965321004664426e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>1.982961010549081e-05</v>
+        <v>1.982961010549117e-05</v>
       </c>
       <c r="E7" t="n">
         <v>1.965361555148775e-05</v>
@@ -5482,22 +5482,22 @@
         <v>1.965361555148775e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>1.97371181640345e-05</v>
+        <v>1.973711816403461e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>1.979527174170366e-05</v>
+        <v>1.979527174170367e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>1.965319127371337e-05</v>
+        <v>1.965319127371339e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>1.990891882612459e-05</v>
+        <v>1.990891882612462e-05</v>
       </c>
       <c r="K7" t="n">
         <v>1.975321711324298e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>1.980470759990919e-05</v>
+        <v>1.980470759990923e-05</v>
       </c>
     </row>
     <row r="8">
@@ -5507,37 +5507,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.120797470890629e-05</v>
+        <v>5.12079747089063e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>7.637837762793316e-05</v>
+        <v>7.637837762793336e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>8.178294171492224e-05</v>
+        <v>8.178294171492247e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>6.94750924872174e-05</v>
+        <v>6.947509248721748e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>5.193404149298749e-05</v>
+        <v>5.193404149298753e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>7.645689581880137e-05</v>
+        <v>7.645689581880149e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>7.651504939646975e-05</v>
+        <v>7.651504939646982e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>7.637296892848032e-05</v>
+        <v>7.637296892848029e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>7.663365672160132e-05</v>
+        <v>7.663365672160152e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>5.076491084868659e-05</v>
+        <v>5.076491084868662e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.000102888994296293</v>
+        <v>0.0001028889942962931</v>
       </c>
     </row>
     <row r="9">
@@ -5547,37 +5547,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.403976855857834e-05</v>
+        <v>3.40397685585785e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>4.020304905669226e-05</v>
+        <v>4.020304905669242e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.037948000072962e-05</v>
+        <v>4.037948000072946e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>4.74010130881061e-05</v>
+        <v>4.740101308810624e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>4.020304812212077e-05</v>
+        <v>4.020304812212085e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.028695717408277e-05</v>
+        <v>4.02869571740827e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>4.034511075175177e-05</v>
+        <v>4.034511075175175e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.020303028376147e-05</v>
+        <v>4.020303028376148e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.045875783617265e-05</v>
+        <v>4.045875783617273e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>3.244890579389603e-05</v>
+        <v>3.668901300085284e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>4.035454660995738e-05</v>
+        <v>4.03545466099573e-05</v>
       </c>
     </row>
   </sheetData>
@@ -5663,37 +5663,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.35569778518897e-05</v>
+        <v>1.346248400221177e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.395594357092891e-05</v>
+        <v>1.377544803180634e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.377258296603342e-05</v>
+        <v>1.347383087114289e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.405267443703751e-05</v>
+        <v>1.385960722293926e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.377784065677067e-05</v>
+        <v>1.363084109382692e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.363169941099951e-05</v>
+        <v>1.346641644945872e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.370095242199375e-05</v>
+        <v>1.34670853738192e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.357675786650594e-05</v>
+        <v>1.346353266135915e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.475194609078912e-05</v>
+        <v>1.409368557654275e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.405339450786835e-05</v>
+        <v>1.382657878895346e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.374743116377127e-05</v>
+        <v>1.346878161245931e-05</v>
       </c>
     </row>
     <row r="3">
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.377124935401542e-05</v>
+        <v>1.355383247525582e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.417252268275618e-05</v>
+        <v>1.408718019852926e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.401923989774557e-05</v>
+        <v>1.363816116220566e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.426993894782347e-05</v>
+        <v>1.422253525718645e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.399510516755673e-05</v>
+        <v>1.384491675515303e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.385719462551605e-05</v>
+        <v>1.358369140022044e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.393714417973689e-05</v>
+        <v>1.361248967760656e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.379134197024909e-05</v>
+        <v>1.356877912776704e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.503623223017636e-05</v>
+        <v>1.472673826910119e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.42771258956299e-05</v>
+        <v>1.41791669534332e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.399056359947023e-05</v>
+        <v>1.362596647623892e-05</v>
       </c>
     </row>
     <row r="4">
@@ -5746,34 +5746,34 @@
         <v>1.181772667121064e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.170802940944173e-05</v>
+        <v>1.17080294094418e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.194589477560539e-05</v>
+        <v>1.19458947756054e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.171792680649399e-05</v>
+        <v>1.171792680649411e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.171792680649397e-05</v>
+        <v>1.171792680649411e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.185068401485329e-05</v>
+        <v>1.185068401485317e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.190395186587262e-05</v>
+        <v>1.190395186587263e-05</v>
       </c>
       <c r="I4" t="n">
         <v>1.178165550759422e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.209481557978152e-05</v>
+        <v>1.209481557978154e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.185516497680725e-05</v>
+        <v>1.185516497680729e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.193225463519407e-05</v>
+        <v>1.193225463519431e-05</v>
       </c>
     </row>
     <row r="5">
@@ -5783,37 +5783,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.354006972922723e-05</v>
+        <v>4.354006972922754e-05</v>
       </c>
       <c r="C5" t="n">
         <v>4.756882711606211e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>4.754066399493474e-05</v>
+        <v>4.754066399493532e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>4.756882742069441e-05</v>
+        <v>4.756882742069525e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.756882742069441e-05</v>
+        <v>4.756882742069525e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>4.524332868734911e-05</v>
+        <v>4.524332868734805e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>4.880044425505206e-05</v>
+        <v>4.880044425505231e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>4.756881172644527e-05</v>
+        <v>4.75688117264464e-05</v>
       </c>
       <c r="J5" t="n">
         <v>4.657833866451868e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>4.738674779241029e-05</v>
+        <v>4.738674779241036e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>4.743702209506444e-05</v>
+        <v>5.000695410972332e-05</v>
       </c>
     </row>
     <row r="6">
@@ -5823,37 +5823,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.305327844313791e-05</v>
+        <v>1.305327844313796e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.301257831490949e-05</v>
+        <v>1.301257831490944e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.616459391952096e-05</v>
+        <v>1.318758745163166e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.297768976629068e-05</v>
+        <v>1.297768976629063e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.301890033371044e-05</v>
+        <v>1.301890033371036e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.308623578678059e-05</v>
+        <v>1.602739839948247e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.611513863666511e-05</v>
+        <v>1.611513863666513e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.595836989222365e-05</v>
+        <v>1.301720727952155e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.341107289783028e-05</v>
+        <v>1.628111439431847e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.309450928687726e-05</v>
+        <v>1.309450928687728e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.31700247362189e-05</v>
+        <v>1.317002473621902e-05</v>
       </c>
     </row>
     <row r="7">
@@ -5863,37 +5863,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.977298462188088e-05</v>
+        <v>1.977298462188091e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>1.973692884788023e-05</v>
+        <v>1.973692884788018e-05</v>
       </c>
       <c r="D7" t="n">
         <v>1.990112112593075e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>1.973815363019518e-05</v>
+        <v>1.97381536301952e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>1.973815363019518e-05</v>
+        <v>1.973815363019521e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>1.980594196552349e-05</v>
+        <v>1.980594196552329e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>1.985920981654282e-05</v>
+        <v>1.985920981654288e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>1.973691345826451e-05</v>
+        <v>1.97369134582645e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.00500735304518e-05</v>
+        <v>2.005007353045179e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>1.981042292747751e-05</v>
+        <v>1.981042292747754e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>1.988751258586472e-05</v>
+        <v>1.988751258586454e-05</v>
       </c>
     </row>
     <row r="8">
@@ -5903,37 +5903,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.126407410771122e-05</v>
+        <v>5.126407410771133e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>7.64875198092107e-05</v>
+        <v>7.648751980921083e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>8.188200681941703e-05</v>
+        <v>8.188200681941722e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>6.958030170025264e-05</v>
+        <v>6.95803017002526e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>5.202925930763265e-05</v>
+        <v>5.20292593076326e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>7.655035492581131e-05</v>
+        <v>7.655035492581133e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>7.660362277683013e-05</v>
+        <v>7.660362277683025e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>7.648132641855226e-05</v>
+        <v>7.648132641855229e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>7.679944949689535e-05</v>
+        <v>7.679944949689546e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>5.083241896432443e-05</v>
+        <v>5.083241896432449e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001030111335679498</v>
+        <v>0.0001030111335679501</v>
       </c>
     </row>
     <row r="9">
@@ -5946,34 +5946,34 @@
         <v>3.302693726732069e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>3.893890735101726e-05</v>
+        <v>3.89389073510173e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>3.910313146936357e-05</v>
+        <v>3.910313146936366e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>4.580280198059777e-05</v>
+        <v>4.580280198059776e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>3.893890636507162e-05</v>
+        <v>3.893890636507167e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>3.900792046866068e-05</v>
+        <v>3.900792046866056e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>3.906118831967997e-05</v>
+        <v>3.906118831968e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>3.893889196140161e-05</v>
+        <v>3.893889196140166e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>3.925205203358891e-05</v>
+        <v>3.925205203358894e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>3.556609198988663e-05</v>
+        <v>3.556609198988666e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>3.90894910890016e-05</v>
+        <v>3.908949108900168e-05</v>
       </c>
     </row>
   </sheetData>
@@ -6059,37 +6059,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.364342746864133e-05</v>
+        <v>1.34389364931651e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.38350250143851e-05</v>
+        <v>1.372553760668575e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.377926446517785e-05</v>
+        <v>1.34460853244988e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.392496476805925e-05</v>
+        <v>1.38039147427897e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.366971112724588e-05</v>
+        <v>1.359144647591967e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.352334536725871e-05</v>
+        <v>1.34326168106716e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.350588487130131e-05</v>
+        <v>1.342870685752953e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.347580718410194e-05</v>
+        <v>1.343012240712042e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.444553203716767e-05</v>
+        <v>1.401107057235374e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.393072616446059e-05</v>
+        <v>1.377500720956788e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.360094044927282e-05</v>
+        <v>1.343296876909513e-05</v>
       </c>
     </row>
     <row r="3">
@@ -6099,37 +6099,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.387213405980548e-05</v>
+        <v>1.356811305023892e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.403790198945491e-05</v>
+        <v>1.400235933089991e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.402837474437155e-05</v>
+        <v>1.362918077664748e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.412851481915043e-05</v>
+        <v>1.412825984918148e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.387326117833709e-05</v>
+        <v>1.377754398372713e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.37340147682831e-05</v>
+        <v>1.352818496297806e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.371422556594948e-05</v>
+        <v>1.352987376133135e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.367656992162705e-05</v>
+        <v>1.351127637988808e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.469263803102794e-05</v>
+        <v>1.454498541330388e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.414076004411551e-05</v>
+        <v>1.408966752188393e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.382352244904636e-05</v>
+        <v>1.355517697481364e-05</v>
       </c>
     </row>
     <row r="4">
@@ -6139,37 +6139,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.183515064092603e-05</v>
+        <v>1.183515064092607e-05</v>
       </c>
       <c r="C4" t="n">
         <v>1.160843627650613e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.191589997946517e-05</v>
+        <v>1.191589997946515e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.161689604320029e-05</v>
+        <v>1.161689604320028e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.16168960432003e-05</v>
+        <v>1.161689604320028e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.175229232955653e-05</v>
+        <v>1.175229232955651e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.175404009435517e-05</v>
+        <v>1.175404009435515e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.168757269755418e-05</v>
+        <v>1.168757269755417e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.190796784902486e-05</v>
+        <v>1.190796784902485e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.176125178984976e-05</v>
+        <v>1.176125178984977e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.181120381219472e-05</v>
+        <v>1.181120381219474e-05</v>
       </c>
     </row>
     <row r="5">
@@ -6179,37 +6179,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.68413399992378e-05</v>
+        <v>4.684133999923919e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.828666953826423e-05</v>
+        <v>4.828666953826425e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.395533573030934e-05</v>
+        <v>5.395533573030958e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>4.828666981966789e-05</v>
+        <v>4.828666981966795e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.828666981966789e-05</v>
+        <v>4.828666981966798e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>4.835868262424854e-05</v>
+        <v>4.835868262424861e-05</v>
       </c>
       <c r="H5" t="n">
         <v>5.423914350157632e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>4.828665538460583e-05</v>
+        <v>4.828665538460588e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660084972751405e-05</v>
+        <v>4.660084972751486e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>4.694676904812351e-05</v>
+        <v>4.694676904812411e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>4.974907265965191e-05</v>
+        <v>4.974907265965199e-05</v>
       </c>
     </row>
     <row r="6">
@@ -6219,37 +6219,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.315641003314725e-05</v>
+        <v>1.627669836759641e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.300533189855033e-05</v>
+        <v>1.300533189855036e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.640436434340661e-05</v>
+        <v>1.64043643434065e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.296800471292776e-05</v>
+        <v>1.296800471292778e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.301091369554279e-05</v>
+        <v>1.301091369554281e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.307355172177778e-05</v>
+        <v>1.619384005622691e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.620901891583319e-05</v>
+        <v>1.307777790076878e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.300883208977544e-05</v>
+        <v>1.612912042422447e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.636130871114534e-05</v>
+        <v>1.63613087111453e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.308825639523323e-05</v>
+        <v>1.308825639523327e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.313520807720049e-05</v>
+        <v>1.31352080772005e-05</v>
       </c>
     </row>
     <row r="7">
@@ -6259,37 +6259,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.035529465341408e-05</v>
+        <v>2.035529465341406e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>2.020773086370056e-05</v>
+        <v>2.020773086370055e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.043601331277961e-05</v>
+        <v>2.04360133127796e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.020815556746069e-05</v>
+        <v>2.02081555674607e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.020815556746069e-05</v>
+        <v>2.020815556746071e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.027243634204454e-05</v>
+        <v>2.027243634204456e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.027418410684323e-05</v>
+        <v>2.027418410684318e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.020771671004221e-05</v>
+        <v>2.020771671004219e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.042811186151285e-05</v>
+        <v>2.042811186151286e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>2.028139580233775e-05</v>
+        <v>2.028139580233774e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>2.033134782468285e-05</v>
+        <v>2.033134782468278e-05</v>
       </c>
     </row>
     <row r="8">
@@ -6299,37 +6299,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.411443879226398e-05</v>
+        <v>5.41144387922641e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>8.103103824207519e-05</v>
+        <v>8.10310382420752e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>8.686432209138976e-05</v>
+        <v>8.686432209138969e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>7.363019465284518e-05</v>
+        <v>7.363019465284529e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>5.482485622965092e-05</v>
+        <v>5.482485622965093e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>8.108997919805663e-05</v>
+        <v>8.108997919805677e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>8.109172696285436e-05</v>
+        <v>8.109172696285433e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>8.102525956605434e-05</v>
+        <v>8.102525956605432e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>8.125097247307686e-05</v>
+        <v>8.12509724730767e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>5.353791629282977e-05</v>
+        <v>5.353791629282984e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001094136507317643</v>
+        <v>0.0001094136507317642</v>
       </c>
     </row>
     <row r="9">
@@ -6339,37 +6339,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.715458571208702e-05</v>
+        <v>3.7154585712087e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>4.409395249103988e-05</v>
+        <v>4.409395249103986e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.432226587713821e-05</v>
+        <v>4.432226587713831e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>5.227211892804569e-05</v>
+        <v>5.227211892804581e-05</v>
       </c>
       <c r="F9" t="n">
         <v>4.409395142322552e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.415865796938387e-05</v>
+        <v>4.415865796938385e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>4.416040573418248e-05</v>
+        <v>4.416040573418253e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.409393833738153e-05</v>
+        <v>4.409393833738152e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.431433348885212e-05</v>
+        <v>4.431433348885227e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>4.006142213411608e-05</v>
+        <v>4.006142213411607e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>4.421756945202205e-05</v>
+        <v>4.42175694520221e-05</v>
       </c>
     </row>
   </sheetData>
@@ -6455,37 +6455,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.389684784958534e-05</v>
+        <v>1.350449014528646e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.41507558054676e-05</v>
+        <v>1.38079202442044e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.414754935854906e-05</v>
+        <v>1.351768406776994e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.424599893693409e-05</v>
+        <v>1.389096178634386e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.397508031684127e-05</v>
+        <v>1.366545486017042e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.386859017659117e-05</v>
+        <v>1.350300300008106e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.419630660569605e-05</v>
+        <v>1.351735368066333e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.377385640302935e-05</v>
+        <v>1.349802458592063e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.477516854408739e-05</v>
+        <v>1.411123029399486e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.427313870486938e-05</v>
+        <v>1.386267221358542e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.401891603449577e-05</v>
+        <v>1.350716112999868e-05</v>
       </c>
     </row>
     <row r="3">
@@ -6495,37 +6495,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.416400274043864e-05</v>
+        <v>1.368929154739665e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.43987627727361e-05</v>
+        <v>1.416889723684607e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.445236140840799e-05</v>
+        <v>1.379791833433739e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.449470028621166e-05</v>
+        <v>1.43023109324209e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.422378166611857e-05</v>
+        <v>1.393007211823094e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.41315005629363e-05</v>
+        <v>1.368821465898474e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.450874926095743e-05</v>
+        <v>1.382408649325131e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.401974009717268e-05</v>
+        <v>1.365373168635191e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.50662773184639e-05</v>
+        <v>1.474369093031336e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.453163088785842e-05</v>
+        <v>1.426890428306254e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.430466123143105e-05</v>
+        <v>1.37433254267468e-05</v>
       </c>
     </row>
     <row r="4">
@@ -6535,22 +6535,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.201890326519311e-05</v>
+        <v>1.201890326519313e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.1821690925843e-05</v>
+        <v>1.182169092584298e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.216793468914793e-05</v>
+        <v>1.216793468914792e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.183138679921907e-05</v>
+        <v>1.183138679921906e-05</v>
       </c>
       <c r="F4" t="n">
         <v>1.183138679921907e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.199060944913807e-05</v>
+        <v>1.199060944913815e-05</v>
       </c>
       <c r="H4" t="n">
         <v>1.219749700479554e-05</v>
@@ -6559,13 +6559,13 @@
         <v>1.189772571615242e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.211370280570558e-05</v>
+        <v>1.211370280570556e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.19846198587329e-05</v>
+        <v>1.198461985873289e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.209277958061032e-05</v>
+        <v>1.20927795806103e-05</v>
       </c>
     </row>
     <row r="5">
@@ -6575,37 +6575,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.571756448997725e-05</v>
+        <v>4.571756448997717e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.986324777330764e-05</v>
+        <v>4.986324777330755e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.584753233118691e-05</v>
+        <v>5.584753233118689e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>4.986324814339115e-05</v>
+        <v>4.986324814339112e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.986324814339115e-05</v>
+        <v>4.986324814339112e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>5.035124671211353e-05</v>
+        <v>5.035124671211445e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>6.177897069471615e-05</v>
+        <v>6.177897069471617e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>4.986322674053471e-05</v>
+        <v>4.986322674053457e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>5.092760841390289e-05</v>
+        <v>5.092760841390295e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>4.771248714026379e-05</v>
+        <v>4.771248714026378e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.571113251835589e-05</v>
+        <v>5.571113251835597e-05</v>
       </c>
     </row>
     <row r="6">
@@ -6615,37 +6615,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.62109591390689e-05</v>
+        <v>1.621095913906893e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.313781992873007e-05</v>
+        <v>1.313781992873012e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.342240026704232e-05</v>
+        <v>1.34223937293985e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.310238892041662e-05</v>
+        <v>1.310238892041661e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.314468816973998e-05</v>
+        <v>1.314468816973996e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.323592055108205e-05</v>
+        <v>1.618266532301392e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.344630131829148e-05</v>
+        <v>1.642074931813738e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.314303681809632e-05</v>
+        <v>1.608978159002818e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.631647755478082e-05</v>
+        <v>1.34398630206409e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.323462180813146e-05</v>
+        <v>1.323462180813147e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.334074009029093e-05</v>
+        <v>1.334074009029091e-05</v>
       </c>
     </row>
     <row r="7">
@@ -6655,37 +6655,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.997932443093545e-05</v>
+        <v>1.997932443093548e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>1.985816791466772e-05</v>
+        <v>1.985816791466768e-05</v>
       </c>
       <c r="D7" t="n">
         <v>2.012832497835376e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>1.985859542002468e-05</v>
+        <v>1.985859542002465e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>1.985859542002468e-05</v>
+        <v>1.985859542002465e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>1.995103061488046e-05</v>
+        <v>1.995103061488049e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.015791817053787e-05</v>
+        <v>2.015791817053789e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>1.985814688189473e-05</v>
+        <v>1.985814688189475e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.007412397144788e-05</v>
+        <v>2.007412397144789e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>1.994504102447523e-05</v>
+        <v>1.994504102447522e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>2.005320074635265e-05</v>
+        <v>2.005320074635267e-05</v>
       </c>
     </row>
     <row r="8">
@@ -6695,37 +6695,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.147008553022399e-05</v>
+        <v>5.147008553022394e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>7.661091643514267e-05</v>
+        <v>7.661091643514251e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>8.211280463723666e-05</v>
+        <v>8.21128046372367e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>6.970289150337761e-05</v>
+        <v>6.970289150337766e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>5.214979696621321e-05</v>
+        <v>5.214979696621315e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>7.669836449875245e-05</v>
+        <v>7.669836449875234e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>7.690525205440947e-05</v>
+        <v>7.690525205440945e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>7.660548076576658e-05</v>
+        <v>7.660548076576654e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>7.682642150005598e-05</v>
+        <v>7.682642150005602e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>5.096664831718082e-05</v>
+        <v>5.096664831718081e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001031831368281426</v>
+        <v>0.0001031831368281427</v>
       </c>
     </row>
     <row r="9">
@@ -6735,37 +6735,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.435189263887482e-05</v>
+        <v>3.435189263887485e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>4.048962587930543e-05</v>
+        <v>4.048962587930552e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.075981406393989e-05</v>
+        <v>4.075981406393997e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>4.771225087287329e-05</v>
+        <v>4.771225087287334e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>4.048962491595933e-05</v>
+        <v>4.048962491595939e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.05824885795182e-05</v>
+        <v>4.058248857951836e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>4.078937613517565e-05</v>
+        <v>4.078937613517577e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.048960484653252e-05</v>
+        <v>4.048960484653248e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.07055819360857e-05</v>
+        <v>4.070558193608576e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>3.680294512506936e-05</v>
+        <v>3.695007378632329e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>4.068465871099046e-05</v>
+        <v>4.068465871099053e-05</v>
       </c>
     </row>
   </sheetData>
@@ -6851,37 +6851,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.410561735815206e-05</v>
+        <v>1.354456429338381e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.439127138305866e-05</v>
+        <v>1.385885927889388e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.510630676320477e-05</v>
+        <v>1.35972285892425e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.4490933660485e-05</v>
+        <v>1.394574298114687e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.420782322624104e-05</v>
+        <v>1.371008803588781e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.413946170377185e-05</v>
+        <v>1.35463454540735e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.453591088874033e-05</v>
+        <v>1.356428401557195e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.400237620463167e-05</v>
+        <v>1.353913805844664e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.601387112024089e-05</v>
+        <v>1.423152484528236e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.43951119803144e-05</v>
+        <v>1.390350049525481e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.422302867815479e-05</v>
+        <v>1.354689423442057e-05</v>
       </c>
     </row>
     <row r="3">
@@ -6891,37 +6891,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.440373143745894e-05</v>
+        <v>1.378713712291793e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.467317335998169e-05</v>
+        <v>1.428617563087724e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.555473154545534e-05</v>
+        <v>1.416802068214501e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.477356056438304e-05</v>
+        <v>1.442580708704496e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.449045013013909e-05</v>
+        <v>1.403681706086922e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.444265944575675e-05</v>
+        <v>1.38050276610225e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.489895935962714e-05</v>
+        <v>1.395983228450703e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.42821436037213e-05</v>
+        <v>1.375466868365273e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.64856305394691e-05</v>
+        <v>1.525776304229822e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.467050071320662e-05</v>
+        <v>1.434165022757549e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.453903913084029e-05</v>
+        <v>1.383626111080694e-05</v>
       </c>
     </row>
     <row r="4">
@@ -6931,37 +6931,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.216184031534621e-05</v>
+        <v>1.216184031534619e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.197434074745521e-05</v>
+        <v>1.19743407474552e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2756707763843e-05</v>
+        <v>1.275670776384301e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.198490825997568e-05</v>
+        <v>1.198490825997571e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.19849082599757e-05</v>
+        <v>1.198490825997571e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.217044093513226e-05</v>
+        <v>1.217044093513221e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.241819657668817e-05</v>
+        <v>1.241819657668815e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.205226104456985e-05</v>
+        <v>1.205226104456983e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.284905658324615e-05</v>
+        <v>1.28490565832461e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.207190281540015e-05</v>
+        <v>1.207190281540013e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.223297675399754e-05</v>
+        <v>1.223297675399751e-05</v>
       </c>
     </row>
     <row r="5">
@@ -6971,37 +6971,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.798632465144235e-05</v>
+        <v>4.798632465144233e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>5.009751823353206e-05</v>
+        <v>5.009751823353501e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>6.110687654825369e-05</v>
+        <v>6.110687654825368e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>5.009751865835347e-05</v>
+        <v>5.00975186583549e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>5.009751865835347e-05</v>
+        <v>5.00975186583549e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>5.101417015844329e-05</v>
+        <v>5.101417015844216e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>5.961591135102165e-05</v>
+        <v>5.961591135102159e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>5.009749111743703e-05</v>
+        <v>5.009749111743623e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>6.163387244100849e-05</v>
+        <v>6.163387244100847e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>4.935320479113147e-05</v>
+        <v>4.935320479113144e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.346501215041706e-05</v>
+        <v>5.434060621073016e-05</v>
       </c>
     </row>
     <row r="6">
@@ -7011,37 +7011,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.342136611960259e-05</v>
+        <v>1.342136611960255e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.330544021252436e-05</v>
+        <v>1.330544021252435e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.403834191655439e-05</v>
+        <v>1.403834191655436e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.326910297537546e-05</v>
+        <v>1.326910297537549e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.33131870306508e-05</v>
+        <v>1.331318703065079e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.639328130235076e-05</v>
+        <v>1.342996673938861e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.668106239240846e-05</v>
+        <v>1.668106239240841e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.331178684882622e-05</v>
+        <v>1.331178684882619e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.708345043629524e-05</v>
+        <v>1.419342764466885e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.333327883319017e-05</v>
+        <v>1.333327883319014e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.349489489629689e-05</v>
+        <v>1.349489489629688e-05</v>
       </c>
     </row>
     <row r="7">
@@ -7051,37 +7051,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.013630795880166e-05</v>
+        <v>2.013630795880162e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>2.002675580412413e-05</v>
+        <v>2.002675580412411e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.073114420550096e-05</v>
+        <v>2.073114420550095e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.002704544366044e-05</v>
+        <v>2.002704544366042e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.002704544366044e-05</v>
+        <v>2.002704544366042e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.014490857858769e-05</v>
+        <v>2.014490857858768e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.039266422014366e-05</v>
+        <v>2.03926642201436e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.002672868802528e-05</v>
+        <v>2.002672868802529e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.082352422670157e-05</v>
+        <v>2.082352422670153e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>2.004637045885561e-05</v>
+        <v>2.004637045885557e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>2.020744439745298e-05</v>
+        <v>2.020744439745293e-05</v>
       </c>
     </row>
     <row r="8">
@@ -7094,34 +7094,34 @@
         <v>5.164387378103595e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>7.682011319377177e-05</v>
+        <v>7.682011319377171e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>8.276132143260672e-05</v>
+        <v>8.276132143260688e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>6.990555641570354e-05</v>
+        <v>6.990555641570373e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>5.233586610770586e-05</v>
+        <v>5.233586610770585e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>7.693297758183159e-05</v>
+        <v>7.693297758183149e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>7.71807332233877e-05</v>
+        <v>7.718073322338772e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>7.68147976912692e-05</v>
+        <v>7.681479769126915e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>7.761656157766254e-05</v>
+        <v>7.761656157766239e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>5.108433795510594e-05</v>
+        <v>5.108433795510593e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001034031128986905</v>
+        <v>0.0001034031128986903</v>
       </c>
     </row>
     <row r="9">
@@ -7131,37 +7131,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.347806137451578e-05</v>
+        <v>3.347806137451573e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>3.934809024467661e-05</v>
+        <v>3.934809024467653e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.005251011890143e-05</v>
+        <v>4.005251011890134e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>4.624839892632038e-05</v>
+        <v>4.624839892632032e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>3.934808930688558e-05</v>
+        <v>3.934808930688551e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>3.946624301914016e-05</v>
+        <v>3.946624301914011e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>3.971399866069607e-05</v>
+        <v>3.971399866069603e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>3.934806312857778e-05</v>
+        <v>3.934806312857772e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.014485866725408e-05</v>
+        <v>4.0144858667254e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>3.576254937415248e-05</v>
+        <v>3.576254937415241e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>3.952877883800546e-05</v>
+        <v>3.95287788380054e-05</v>
       </c>
     </row>
   </sheetData>
@@ -7247,37 +7247,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.344827169639389e-05</v>
+        <v>1.341258106764223e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.373334878354747e-05</v>
+        <v>1.370143060846467e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.363708701169009e-05</v>
+        <v>1.342251804266879e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.382248741106427e-05</v>
+        <v>1.377908062404276e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.356965151196104e-05</v>
+        <v>1.356862460606136e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.342443633012005e-05</v>
+        <v>1.341132665965607e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.347876953753448e-05</v>
+        <v>1.341127180908885e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.33776361839803e-05</v>
+        <v>1.340887094210853e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.431334964412499e-05</v>
+        <v>1.398272558435653e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.373569066007345e-05</v>
+        <v>1.374162229292382e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.354418155266978e-05</v>
+        <v>1.341395393638197e-05</v>
       </c>
     </row>
     <row r="3">
@@ -7287,37 +7287,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.364662738665701e-05</v>
+        <v>1.348803323161743e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.392043681204202e-05</v>
+        <v>1.395417632193159e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.386380411222237e-05</v>
+        <v>1.35626048278416e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.40102539238234e-05</v>
+        <v>1.407892021205907e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.375741802472017e-05</v>
+        <v>1.37315260654947e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.361921177796084e-05</v>
+        <v>1.348091828921763e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.368200576620841e-05</v>
+        <v>1.351035614358085e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.356257275542399e-05</v>
+        <v>1.346785015749652e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.454058548343327e-05</v>
+        <v>1.448190179822058e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.391674706413761e-05</v>
+        <v>1.399756173448356e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.375719855690828e-05</v>
+        <v>1.352445207058332e-05</v>
       </c>
     </row>
     <row r="4">
@@ -7327,37 +7327,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.171165935613764e-05</v>
+        <v>1.171165935613759e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.154155010869267e-05</v>
+        <v>1.154155010869259e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.182390206029763e-05</v>
+        <v>1.182390206029754e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.154995607673577e-05</v>
+        <v>1.154995607673572e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.154995607673577e-05</v>
+        <v>1.15499560767357e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.168602198532047e-05</v>
+        <v>1.168602198532032e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.17304244466279e-05</v>
+        <v>1.173042444662753e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.162177305124716e-05</v>
+        <v>1.162177305124714e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.182595501332135e-05</v>
+        <v>1.182595501332133e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.164319595306342e-05</v>
+        <v>1.164319595306337e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.176996960384444e-05</v>
+        <v>1.176996960384439e-05</v>
       </c>
     </row>
     <row r="5">
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.464814139884329e-05</v>
+        <v>4.464814139884309e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.730948073675188e-05</v>
+        <v>4.730948073675125e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>4.880087759365841e-05</v>
+        <v>4.880087759365758e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>4.730948104770661e-05</v>
+        <v>4.730948104770646e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.730948104770661e-05</v>
+        <v>4.730948104770646e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>4.53908781201582e-05</v>
+        <v>4.539087812015523e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>5.24758124122284e-05</v>
+        <v>5.247581241222421e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>4.730946675673852e-05</v>
+        <v>4.730946675673818e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>4.526625898246915e-05</v>
+        <v>4.526625898246877e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>4.315308163081926e-05</v>
+        <v>4.315308163081903e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>4.762203144884836e-05</v>
+        <v>4.537205260771136e-05</v>
       </c>
     </row>
     <row r="6">
@@ -7407,37 +7407,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.302764290735079e-05</v>
+        <v>1.302764290735075e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.293396625515342e-05</v>
+        <v>1.293396625515328e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.31487401878308e-05</v>
+        <v>1.314874018783065e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.289703975068998e-05</v>
+        <v>1.289703975068991e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.293949257877048e-05</v>
+        <v>1.293949257877045e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.611507579717387e-05</v>
+        <v>1.611507579717371e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.617396069139522e-05</v>
+        <v>1.617396069139492e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.605082686310056e-05</v>
+        <v>1.605082686310028e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.626733762188834e-05</v>
+        <v>1.626733762188827e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.296290090344523e-05</v>
+        <v>1.296290090344518e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.308860463129561e-05</v>
+        <v>1.308860463129555e-05</v>
       </c>
     </row>
     <row r="7">
@@ -7447,37 +7447,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.022697416833668e-05</v>
+        <v>2.022697416833657e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>2.013710184345963e-05</v>
+        <v>2.013710184345956e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.033918660086017e-05</v>
+        <v>2.033918660085999e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.013719899449492e-05</v>
+        <v>2.013719899449477e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.013719899449492e-05</v>
+        <v>2.013719899449477e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.020133679751952e-05</v>
+        <v>2.020133679751943e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.024573925882693e-05</v>
+        <v>2.024573925882672e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.013708786344622e-05</v>
+        <v>2.013708786344613e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.034126982552039e-05</v>
+        <v>2.034126982552024e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>2.015851076526247e-05</v>
+        <v>2.015851076526236e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>2.028528441604349e-05</v>
+        <v>2.028528441604338e-05</v>
       </c>
     </row>
     <row r="8">
@@ -7487,37 +7487,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.398173369330115e-05</v>
+        <v>5.398173369330096e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>8.094836698361424e-05</v>
+        <v>8.094836698359381e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>8.675424549034607e-05</v>
+        <v>8.675424549034579e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>7.354956509545002e-05</v>
+        <v>7.354956509544977e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>5.474941422118057e-05</v>
+        <v>5.474941422118035e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>8.10071526618171e-05</v>
+        <v>8.100715266181675e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>8.105155512312366e-05</v>
+        <v>8.105155512312312e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>8.094290372774386e-05</v>
+        <v>8.094290372774365e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>8.115240200240098e-05</v>
+        <v>8.115240200240075e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>5.341078303030469e-05</v>
+        <v>5.34107830303044e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001093481906038266</v>
+        <v>0.0001093481906038262</v>
       </c>
     </row>
     <row r="9">
@@ -7527,37 +7527,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.700203263085803e-05</v>
+        <v>3.700203263085771e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>4.39904060550105e-05</v>
+        <v>4.399040605501001e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.419252130520483e-05</v>
+        <v>4.41925213052044e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>5.215855037226589e-05</v>
+        <v>5.215855037226565e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>4.399040500200879e-05</v>
+        <v>4.39904050020085e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.405464100907042e-05</v>
+        <v>4.405464100907013e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>4.409904347037785e-05</v>
+        <v>4.409904347037764e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.399039207499709e-05</v>
+        <v>4.399039207499692e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.419457403707129e-05</v>
+        <v>4.419457403707103e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>3.991065168442678e-05</v>
+        <v>3.99106516844266e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>4.413858862759438e-05</v>
+        <v>4.413858862759415e-05</v>
       </c>
     </row>
   </sheetData>
@@ -7643,37 +7643,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.379920439478742e-05</v>
+        <v>1.348134083948757e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.406772622942725e-05</v>
+        <v>1.378384604597132e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.365782413966651e-05</v>
+        <v>1.347390027746435e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.416207228696948e-05</v>
+        <v>1.386606172726156e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.389385606385882e-05</v>
+        <v>1.364280396830358e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.373349332995569e-05</v>
+        <v>1.347788259665816e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.396205469179539e-05</v>
+        <v>1.348699982954824e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.369309164787696e-05</v>
+        <v>1.347576403638333e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.459977880121053e-05</v>
+        <v>1.407924169708051e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.410034403841106e-05</v>
+        <v>1.383041757247906e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.37610849270423e-05</v>
+        <v>1.347552298502668e-05</v>
       </c>
     </row>
     <row r="3">
@@ -7683,37 +7683,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.405039590836149e-05</v>
+        <v>1.364441085625457e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.430231634325706e-05</v>
+        <v>1.41260570641428e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.38877793281408e-05</v>
+        <v>1.360206188421917e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.439734688413733e-05</v>
+        <v>1.425817781626092e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.412913066102667e-05</v>
+        <v>1.388965181106658e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.397481457179896e-05</v>
+        <v>1.362628727484777e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.423801375425713e-05</v>
+        <v>1.372043274821948e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.392558607357594e-05</v>
+        <v>1.361395536287598e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.486416072524319e-05</v>
+        <v>1.465571366511844e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.433257672924197e-05</v>
+        <v>1.418924965205856e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.400681051397514e-05</v>
+        <v>1.363420938925363e-05</v>
       </c>
     </row>
     <row r="4">
@@ -7723,25 +7723,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.195264506510808e-05</v>
+        <v>1.195264506510807e-05</v>
       </c>
       <c r="C4" t="n">
         <v>1.176614468035831e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.18686004942283e-05</v>
+        <v>1.186860049422828e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.177562951273444e-05</v>
+        <v>1.177562951273453e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.177562951273446e-05</v>
+        <v>1.177562951273452e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.190211450602068e-05</v>
+        <v>1.190211450602067e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.205005313007829e-05</v>
+        <v>1.205005313007828e-05</v>
       </c>
       <c r="I4" t="n">
         <v>1.184169031559323e-05</v>
@@ -7750,7 +7750,7 @@
         <v>1.200484724140322e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.18776139043799e-05</v>
+        <v>1.187761390437988e-05</v>
       </c>
       <c r="L4" t="n">
         <v>1.193131890209734e-05</v>
@@ -7763,37 +7763,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.481833024210804e-05</v>
+        <v>4.481833024210802e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.849980407713917e-05</v>
+        <v>4.849980407713913e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>4.890520910919114e-05</v>
+        <v>4.890520910919121e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>4.849980443901975e-05</v>
+        <v>4.849980443901971e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.849980443901975e-05</v>
+        <v>4.849980443901971e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>4.751453210105138e-05</v>
+        <v>4.751453210105189e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>5.557854926853043e-05</v>
+        <v>5.557854926853048e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>4.849979058819341e-05</v>
+        <v>4.849979058819334e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>4.522475565652922e-05</v>
+        <v>4.522475565652914e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>4.611735923259378e-05</v>
+        <v>4.611735923259381e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.118231006957147e-05</v>
+        <v>4.817407968987906e-05</v>
       </c>
     </row>
     <row r="6">
@@ -7803,37 +7803,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.613017561371934e-05</v>
+        <v>1.613017561371935e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.307652648707908e-05</v>
+        <v>1.307652648707906e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.311007532502002e-05</v>
+        <v>1.311006873898244e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.304153599228153e-05</v>
+        <v>1.304153599228152e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.308257044860916e-05</v>
+        <v>1.308257044860917e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.314122115524897e-05</v>
+        <v>1.607964505463195e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.625680809293765e-05</v>
+        <v>1.625680809293764e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.601922086420447e-05</v>
+        <v>1.60192208642045e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.332416552491939e-05</v>
+        <v>1.332416552491936e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.312023935865772e-05</v>
+        <v>1.31202393586577e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.317257867064539e-05</v>
+        <v>1.317257867064537e-05</v>
       </c>
     </row>
     <row r="7">
@@ -7843,13 +7843,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.990714241568658e-05</v>
+        <v>1.990714241568655e-05</v>
       </c>
       <c r="C7" t="n">
         <v>1.979620115511747e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>1.982306702768455e-05</v>
+        <v>1.982306702768451e-05</v>
       </c>
       <c r="E7" t="n">
         <v>1.979662320018802e-05</v>
@@ -7858,22 +7858,22 @@
         <v>1.979662320018802e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>1.985661185659916e-05</v>
+        <v>1.985661185659917e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.000455048065678e-05</v>
+        <v>2.000455048065675e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>1.97961876661717e-05</v>
+        <v>1.979618766617171e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>1.995934459198172e-05</v>
+        <v>1.995934459198168e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>1.98321112549584e-05</v>
+        <v>1.983211125495837e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>1.988581625267584e-05</v>
+        <v>1.988581625267581e-05</v>
       </c>
     </row>
     <row r="8">
@@ -7883,37 +7883,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.139315083927786e-05</v>
+        <v>5.139315083927781e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>7.653564811091772e-05</v>
+        <v>7.653564811091767e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>8.179248082490728e-05</v>
+        <v>8.179248082490713e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>6.962996007413417e-05</v>
+        <v>6.962996007413404e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>5.208280346962644e-05</v>
+        <v>5.208280346962642e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>7.659065115819755e-05</v>
+        <v>7.659065115819752e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>7.673858978225465e-05</v>
+        <v>7.673858978225454e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>7.653022696777018e-05</v>
+        <v>7.653022696777006e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>7.669834585960603e-05</v>
+        <v>7.669834585960599e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>5.084912454226485e-05</v>
+        <v>5.084912454226481e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001029935350165292</v>
+        <v>0.0001029935350165289</v>
       </c>
     </row>
     <row r="9">
@@ -7923,37 +7923,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.425452615999e-05</v>
+        <v>3.425452615998994e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>4.039310625690025e-05</v>
+        <v>4.039310625690024e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.042000318031827e-05</v>
+        <v>4.042000318031826e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>4.760492032675378e-05</v>
+        <v>4.760492032675375e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>4.039310530791314e-05</v>
+        <v>4.039310530791321e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.045351695838184e-05</v>
+        <v>4.045351695838193e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>4.060145558243956e-05</v>
+        <v>4.060145558243951e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.039309276795447e-05</v>
+        <v>4.039309276795449e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.055624969376449e-05</v>
+        <v>4.055624969376446e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>3.255975337148082e-05</v>
+        <v>3.680801923675819e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>4.04827213544586e-05</v>
+        <v>4.048272135445857e-05</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Ammonia/ammonia resource use mineral and metals results.xlsx
+++ b/Results/Ammonia/ammonia resource use mineral and metals results.xlsx
@@ -515,25 +515,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.339185046789549e-05</v>
+        <v>1.339185046789552e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.368617434489113e-05</v>
+        <v>1.368617434489115e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.340440121877934e-05</v>
+        <v>1.340440121877933e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.376282308511024e-05</v>
+        <v>1.376282308511023e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.355526323846732e-05</v>
+        <v>1.355526323846734e-05</v>
       </c>
       <c r="G2" t="n">
         <v>1.339624278756645e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.339721711264679e-05</v>
+        <v>1.339721711264681e-05</v>
       </c>
       <c r="I2" t="n">
         <v>1.339564444194992e-05</v>
@@ -542,7 +542,7 @@
         <v>1.395894591533589e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.372682910720864e-05</v>
+        <v>1.372682910720863e-05</v>
       </c>
       <c r="L2" t="n">
         <v>1.339741112047875e-05</v>
@@ -555,37 +555,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.342385095165073e-05</v>
+        <v>1.342385095165074e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.393565492487959e-05</v>
+        <v>1.393565492487961e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.351078816011193e-05</v>
+        <v>1.351078816011192e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.40587892178542e-05</v>
+        <v>1.405878921785419e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.371617587927313e-05</v>
+        <v>1.371617587927314e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.345354829289506e-05</v>
+        <v>1.345354829289507e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.348268508097658e-05</v>
+        <v>1.348268508097657e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.345271814185358e-05</v>
+        <v>1.34527181418536e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.443599108047507e-05</v>
+        <v>1.443599108047508e-05</v>
       </c>
       <c r="K3" t="n">
         <v>1.398557255740188e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.349089554249179e-05</v>
+        <v>1.349089554249181e-05</v>
       </c>
     </row>
     <row r="4">
@@ -595,37 +595,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.161489655858471e-05</v>
+        <v>1.16148965585847e-05</v>
       </c>
       <c r="C4" t="n">
         <v>1.152187350868455e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.175666306344815e-05</v>
+        <v>1.175666306344816e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.153121529190447e-05</v>
+        <v>1.153121529190449e-05</v>
       </c>
       <c r="F4" t="n">
         <v>1.153121529190448e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.165304881725249e-05</v>
+        <v>1.165304881725243e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.170864708766316e-05</v>
+        <v>1.170864708766317e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.160983064447437e-05</v>
+        <v>1.160983064447439e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.177499409346278e-05</v>
+        <v>1.177499409346279e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.163785727709452e-05</v>
+        <v>1.163785727709453e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.172050944431561e-05</v>
+        <v>1.172050944431562e-05</v>
       </c>
     </row>
     <row r="5">
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.44502243995218e-05</v>
+        <v>4.445022439952203e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.632884822960042e-05</v>
+        <v>4.632884822960054e-05</v>
       </c>
       <c r="D5" t="n">
         <v>4.573712728866047e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>4.632884856018761e-05</v>
+        <v>4.632884856018765e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.632884856018761e-05</v>
+        <v>4.632884856018765e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>4.445667788304146e-05</v>
+        <v>4.44566778830403e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>4.784242355815499e-05</v>
+        <v>4.784242355815506e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>4.632883919781209e-05</v>
+        <v>4.632883919781219e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>4.665410729196225e-05</v>
+        <v>4.665410729196237e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>4.350143166793674e-05</v>
+        <v>4.350143166793684e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>4.901526557079489e-05</v>
+        <v>4.901526557079498e-05</v>
       </c>
     </row>
     <row r="6">
@@ -675,37 +675,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.301706189976003e-05</v>
+        <v>1.301706189976005e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.30084214738197e-05</v>
+        <v>1.300842147381973e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.31661353628444e-05</v>
+        <v>1.316613536284441e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.296935699022542e-05</v>
+        <v>1.296935699022543e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.301394121601593e-05</v>
+        <v>1.301394121601595e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.636951355065355e-05</v>
+        <v>1.636951355065357e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.644092666518658e-05</v>
+        <v>1.64409266651866e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.632629537787551e-05</v>
+        <v>1.632629537787552e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.650633894518229e-05</v>
+        <v>1.650633894518228e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.304515483422016e-05</v>
+        <v>1.304515483422019e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.312541726139144e-05</v>
+        <v>1.312541726139145e-05</v>
       </c>
     </row>
     <row r="7">
@@ -715,37 +715,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.071568662234861e-05</v>
+        <v>2.071568662234869e-05</v>
       </c>
       <c r="C7" t="n">
         <v>2.071062974002671e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.085742513856571e-05</v>
+        <v>2.085742513856569e-05</v>
       </c>
       <c r="E7" t="n">
         <v>2.071049300448548e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.071049300448547e-05</v>
+        <v>2.071049300448548e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.075383888101637e-05</v>
+        <v>2.075383888101639e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.080943715142712e-05</v>
+        <v>2.080943715142716e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.071062070823832e-05</v>
+        <v>2.071062070823833e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.087578415722673e-05</v>
+        <v>2.087578415722678e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>2.073864734085844e-05</v>
+        <v>2.073864734085847e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>2.082129950807957e-05</v>
+        <v>2.082129950807958e-05</v>
       </c>
     </row>
     <row r="8">
@@ -755,37 +755,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.677766225488535e-05</v>
+        <v>5.677766225488544e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>8.567937886377816e-05</v>
+        <v>8.56793788637783e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>9.18134657274505e-05</v>
+        <v>9.181346572745061e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>7.777456962783331e-05</v>
+        <v>7.777456962783345e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>5.768866364651716e-05</v>
+        <v>5.768866364651724e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>8.571700198496209e-05</v>
+        <v>8.57170019849623e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>8.577260025537276e-05</v>
+        <v>8.577260025537296e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>8.567378381218412e-05</v>
+        <v>8.567378381218427e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>8.584462717790038e-05</v>
+        <v>8.584462717790043e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>5.626376857781195e-05</v>
+        <v>5.626376857781196e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001159741696087403</v>
+        <v>0.0001159741696087406</v>
       </c>
     </row>
     <row r="9">
@@ -795,37 +795,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.063781717012183e-05</v>
+        <v>4.063781717012187e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>4.874854862276973e-05</v>
+        <v>4.874854862276981e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.889537223620778e-05</v>
+        <v>4.88953722362078e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>5.811399500583087e-05</v>
+        <v>5.811399500583099e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>4.874854750687964e-05</v>
+        <v>4.874854750687969e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.879175776375942e-05</v>
+        <v>4.879175776375949e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>4.884735603417015e-05</v>
+        <v>4.88473560341702e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.87485395909814e-05</v>
+        <v>4.874853959098143e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.891370303996976e-05</v>
+        <v>4.891370303996983e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>3.855733998814117e-05</v>
+        <v>3.855733998814121e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>4.885921839082263e-05</v>
+        <v>4.885921839082265e-05</v>
       </c>
     </row>
   </sheetData>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.351703907055126e-05</v>
+        <v>1.351703907055127e-05</v>
       </c>
       <c r="C2" t="n">
         <v>1.384057497197967e-05</v>
@@ -926,22 +926,22 @@
         <v>1.36942131489897e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.352115174053088e-05</v>
+        <v>1.352115174053087e-05</v>
       </c>
       <c r="H2" t="n">
         <v>1.35412118577926e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.352147529570017e-05</v>
+        <v>1.352147529570018e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.417587299838811e-05</v>
+        <v>1.41758729983881e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.387654575871276e-05</v>
+        <v>1.387654575871279e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.35379128379324e-05</v>
+        <v>1.353791283793223e-05</v>
       </c>
     </row>
     <row r="3">
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.37004422883095e-05</v>
+        <v>1.370044228830949e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.426827121885225e-05</v>
+        <v>1.426827121885224e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.392787584919753e-05</v>
+        <v>1.392787584919752e-05</v>
       </c>
       <c r="E3" t="n">
         <v>1.440548868075552e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.402299101157877e-05</v>
+        <v>1.402299101157875e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.373317132802562e-05</v>
+        <v>1.37331713280256e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.390071295569764e-05</v>
+        <v>1.390071295569763e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.373789139018377e-05</v>
+        <v>1.373789139018376e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.501229186020417e-05</v>
+        <v>1.501229186020415e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.42731136106727e-05</v>
+        <v>1.427311361067279e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.387854171649923e-05</v>
+        <v>1.387854171649915e-05</v>
       </c>
     </row>
     <row r="4">
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.20340595609487e-05</v>
+        <v>1.203405956094863e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.196115784665599e-05</v>
+        <v>1.196115784665597e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.238597798266455e-05</v>
+        <v>1.238597798266451e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.197138387048235e-05</v>
+        <v>1.197138387048229e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.197138387048231e-05</v>
+        <v>1.197138387048229e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.20690561931789e-05</v>
+        <v>1.206905619317884e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.233992693764269e-05</v>
+        <v>1.233992693764264e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.203628563081943e-05</v>
+        <v>1.203628563081937e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.249921896149265e-05</v>
+        <v>1.249921896149259e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.198073186345557e-05</v>
+        <v>1.198073186345553e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.23116672387445e-05</v>
+        <v>1.231166723874445e-05</v>
       </c>
     </row>
     <row r="5">
@@ -1031,37 +1031,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.64097337941722e-05</v>
+        <v>4.640973379417222e-05</v>
       </c>
       <c r="C5" t="n">
         <v>5.02473691047571e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.52631982190119e-05</v>
+        <v>5.526319821901191e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>5.02473694672949e-05</v>
+        <v>5.024736946729483e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>5.02473694672949e-05</v>
+        <v>5.024736946729483e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>4.896979436222046e-05</v>
+        <v>4.896979436221983e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>5.695718416964081e-05</v>
+        <v>5.695718416964076e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>5.02473616230387e-05</v>
+        <v>5.024736162303873e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>5.380197261433267e-05</v>
+        <v>5.380197261433247e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>4.813112484478881e-05</v>
+        <v>4.813112484478877e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.463416823243825e-05</v>
+        <v>5.46341682324381e-05</v>
       </c>
     </row>
     <row r="6">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.328607649050101e-05</v>
+        <v>1.3286076490501e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.328526092940919e-05</v>
+        <v>1.328526092940916e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.663912980021294e-05</v>
+        <v>1.663912980021292e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.324939203996406e-05</v>
+        <v>1.324939203996403e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.329089507185348e-05</v>
+        <v>1.329089507185347e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.627813608554972e-05</v>
+        <v>1.627813608554967e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.658658453632423e-05</v>
+        <v>1.658658453632417e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.328830256037175e-05</v>
+        <v>1.328830256037174e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.383470879267309e-05</v>
+        <v>1.383470879267307e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.323476468503915e-05</v>
+        <v>1.323476468503912e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.356751906994662e-05</v>
+        <v>1.356751906994659e-05</v>
       </c>
     </row>
     <row r="7">
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.000219170353658e-05</v>
+        <v>2.000219170353657e-05</v>
       </c>
       <c r="C7" t="n">
         <v>2.000442525512566e-05</v>
@@ -1120,28 +1120,28 @@
         <v>2.035407859815215e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.000518253399125e-05</v>
+        <v>2.000518253399123e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.000518253399125e-05</v>
+        <v>2.000518253399123e-05</v>
       </c>
       <c r="G7" t="n">
         <v>2.003718833576678e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.030805908023058e-05</v>
+        <v>2.030805908023057e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.000441777340732e-05</v>
+        <v>2.000441777340728e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.046735110408054e-05</v>
+        <v>2.046735110408053e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>1.994886400604347e-05</v>
+        <v>1.994886400604346e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>2.02797993813324e-05</v>
+        <v>2.027979938133238e-05</v>
       </c>
     </row>
     <row r="8">
@@ -1151,37 +1151,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.1504295113589e-05</v>
+        <v>5.150429511358896e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>7.678343226999997e-05</v>
+        <v>7.678343226999993e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>8.236752449645242e-05</v>
+        <v>8.236752449645241e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>6.987138070769784e-05</v>
+        <v>6.987138070769777e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>5.230805641749265e-05</v>
+        <v>5.230805641749257e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>7.681046111217385e-05</v>
+        <v>7.681046111217379e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>7.708133185663731e-05</v>
+        <v>7.708133185663737e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>7.677769054981431e-05</v>
+        <v>7.67776905498143e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>7.724559039385995e-05</v>
+        <v>7.724559039385988e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>5.098154247050947e-05</v>
+        <v>5.098154247050948e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001034509217058613</v>
+        <v>0.0001034509217058614</v>
       </c>
     </row>
     <row r="9">
@@ -1191,37 +1191,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.331946840687406e-05</v>
+        <v>3.331946840687403e-05</v>
       </c>
       <c r="C9" t="n">
         <v>3.929196194792479e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>3.964164704719988e-05</v>
+        <v>3.964164704719983e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>4.618151426014217e-05</v>
+        <v>4.618151426014212e-05</v>
       </c>
       <c r="F9" t="n">
         <v>3.929196095418863e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>3.932472502856584e-05</v>
+        <v>3.932472502856592e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>3.959559577302972e-05</v>
+        <v>3.959559577302976e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>3.929195446620642e-05</v>
+        <v>3.929195446620643e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>3.975488779687971e-05</v>
+        <v>3.975488779687969e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>3.577720871030666e-05</v>
+        <v>3.577720871030662e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>3.956733607413149e-05</v>
+        <v>3.956733607413151e-05</v>
       </c>
     </row>
   </sheetData>
@@ -1307,37 +1307,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.391776340519942e-05</v>
+        <v>1.39177634051995e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.376818043494141e-05</v>
+        <v>1.37681804349414e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.394859760151833e-05</v>
+        <v>1.394859760151844e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.393884706270342e-05</v>
+        <v>1.393884706270343e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.393884402550683e-05</v>
+        <v>1.393884402550692e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.393307706908986e-05</v>
+        <v>1.393307706908978e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.396213401442926e-05</v>
+        <v>1.396213401442925e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.393779364311155e-05</v>
+        <v>1.393779364311158e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.402087967974375e-05</v>
+        <v>1.402087967974387e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.402909940256885e-05</v>
+        <v>1.402909940256886e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.392335343845929e-05</v>
+        <v>1.392335343845931e-05</v>
       </c>
     </row>
     <row r="3">
@@ -1347,34 +1347,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.403152526847521e-05</v>
+        <v>1.403152526847532e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.384645776265103e-05</v>
+        <v>1.3846457762651e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.429039386175278e-05</v>
+        <v>1.42903938617529e-05</v>
       </c>
       <c r="E3" t="n">
         <v>1.42155603233209e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.421555728612452e-05</v>
+        <v>1.421555728612437e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.418035745066161e-05</v>
+        <v>1.418035745066162e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.441039336747602e-05</v>
+        <v>1.441039336747609e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.421386347049967e-05</v>
+        <v>1.421386347049974e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.423279164024785e-05</v>
+        <v>1.423279164024779e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.429700128693477e-05</v>
+        <v>1.429700128693472e-05</v>
       </c>
       <c r="L3" t="n">
         <v>1.414140586242129e-05</v>
@@ -1387,37 +1387,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.191331561778155e-05</v>
+        <v>1.191331561778154e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.176400091926855e-05</v>
+        <v>1.176400091926856e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.226160204963469e-05</v>
+        <v>1.22616020496347e-05</v>
       </c>
       <c r="E4" t="n">
+        <v>1.200574108810619e-05</v>
+      </c>
+      <c r="F4" t="n">
         <v>1.200574108810618e-05</v>
       </c>
-      <c r="F4" t="n">
-        <v>1.200574108810619e-05</v>
-      </c>
       <c r="G4" t="n">
-        <v>1.207463822591219e-05</v>
+        <v>1.207463822591218e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.244567901533531e-05</v>
+        <v>1.244567901533536e-05</v>
       </c>
       <c r="I4" t="n">
         <v>1.209055656274147e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.18927530389195e-05</v>
+        <v>1.189275303891948e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.200059286747269e-05</v>
+        <v>1.200059286747265e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.202227763204331e-05</v>
+        <v>1.202227763204327e-05</v>
       </c>
     </row>
     <row r="5">
@@ -1427,37 +1427,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.020308292730354e-05</v>
+        <v>2.020308292730355e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.29196276656882e-05</v>
+        <v>4.291962766568827e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>4.791755301991499e-05</v>
+        <v>4.791755301991498e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>4.591281052953465e-05</v>
+        <v>4.591281052953508e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.591281052953465e-05</v>
+        <v>4.591281052953519e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>4.504389198725525e-05</v>
+        <v>4.504389198725384e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>5.48737326277465e-05</v>
+        <v>5.487373262774742e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>4.591281209619625e-05</v>
+        <v>4.591281209619733e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>4.227518877808848e-05</v>
+        <v>4.227518877808847e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>4.333204187726746e-05</v>
+        <v>4.333204187726752e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>4.690117673071695e-05</v>
+        <v>4.690117673071694e-05</v>
       </c>
     </row>
     <row r="6">
@@ -1467,28 +1467,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.634820184296554e-05</v>
+        <v>1.634820184296557e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.315291256075285e-05</v>
+        <v>1.315291256075287e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.353896307394473e-05</v>
+        <v>1.353896307394476e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.331893571459898e-05</v>
+        <v>1.331893571459908e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.336273142618843e-05</v>
+        <v>1.336273142618846e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.334418690439289e-05</v>
+        <v>1.334418690439295e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.709223762658689e-05</v>
+        <v>1.709223762658697e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.336010524122223e-05</v>
+        <v>1.336010524122224e-05</v>
       </c>
       <c r="J6" t="n">
         <v>1.638179218253072e-05</v>
@@ -1497,7 +1497,7 @@
         <v>1.327203724141109e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.329423146030174e-05</v>
+        <v>1.329423146030176e-05</v>
       </c>
     </row>
     <row r="7">
@@ -1507,37 +1507,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.042338480444183e-05</v>
+        <v>2.042338480444186e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>2.040938234040248e-05</v>
+        <v>2.040938234040249e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.077166617987054e-05</v>
+        <v>2.077166617987059e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.060066536220677e-05</v>
+        <v>2.060066536220683e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.060066536220677e-05</v>
+        <v>2.060066536220685e-05</v>
       </c>
       <c r="G7" t="n">
         <v>2.058470741257249e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.095574820199554e-05</v>
+        <v>2.095574820199564e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.060062574940171e-05</v>
+        <v>2.060062574940177e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.040282222557975e-05</v>
+        <v>2.040282222557977e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>2.051066205413293e-05</v>
+        <v>2.051066205413294e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>2.053234681870355e-05</v>
+        <v>2.053234681870356e-05</v>
       </c>
     </row>
     <row r="8">
@@ -1547,37 +1547,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.380320141105266e-05</v>
+        <v>5.380320141105258e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>8.065288754079338e-05</v>
+        <v>8.065288754079344e-05</v>
       </c>
       <c r="D8" t="n">
         <v>8.65790991966861e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>7.349804280671197e-05</v>
+        <v>7.349804280671192e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>5.483183678871397e-05</v>
+        <v>5.483183678871404e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>8.082288024354554e-05</v>
+        <v>8.08228802435455e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>8.119392103297846e-05</v>
+        <v>8.119392103297864e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>8.083879858037484e-05</v>
+        <v>8.083879858037472e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>8.064627349791415e-05</v>
+        <v>8.064627349791427e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>5.3391570904368e-05</v>
+        <v>5.339157090436789e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001088263185897384</v>
+        <v>0.0001088263185897382</v>
       </c>
     </row>
     <row r="9">
@@ -1587,37 +1587,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.702874083957803e-05</v>
+        <v>3.702874083957802e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>4.406587089434934e-05</v>
+        <v>4.406587089434942e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.442816013082364e-05</v>
+        <v>4.442816013082372e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>5.239396878781258e-05</v>
+        <v>5.239396878781267e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>4.425711139644788e-05</v>
+        <v>4.425711139644797e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.424119596651929e-05</v>
+        <v>4.424119596651945e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>4.461223675594239e-05</v>
+        <v>4.461223675594249e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.425711430334873e-05</v>
+        <v>4.425711430334869e-05</v>
       </c>
       <c r="J9" t="n">
         <v>4.405931077952667e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>4.008169687799341e-05</v>
+        <v>4.008169687799347e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>4.418883537265051e-05</v>
+        <v>4.418883537265049e-05</v>
       </c>
     </row>
   </sheetData>
@@ -1703,37 +1703,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.393830117240029e-05</v>
+        <v>1.393830117240037e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.38212815649132e-05</v>
+        <v>1.382128156491321e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.397214412148148e-05</v>
+        <v>1.397214412148152e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.399909543878514e-05</v>
+        <v>1.399909543878518e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.399909285071932e-05</v>
+        <v>1.399909285071937e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.395652562471763e-05</v>
+        <v>1.395652562471774e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.398782189119695e-05</v>
+        <v>1.398782189119686e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.396319237245327e-05</v>
+        <v>1.39631923724533e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.407971849872587e-05</v>
+        <v>1.407971849872588e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.407689731050637e-05</v>
+        <v>1.407689731050631e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.394529877118527e-05</v>
+        <v>1.394529877118524e-05</v>
       </c>
     </row>
     <row r="3">
@@ -1743,37 +1743,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.41037330519754e-05</v>
+        <v>1.410373305197545e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.399893599928512e-05</v>
+        <v>1.39989359992851e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.43839078547058e-05</v>
+        <v>1.438390785470582e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.437984167911394e-05</v>
+        <v>1.437984167911399e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.437983909104812e-05</v>
+        <v>1.437983909104819e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.427332260090168e-05</v>
+        <v>1.427332260090169e-05</v>
       </c>
       <c r="H3" t="n">
         <v>1.452027241624995e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.432062658449858e-05</v>
+        <v>1.432062658449855e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.431925217803194e-05</v>
+        <v>1.431925217803195e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.441771570820412e-05</v>
+        <v>1.441771570820406e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.422476422120535e-05</v>
+        <v>1.422476422120529e-05</v>
       </c>
     </row>
     <row r="4">
@@ -1783,37 +1783,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.209774308928707e-05</v>
+        <v>1.209774308928704e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.199960083449857e-05</v>
+        <v>1.199960083449854e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.248001476768476e-05</v>
+        <v>1.248001476768478e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.225100979485817e-05</v>
+        <v>1.225100979485818e-05</v>
       </c>
       <c r="F4" t="n">
         <v>1.225100979485818e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.229192660752509e-05</v>
+        <v>1.229192660752508e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.268892184735205e-05</v>
+        <v>1.268892184735203e-05</v>
       </c>
       <c r="I4" t="n">
         <v>1.232981077209135e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.19762484088867e-05</v>
+        <v>1.197624840888671e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.219248043171701e-05</v>
+        <v>1.219248043171702e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.222362605847705e-05</v>
+        <v>1.222362605847701e-05</v>
       </c>
     </row>
     <row r="5">
@@ -1823,13 +1823,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.202920506076161e-05</v>
+        <v>2.202920506076157e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.448575614608462e-05</v>
+        <v>4.448575614608458e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>4.881243292882322e-05</v>
+        <v>4.881243292882326e-05</v>
       </c>
       <c r="E5" t="n">
         <v>4.728994880038032e-05</v>
@@ -1838,16 +1838,16 @@
         <v>4.728994880038032e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>4.613900969873981e-05</v>
+        <v>4.613900969874187e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>5.622990819964938e-05</v>
+        <v>5.622990819964897e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>4.728995450056442e-05</v>
+        <v>4.728995450056435e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>4.117714948869203e-05</v>
+        <v>4.117714948869202e-05</v>
       </c>
       <c r="K5" t="n">
         <v>4.401353592524347e-05</v>
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.635461969794761e-05</v>
+        <v>1.635461969794755e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.334432491091047e-05</v>
+        <v>1.33443249109105e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.683465062796117e-05</v>
+        <v>1.683465062796112e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.351308551137309e-05</v>
+        <v>1.351308551137311e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.355665794338865e-05</v>
+        <v>1.355665794338862e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.654880321618557e-05</v>
+        <v>1.654880321618564e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.723240504500956e-05</v>
+        <v>1.723240504500951e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.355363423992491e-05</v>
+        <v>1.355363423992487e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.32819099066707e-05</v>
+        <v>1.328190990667069e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.341664958962801e-05</v>
+        <v>1.3416649589628e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.344965602872236e-05</v>
+        <v>1.344965602872237e-05</v>
       </c>
     </row>
     <row r="7">
@@ -1903,37 +1903,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.016931433572519e-05</v>
+        <v>2.016931433572515e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>2.020953865362538e-05</v>
+        <v>2.020953865362536e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.05515836998891e-05</v>
+        <v>2.055158369988906e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.040242606977063e-05</v>
+        <v>2.040242606977067e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.040242606977063e-05</v>
+        <v>2.040242606977067e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.036349785396327e-05</v>
+        <v>2.036349785396331e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.076049309379019e-05</v>
+        <v>2.076049309379016e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.040138201852948e-05</v>
+        <v>2.040138201852943e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.004781965532485e-05</v>
+        <v>2.004781965532483e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>2.026405167815515e-05</v>
+        <v>2.026405167815511e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>2.029519730491516e-05</v>
+        <v>2.029519730491515e-05</v>
       </c>
     </row>
     <row r="8">
@@ -1943,34 +1943,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.184004291361394e-05</v>
+        <v>5.1840042913614e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>7.737470043608735e-05</v>
+        <v>7.737470043608729e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>8.299591068176619e-05</v>
+        <v>8.29959106817661e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>7.059504634410778e-05</v>
+        <v>7.059504634410783e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>5.288067569573443e-05</v>
+        <v>5.288067569573436e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>7.75226349694503e-05</v>
+        <v>7.752263496945024e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>7.791963020930659e-05</v>
+        <v>7.791963020930641e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>7.756051913401649e-05</v>
+        <v>7.756051913401652e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>7.721196597783588e-05</v>
+        <v>7.72119659778358e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>5.146131998129573e-05</v>
+        <v>5.146131998129565e-05</v>
       </c>
       <c r="L8" t="n">
         <v>0.0001040791084482037</v>
@@ -1983,37 +1983,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.460385835486891e-05</v>
+        <v>3.460385835486875e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>4.097124843448996e-05</v>
+        <v>4.097124843448999e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.131329617596492e-05</v>
+        <v>4.131329617596489e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>4.846449997312817e-05</v>
+        <v>4.846449997312824e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>4.11630848176768e-05</v>
+        <v>4.116308481767679e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.112520763482786e-05</v>
+        <v>4.112520763482793e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>4.152220287465482e-05</v>
+        <v>4.152220287465475e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.116309179939415e-05</v>
+        <v>4.116309179939399e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.080952943618942e-05</v>
+        <v>4.080952943618946e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>3.735977692821827e-05</v>
+        <v>3.735977692821829e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>4.105690708577991e-05</v>
+        <v>4.105690708577984e-05</v>
       </c>
     </row>
   </sheetData>
@@ -2102,34 +2102,34 @@
         <v>1.394775228289149e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.387112406745809e-05</v>
+        <v>1.387112406745803e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.398405405524472e-05</v>
+        <v>1.398405405524475e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.404265898821278e-05</v>
+        <v>1.404265898821277e-05</v>
       </c>
       <c r="F2" t="n">
         <v>1.404265681438251e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.396865347457209e-05</v>
+        <v>1.39686534745722e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.399679654693295e-05</v>
+        <v>1.399679654693298e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.397336451737154e-05</v>
+        <v>1.397336451737153e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.416112259147008e-05</v>
+        <v>1.416112259146997e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.410261951152301e-05</v>
+        <v>1.410261951152307e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.39620759914168e-05</v>
+        <v>1.396207599141681e-05</v>
       </c>
     </row>
     <row r="3">
@@ -2142,34 +2142,34 @@
         <v>1.412812193770061e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.411209682820425e-05</v>
+        <v>1.411209682820426e-05</v>
       </c>
       <c r="D3" t="n">
         <v>1.44257501552625e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.4464439212395e-05</v>
+        <v>1.446443921239493e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.446443703856481e-05</v>
+        <v>1.446443703856464e-05</v>
       </c>
       <c r="G3" t="n">
         <v>1.431680430472153e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.454203198808912e-05</v>
+        <v>1.454203198808915e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.43501150329426e-05</v>
+        <v>1.435011503294258e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.445956650112834e-05</v>
+        <v>1.445956650112849e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.447121529685241e-05</v>
+        <v>1.447121529685255e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.430188438612257e-05</v>
+        <v>1.430188438612262e-05</v>
       </c>
     </row>
     <row r="4">
@@ -2179,37 +2179,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.22678472146229e-05</v>
+        <v>1.226784721462293e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.220242627709397e-05</v>
+        <v>1.220242627709401e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.267789243299323e-05</v>
+        <v>1.267789243299327e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.242932633132193e-05</v>
+        <v>1.242932633132196e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.242932633132195e-05</v>
+        <v>1.242932633132196e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.249222474137079e-05</v>
+        <v>1.249222474137077e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.285471073114969e-05</v>
+        <v>1.285471073114974e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.250782471130137e-05</v>
+        <v>1.250782471130142e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.214040196915688e-05</v>
+        <v>1.214040196915692e-05</v>
       </c>
       <c r="K4" t="n">
         <v>1.236733658174845e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.247630859362918e-05</v>
+        <v>1.247630859362921e-05</v>
       </c>
     </row>
     <row r="5">
@@ -2219,37 +2219,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.322195273793228e-05</v>
+        <v>2.322195273793235e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.646516718545658e-05</v>
+        <v>4.646516718545661e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.044699942283843e-05</v>
+        <v>5.044699942283842e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>4.86024199522504e-05</v>
+        <v>4.860241995225041e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.86024199522504e-05</v>
+        <v>4.860241995225041e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>4.786066600863638e-05</v>
+        <v>4.786066600863632e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>5.744567639429383e-05</v>
+        <v>5.744567639429397e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>4.86024196663828e-05</v>
+        <v>4.860241966638276e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>4.22875273082717e-05</v>
+        <v>4.228752730827171e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>4.526139477391305e-05</v>
+        <v>4.526139477391308e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.083925316810693e-05</v>
+        <v>5.083925316810696e-05</v>
       </c>
     </row>
     <row r="6">
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.349927338417737e-05</v>
+        <v>1.349927338417739e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.356437321951135e-05</v>
+        <v>1.356437321951141e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.391540461684299e-05</v>
+        <v>1.391540461684303e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.369564378601456e-05</v>
+        <v>1.369564378601464e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.374241281233658e-05</v>
+        <v>1.374241281233662e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.680552107676658e-05</v>
+        <v>1.680552107676662e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.753894821666787e-05</v>
+        <v>1.753894821666793e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.682112104669719e-05</v>
+        <v>1.682112104669725e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.65299460652383e-05</v>
+        <v>1.652994606523834e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.359778643224977e-05</v>
+        <v>1.359778643224969e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.371019902058353e-05</v>
+        <v>1.371019902058359e-05</v>
       </c>
     </row>
     <row r="7">
@@ -2299,37 +2299,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.038229116633165e-05</v>
+        <v>2.03822911663317e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>2.046766192745737e-05</v>
+        <v>2.04676619274574e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.079233482166567e-05</v>
+        <v>2.07923348216657e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.062410856243376e-05</v>
+        <v>2.06241085624338e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.062410856243376e-05</v>
+        <v>2.06241085624338e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.060666869307952e-05</v>
+        <v>2.060666869307956e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.096915468285851e-05</v>
+        <v>2.096915468285854e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.062226866301013e-05</v>
+        <v>2.062226866301016e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.025484592086569e-05</v>
+        <v>2.025484592086571e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>2.04817805334572e-05</v>
+        <v>2.048178053345724e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>2.059075254533797e-05</v>
+        <v>2.059075254533801e-05</v>
       </c>
     </row>
     <row r="8">
@@ -2339,34 +2339,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.212117413502861e-05</v>
+        <v>5.212117413502865e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>7.778958147531179e-05</v>
+        <v>7.778958147531185e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>8.341085735678949e-05</v>
+        <v>8.341085735678952e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>7.094859248875223e-05</v>
+        <v>7.094859248875244e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>5.317297752998703e-05</v>
+        <v>5.317297752998706e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>7.792179002626671e-05</v>
+        <v>7.792179002626683e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>7.828427601609089e-05</v>
+        <v>7.828427601609102e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>7.793738999619744e-05</v>
+        <v>7.79373899961974e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>7.757499372201941e-05</v>
+        <v>7.757499372201948e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>5.174557174326675e-05</v>
+        <v>5.174557174326676e-05</v>
       </c>
       <c r="L8" t="n">
         <v>0.0001046223935046775</v>
@@ -2379,37 +2379,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.375005360819522e-05</v>
+        <v>3.37500536081953e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>3.988694600335265e-05</v>
+        <v>3.988694600335275e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.021162091012696e-05</v>
+        <v>4.021162091012707e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>4.702487948860906e-05</v>
+        <v>4.702487948860913e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>4.004155174860125e-05</v>
+        <v>4.004155174860131e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.002595276897485e-05</v>
+        <v>4.002595276897488e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>4.038843875875382e-05</v>
+        <v>4.03884387587539e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.004155273890543e-05</v>
+        <v>4.004155273890553e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>3.9674129996761e-05</v>
+        <v>3.967412999676109e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>3.625253536483394e-05</v>
+        <v>3.625253536483395e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>4.001003662123327e-05</v>
+        <v>4.001003662123338e-05</v>
       </c>
     </row>
   </sheetData>
@@ -2498,34 +2498,34 @@
         <v>1.398654619207236e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.382142316524827e-05</v>
+        <v>1.382142316524828e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.402774805490239e-05</v>
+        <v>1.402774805490238e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.399611617359372e-05</v>
+        <v>1.399611617359377e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.399611324245315e-05</v>
+        <v>1.399611324245317e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.400357094631251e-05</v>
+        <v>1.400357094631248e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.402700987122823e-05</v>
+        <v>1.402700987122822e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.400704176497752e-05</v>
+        <v>1.40070417649776e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.407115921886096e-05</v>
+        <v>1.407115921886093e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.408895155093241e-05</v>
+        <v>1.408895155093249e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.399293980695165e-05</v>
+        <v>1.399293980695167e-05</v>
       </c>
     </row>
     <row r="3">
@@ -2538,34 +2538,34 @@
         <v>1.416214622527263e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.394883704791351e-05</v>
+        <v>1.394883704791353e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.449471363272607e-05</v>
+        <v>1.449471363272605e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.432962748137771e-05</v>
+        <v>1.432962748137765e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.432962455023708e-05</v>
+        <v>1.432962455023706e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.432317605853494e-05</v>
+        <v>1.432317605853496e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.451433266554292e-05</v>
+        <v>1.451433266554298e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.434770544829247e-05</v>
+        <v>1.434770544829245e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.435839904446101e-05</v>
+        <v>1.435839904446096e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.438419517205833e-05</v>
+        <v>1.438419517205843e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.427875223741401e-05</v>
+        <v>1.427875223741403e-05</v>
       </c>
     </row>
     <row r="4">
@@ -2581,31 +2581,31 @@
         <v>1.190868375479129e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2527913331697e-05</v>
+        <v>1.252791333169702e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.216581375440226e-05</v>
+        <v>1.216581375440228e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.216581375440226e-05</v>
+        <v>1.216581375440227e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2243137658212e-05</v>
+        <v>1.224313765821203e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.255235824393124e-05</v>
+        <v>1.255235824393125e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.224479833794876e-05</v>
+        <v>1.224479833794879e-05</v>
       </c>
       <c r="J4" t="n">
         <v>1.209428854548755e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.209084292501982e-05</v>
+        <v>1.209084292501983e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.218130554821838e-05</v>
+        <v>1.21813055482184e-05</v>
       </c>
     </row>
     <row r="5">
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.284608449826766e-05</v>
+        <v>2.284608449826765e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.545186984091766e-05</v>
+        <v>4.545186984091769e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.257896936307022e-05</v>
+        <v>5.25789693630702e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>4.85986866720723e-05</v>
+        <v>4.859868667207324e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.85986866720723e-05</v>
+        <v>4.859868667207324e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>4.803876193295826e-05</v>
+        <v>4.803876193295863e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>5.690542125732567e-05</v>
+        <v>5.690542125732581e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>4.859868483005136e-05</v>
+        <v>4.859868483005221e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>4.595327541999807e-05</v>
+        <v>4.595327541999821e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>4.484970550396436e-05</v>
+        <v>4.48497055039644e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.004668324617929e-05</v>
+        <v>5.004668324617933e-05</v>
       </c>
     </row>
     <row r="6">
@@ -2658,34 +2658,34 @@
         <v>1.335093973417998e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.33150602590329e-05</v>
+        <v>1.331506025902846e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.382765943508974e-05</v>
+        <v>1.382765943508977e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.349246731526411e-05</v>
+        <v>1.349246731526417e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.353619047183288e-05</v>
+        <v>1.353619047183291e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.353155805515355e-05</v>
+        <v>1.353155805515357e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.722012056630222e-05</v>
+        <v>1.722012056630228e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.670263567466098e-05</v>
+        <v>1.670263567466106e-05</v>
       </c>
       <c r="J6" t="n">
         <v>1.346842459016716e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.337846722822521e-05</v>
+        <v>1.337846722822522e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.347218873042275e-05</v>
+        <v>1.347218873042278e-05</v>
       </c>
     </row>
     <row r="7">
@@ -2695,37 +2695,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.055781616621843e-05</v>
+        <v>2.055781616621844e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>2.053823735066828e-05</v>
+        <v>2.053823735066834e-05</v>
       </c>
       <c r="D7" t="n">
         <v>2.102320487415377e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.07417567485937e-05</v>
+        <v>2.074175674859379e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.07417567485937e-05</v>
+        <v>2.074175674859379e-05</v>
       </c>
       <c r="G7" t="n">
         <v>2.073843448719203e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.104765507291127e-05</v>
+        <v>2.104765507291128e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.074009516692881e-05</v>
+        <v>2.074009516692889e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.058958537446758e-05</v>
+        <v>2.05895853744676e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>2.058613975399984e-05</v>
+        <v>2.058613975399983e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>2.06766023771984e-05</v>
+        <v>2.067660237719844e-05</v>
       </c>
     </row>
     <row r="8">
@@ -2735,37 +2735,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.394216546293692e-05</v>
+        <v>5.394216546293684e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>8.077541447597431e-05</v>
+        <v>8.077541447597441e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>8.682019306598624e-05</v>
+        <v>8.682019306598618e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>7.363441720493589e-05</v>
+        <v>7.363441720493581e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>5.497641475985414e-05</v>
+        <v>5.497641475985419e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>8.09687346043913e-05</v>
+        <v>8.096873460439119e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>8.127795519012022e-05</v>
+        <v>8.127795519011997e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>8.097039528412807e-05</v>
+        <v>8.0970395284128e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>8.082516149501846e-05</v>
+        <v>8.082516149501841e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>5.3471811731088e-05</v>
+        <v>5.347181173108806e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001089497429527886</v>
+        <v>0.0001089497429527884</v>
       </c>
     </row>
     <row r="9">
@@ -2775,37 +2775,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.724477419194657e-05</v>
+        <v>3.724477419194671e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>4.429224225810981e-05</v>
+        <v>4.429224225810989e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.477721545593748e-05</v>
+        <v>4.47772154559377e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>5.264932283500892e-05</v>
+        <v>5.2649322835009e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>4.449410056610419e-05</v>
+        <v>4.449410056610435e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.449243939463351e-05</v>
+        <v>4.449243939463365e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>4.480165998035281e-05</v>
+        <v>4.480165998035289e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.449410007437031e-05</v>
+        <v>4.449410007437041e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.434359028190908e-05</v>
+        <v>4.434359028190917e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>4.024547010685644e-05</v>
+        <v>4.024547010685648e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>4.443060728463997e-05</v>
+        <v>4.443060728464001e-05</v>
       </c>
     </row>
   </sheetData>
@@ -2891,37 +2891,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.404372222484132e-05</v>
+        <v>1.404372222484141e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.390065539960051e-05</v>
+        <v>1.390065539960046e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.410244338281785e-05</v>
+        <v>1.410244338281761e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.408468021429715e-05</v>
+        <v>1.408468021429731e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.408467789460108e-05</v>
+        <v>1.408467789460113e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.406934975048214e-05</v>
+        <v>1.406934975048219e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.408822720432267e-05</v>
+        <v>1.408822720432263e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.40665500718454e-05</v>
+        <v>1.406655007184547e-05</v>
       </c>
       <c r="J2" t="n">
         <v>1.419035282432942e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.418010309729796e-05</v>
+        <v>1.418010309729809e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.405853973112417e-05</v>
+        <v>1.405853973112414e-05</v>
       </c>
     </row>
     <row r="3">
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.426815234598989e-05</v>
+        <v>1.426815234598979e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.412381444199876e-05</v>
+        <v>1.412381444199874e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.472536299290084e-05</v>
+        <v>1.472536299290094e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.450012023874146e-05</v>
+        <v>1.450012023874114e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4500117919045e-05</v>
+        <v>1.450011791904493e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.449054001184814e-05</v>
+        <v>1.449054001184815e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.465079071822879e-05</v>
+        <v>1.465079071822878e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.447024410554433e-05</v>
+        <v>1.447024410554429e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.469107336929213e-05</v>
+        <v>1.469107336929216e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.455661096737136e-05</v>
+        <v>1.455661096737133e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.444634621865133e-05</v>
+        <v>1.444634621865131e-05</v>
       </c>
     </row>
     <row r="4">
@@ -2971,31 +2971,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.226721980075721e-05</v>
+        <v>1.226721980075719e-05</v>
       </c>
       <c r="C4" t="n">
         <v>1.217813674866554e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.293050229316585e-05</v>
+        <v>1.293050229316584e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.239958734937327e-05</v>
+        <v>1.239958734937325e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.239958734937327e-05</v>
+        <v>1.239958734937324e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.254492430258223e-05</v>
+        <v>1.25449243025822e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.280462261316124e-05</v>
+        <v>1.28046226131612e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.247530612374933e-05</v>
+        <v>1.24753061237493e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.255453159840512e-05</v>
+        <v>1.25545315984051e-05</v>
       </c>
       <c r="K4" t="n">
         <v>1.231708827037593e-05</v>
@@ -3011,37 +3011,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.472562197602545e-05</v>
+        <v>2.47256219760254e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.729194436282927e-05</v>
+        <v>4.729194436282928e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.620890512037713e-05</v>
+        <v>5.620890512037705e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>4.953436500815988e-05</v>
+        <v>4.95343650081599e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.953436500815988e-05</v>
+        <v>4.95343650081599e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>5.029461844205299e-05</v>
+        <v>5.029461844205412e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>5.814741303347314e-05</v>
+        <v>5.814741303347325e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>4.95343462652299e-05</v>
+        <v>4.953434626522986e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>5.122487057771269e-05</v>
+        <v>5.122487057771279e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>4.587808691178112e-05</v>
+        <v>4.587808691178113e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.264854615375818e-05</v>
+        <v>5.264854615375814e-05</v>
       </c>
     </row>
     <row r="6">
@@ -3051,34 +3051,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.351327402539055e-05</v>
+        <v>1.351327402539052e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.354156649853338e-05</v>
+        <v>1.354156649853336e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.731836400305665e-05</v>
+        <v>1.731836400305667e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.367833485085477e-05</v>
+        <v>1.367833485085476e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.37242708125205e-05</v>
+        <v>1.372427081252048e-05</v>
       </c>
       <c r="G6" t="n">
         <v>1.379097852721551e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.738995179543982e-05</v>
+        <v>1.738995179543979e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.676322390631686e-05</v>
+        <v>1.676322390631685e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.690727290236138e-05</v>
+        <v>1.690727290236134e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.355904754527538e-05</v>
+        <v>1.355904754527533e-05</v>
       </c>
       <c r="L6" t="n">
         <v>1.37309885802276e-05</v>
@@ -3091,31 +3091,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.032634187723669e-05</v>
+        <v>2.032634187723666e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>2.037322784061248e-05</v>
+        <v>2.037322784061246e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.098962127593065e-05</v>
+        <v>2.098962127593064e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.053663564789262e-05</v>
+        <v>2.053663564789259e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.053663564789262e-05</v>
+        <v>2.053663564789259e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.06040463790617e-05</v>
+        <v>2.060404637906164e-05</v>
       </c>
       <c r="H7" t="n">
         <v>2.086374468964068e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.05344282002288e-05</v>
+        <v>2.053442820022876e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.061365367488461e-05</v>
+        <v>2.061365367488455e-05</v>
       </c>
       <c r="K7" t="n">
         <v>2.03762103468554e-05</v>
@@ -3137,31 +3137,31 @@
         <v>7.754533471041656e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>8.343867370396451e-05</v>
+        <v>8.343867370396447e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>7.07364387811389e-05</v>
+        <v>7.073643878113908e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>5.302556622754587e-05</v>
+        <v>5.302556622754591e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>7.776903966487113e-05</v>
+        <v>7.776903966487104e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>7.802873797548203e-05</v>
+        <v>7.802873797548205e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>7.769942148603835e-05</v>
+        <v>7.769942148603819e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>7.778365509528852e-05</v>
+        <v>7.778365509528848e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>5.158489298620245e-05</v>
+        <v>5.158489298620243e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001043254453767196</v>
+        <v>0.0001043254453767194</v>
       </c>
     </row>
     <row r="9">
@@ -3171,37 +3171,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.485316130727044e-05</v>
+        <v>3.485316130727043e-05</v>
       </c>
       <c r="C9" t="n">
         <v>4.12472284260963e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.186362542261559e-05</v>
+        <v>4.186362542261553e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>4.87329588049815e-05</v>
+        <v>4.873295880498152e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>4.140844623450948e-05</v>
+        <v>4.140844623450936e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.147804696454557e-05</v>
+        <v>4.147804696454545e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>4.173774527512454e-05</v>
+        <v>4.173774527512456e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.140842878571269e-05</v>
+        <v>4.140842878571261e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.148765426036841e-05</v>
+        <v>4.148765426036844e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>3.757262944019003e-05</v>
+        <v>3.757262944019001e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>4.141537873558752e-05</v>
+        <v>4.141537873558757e-05</v>
       </c>
     </row>
   </sheetData>
@@ -3287,37 +3287,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.41080874132815e-05</v>
+        <v>1.410808741328125e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.401668272987898e-05</v>
+        <v>1.401668272987891e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.416457843966561e-05</v>
+        <v>1.416457843966549e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.419791972628827e-05</v>
+        <v>1.419791972628849e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.419791905960949e-05</v>
+        <v>1.41979190596094e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.413553047228757e-05</v>
+        <v>1.413553047228755e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.415051116844051e-05</v>
+        <v>1.415051116844048e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.412836997302023e-05</v>
+        <v>1.412836997302007e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.440841303870639e-05</v>
+        <v>1.440841303870622e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.42847910072011e-05</v>
+        <v>1.428479100720101e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.412675810662197e-05</v>
+        <v>1.412675810662194e-05</v>
       </c>
     </row>
     <row r="3">
@@ -3327,37 +3327,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.431597310275427e-05</v>
+        <v>1.431597310275401e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.42904515747993e-05</v>
+        <v>1.429045157479927e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.475725850979835e-05</v>
+        <v>1.475725850979796e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.46146420511314e-05</v>
+        <v>1.461464205113128e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.461464138445263e-05</v>
+        <v>1.461464138445294e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.455131535149585e-05</v>
+        <v>1.455131535149581e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.468471064667325e-05</v>
+        <v>1.468471064667321e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.449990208288113e-05</v>
+        <v>1.449990208288103e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.511149937629058e-05</v>
+        <v>1.511149937629032e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.466410266439559e-05</v>
+        <v>1.466410266439597e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.452226038467364e-05</v>
+        <v>1.452226038467361e-05</v>
       </c>
     </row>
     <row r="4">
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.249486095563659e-05</v>
+        <v>1.249486095563657e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.246515278826021e-05</v>
+        <v>1.246515278826013e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.313295308580126e-05</v>
+        <v>1.313295308580122e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.260504762787378e-05</v>
+        <v>1.260504762787376e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.260504762787378e-05</v>
+        <v>1.260504762787376e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.279301148032968e-05</v>
+        <v>1.279301148032881e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.301031359042515e-05</v>
+        <v>1.301031359042513e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.267384402711465e-05</v>
+        <v>1.267384402711476e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.302672887972985e-05</v>
+        <v>1.302672887972976e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.253058426099737e-05</v>
+        <v>1.253058426099732e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.275385273650343e-05</v>
+        <v>1.275385273650337e-05</v>
       </c>
     </row>
     <row r="5">
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.573438992365215e-05</v>
+        <v>2.573438992365202e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.949985552181978e-05</v>
+        <v>4.949985552181973e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.676764200400728e-05</v>
+        <v>5.676764200400724e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>5.003588409677516e-05</v>
+        <v>5.003588409677499e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>5.003588409677516e-05</v>
+        <v>5.003588409677495e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>5.166449155487821e-05</v>
+        <v>5.166449155487677e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>5.882307813272316e-05</v>
+        <v>5.882307813272313e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>5.003585374489399e-05</v>
+        <v>5.003585374489383e-05</v>
       </c>
       <c r="J5" t="n">
         <v>5.662071606693105e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>4.662704337566347e-05</v>
+        <v>4.662704337566339e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.462042674247719e-05</v>
+        <v>5.462042674247708e-05</v>
       </c>
     </row>
     <row r="6">
@@ -3447,37 +3447,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.690031583922191e-05</v>
+        <v>1.690031583922186e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.387001615652144e-05</v>
+        <v>1.387001615652141e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.442090526838223e-05</v>
+        <v>1.442090526838218e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.390227640358041e-05</v>
+        <v>1.390227640358039e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.395664658465227e-05</v>
+        <v>1.395664658465224e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.719846636391398e-05</v>
+        <v>1.719846636391407e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.429490609096801e-05</v>
+        <v>1.429490609096798e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.707929891070003e-05</v>
+        <v>1.707929891069999e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.439779855578526e-05</v>
+        <v>1.439779855578527e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.380482554424126e-05</v>
+        <v>1.380482554424127e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.403644142448e-05</v>
+        <v>1.403644142447998e-05</v>
       </c>
     </row>
     <row r="7">
@@ -3487,37 +3487,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.061362949889839e-05</v>
+        <v>2.061362949889832e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>2.072912399796026e-05</v>
+        <v>2.07291239979602e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.125171790305995e-05</v>
+        <v>2.125171790305988e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.079780911181715e-05</v>
+        <v>2.079780911181711e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.079780911181715e-05</v>
+        <v>2.079780911181711e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.091178002359053e-05</v>
+        <v>2.091178002359039e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.112908213368692e-05</v>
+        <v>2.112908213368686e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.079261257037654e-05</v>
+        <v>2.079261257037652e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.114549742299155e-05</v>
+        <v>2.11454974229915e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>2.064935280425914e-05</v>
+        <v>2.064935280425905e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>2.087262127976513e-05</v>
+        <v>2.087262127976512e-05</v>
       </c>
     </row>
     <row r="8">
@@ -3527,37 +3527,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.239411463969785e-05</v>
+        <v>5.239411463969783e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>7.814210495352661e-05</v>
+        <v>7.81421049535265e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>8.39677040075608e-05</v>
+        <v>8.396770400756079e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>7.11970345682887e-05</v>
+        <v>7.119703456828861e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>5.338840598246289e-05</v>
+        <v>5.338840598246287e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>7.831476926206484e-05</v>
+        <v>7.83147692620648e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>7.853207137220997e-05</v>
+        <v>7.853207137220986e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>7.819560180885082e-05</v>
+        <v>7.819560180885075e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>7.855352222144316e-05</v>
+        <v>7.8553522221443e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>5.195388677647857e-05</v>
+        <v>5.19538867764784e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001050404585708853</v>
+        <v>0.0001050404585708852</v>
       </c>
     </row>
     <row r="9">
@@ -3567,37 +3567,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.406408575422951e-05</v>
+        <v>3.406408575422955e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>4.026260320895454e-05</v>
+        <v>4.026260320895453e-05</v>
       </c>
       <c r="D9" t="n">
         <v>4.078520139487634e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>4.734580052582591e-05</v>
+        <v>4.734580052582593e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>4.032612083814564e-05</v>
+        <v>4.032612083814566e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.044525923458482e-05</v>
+        <v>4.044525923458487e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>4.066256134468128e-05</v>
+        <v>4.066256134468117e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.032609178137082e-05</v>
+        <v>4.032609178137077e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.067897663398577e-05</v>
+        <v>4.067897663398575e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>3.665830485822178e-05</v>
+        <v>3.665830485822174e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>4.040610049075945e-05</v>
+        <v>4.040610049075938e-05</v>
       </c>
     </row>
   </sheetData>
@@ -3683,37 +3683,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.403147758799296e-05</v>
+        <v>1.403147758799297e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.389393735809818e-05</v>
+        <v>1.389393735809823e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.408656970206036e-05</v>
+        <v>1.408656970206012e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.403238753865743e-05</v>
+        <v>1.403238753865741e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.403238472605402e-05</v>
+        <v>1.403238472605381e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.405285861532008e-05</v>
+        <v>1.405285861532006e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.40726183897753e-05</v>
+        <v>1.407261838977533e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.405363878953685e-05</v>
+        <v>1.405363878953648e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.411109352264016e-05</v>
+        <v>1.411109352264004e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.414056619718997e-05</v>
+        <v>1.414056619719002e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.40373256109756e-05</v>
+        <v>1.403732561097551e-05</v>
       </c>
     </row>
     <row r="3">
@@ -3723,37 +3723,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.422420420710207e-05</v>
+        <v>1.42242042071022e-05</v>
       </c>
       <c r="C3" t="n">
         <v>1.406664240749473e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.465565784136075e-05</v>
+        <v>1.465565784136024e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.438648230028262e-05</v>
+        <v>1.438648230028233e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.438647948767923e-05</v>
+        <v>1.4386479487679e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.441630468877186e-05</v>
+        <v>1.441630468877189e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.458191740694923e-05</v>
+        <v>1.458191740694919e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.442160497706048e-05</v>
+        <v>1.442160497706069e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.447386580976694e-05</v>
+        <v>1.447386580976676e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.44646754401165e-05</v>
+        <v>1.446467544011666e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.433768337915171e-05</v>
+        <v>1.433768337915166e-05</v>
       </c>
     </row>
     <row r="4">
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.211105199057131e-05</v>
+        <v>1.211105199057126e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.197737531434634e-05</v>
+        <v>1.197737531434632e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2733342762586e-05</v>
+        <v>1.273334276258595e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.223351462974717e-05</v>
+        <v>1.223351462974718e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.223351462974717e-05</v>
+        <v>1.223351462974719e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.234084226181072e-05</v>
+        <v>1.234084226181068e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.260952360578294e-05</v>
+        <v>1.260952360578287e-05</v>
       </c>
       <c r="I4" t="n">
         <v>1.23119162447366e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.226961960598521e-05</v>
+        <v>1.226961960598523e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.215470102833994e-05</v>
+        <v>1.215470102833996e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.222481580853996e-05</v>
+        <v>1.222481580854005e-05</v>
       </c>
     </row>
     <row r="5">
@@ -3803,37 +3803,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.363842533183564e-05</v>
+        <v>2.363842533183567e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.662612076748181e-05</v>
+        <v>4.662612076748185e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.615595939135834e-05</v>
+        <v>5.615595939135825e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>4.971583395316511e-05</v>
+        <v>4.971583395316487e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.971583395316512e-05</v>
+        <v>4.971583395316487e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>4.973605003743406e-05</v>
+        <v>4.97360500374342e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>5.794564382530863e-05</v>
+        <v>5.794564382530903e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>4.971582497593312e-05</v>
+        <v>4.971582497593311e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>4.914433164163337e-05</v>
+        <v>4.914433164163344e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>4.589812974166662e-05</v>
+        <v>4.589812974166651e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.082623213957948e-05</v>
+        <v>5.082623213957941e-05</v>
       </c>
     </row>
     <row r="6">
@@ -3843,22 +3843,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.34101774489875e-05</v>
+        <v>1.341017744898749e-05</v>
       </c>
       <c r="C6" t="n">
         <v>1.339453624983245e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.404786476999956e-05</v>
+        <v>1.404786476999953e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.356942606075026e-05</v>
+        <v>1.356942606075027e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.36141026507011e-05</v>
+        <v>1.361410265070109e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.36399677202269e-05</v>
+        <v>1.363996772022693e-05</v>
       </c>
       <c r="H6" t="n">
         <v>1.729229771510228e-05</v>
@@ -3867,13 +3867,13 @@
         <v>1.361104170315283e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.36555686441194e-05</v>
+        <v>1.365556864411932e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.345239116991431e-05</v>
+        <v>1.345239116991434e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.352636175590472e-05</v>
+        <v>1.352636175590477e-05</v>
       </c>
     </row>
     <row r="7">
@@ -3883,37 +3883,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.060128060316742e-05</v>
+        <v>2.060128060316744e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>2.060257369408766e-05</v>
+        <v>2.06025736940877e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.122356622168287e-05</v>
+        <v>2.122356622168289e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.080405213394794e-05</v>
+        <v>2.080405213394801e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.080405213394794e-05</v>
+        <v>2.080405213394801e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.083107087440691e-05</v>
+        <v>2.083107087440685e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.109975221837907e-05</v>
+        <v>2.109975221837902e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.080214485733272e-05</v>
+        <v>2.080214485733278e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.075984821858147e-05</v>
+        <v>2.075984821858142e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>2.064492964093608e-05</v>
+        <v>2.064492964093613e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>2.071504442113622e-05</v>
+        <v>2.071504442113624e-05</v>
       </c>
     </row>
     <row r="8">
@@ -3923,37 +3923,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.398802168569892e-05</v>
+        <v>5.398802168569907e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>8.08388841000177e-05</v>
+        <v>8.083888410001783e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>8.701873778049636e-05</v>
+        <v>8.701873778049655e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>7.369653673042582e-05</v>
+        <v>7.369653673042597e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>5.504089511825654e-05</v>
+        <v>5.504089511825673e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>8.106027724041578e-05</v>
+        <v>8.106027724041601e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>8.132895858439753e-05</v>
+        <v>8.132895858439765e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>8.103135122334171e-05</v>
+        <v>8.103135122334186e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>8.099432990292281e-05</v>
+        <v>8.099432990292271e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>5.353305814947783e-05</v>
+        <v>5.353305814947786e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001089834503106694</v>
+        <v>0.0001089834503106696</v>
       </c>
     </row>
     <row r="9">
@@ -3963,37 +3963,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.733200472206803e-05</v>
+        <v>3.733200472206805e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>4.441026984135149e-05</v>
+        <v>4.441026984135154e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.503126794598029e-05</v>
+        <v>4.503126794598035e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>5.277652433821626e-05</v>
+        <v>5.277652433821633e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>4.46098486288994e-05</v>
+        <v>4.460984862889944e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.463876702167073e-05</v>
+        <v>4.463876702167069e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>4.490744836564291e-05</v>
+        <v>4.490744836564285e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.460984100459658e-05</v>
+        <v>4.460984100459664e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.456754436584527e-05</v>
+        <v>4.456754436584522e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>4.035220057968887e-05</v>
+        <v>4.035220057968888e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>4.452274056840003e-05</v>
+        <v>4.452274056840007e-05</v>
       </c>
     </row>
   </sheetData>
@@ -4079,37 +4079,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.416856107440696e-05</v>
+        <v>1.416856107440572e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.406869447577936e-05</v>
+        <v>1.406869447577935e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.422544320770412e-05</v>
+        <v>1.422544320770271e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.422189077627245e-05</v>
+        <v>1.422189077627194e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.422188832545958e-05</v>
+        <v>1.422188832545931e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.419447222686213e-05</v>
+        <v>1.419447222686087e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.421296498870213e-05</v>
+        <v>1.421296498870216e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.418974724666206e-05</v>
+        <v>1.418974724666081e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.429662118013509e-05</v>
+        <v>1.429662118013461e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.437532560426451e-05</v>
+        <v>1.437532560426403e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.418383303637869e-05</v>
+        <v>1.418383303637868e-05</v>
       </c>
     </row>
     <row r="3">
@@ -4119,37 +4119,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.434480708210294e-05</v>
+        <v>1.434480708210256e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.427719922661558e-05</v>
+        <v>1.427719922661557e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.478889355260657e-05</v>
+        <v>1.478889355260622e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.45881900475637e-05</v>
+        <v>1.4588190047564e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.458818759675079e-05</v>
+        <v>1.458818759675112e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.456921597381888e-05</v>
+        <v>1.456921597381855e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.472688138409739e-05</v>
+        <v>1.472688138409738e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.453518273214042e-05</v>
+        <v>1.45351827321401e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.484543162088313e-05</v>
+        <v>1.484543162088308e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.474472761682136e-05</v>
+        <v>1.474472761682135e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.452639376861433e-05</v>
+        <v>1.452639376861432e-05</v>
       </c>
     </row>
     <row r="4">
@@ -4159,37 +4159,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.228661843398269e-05</v>
+        <v>1.22866184339827e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.220907581277982e-05</v>
+        <v>1.220907581277983e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.292912829664845e-05</v>
+        <v>1.292912829664848e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.240447740856417e-05</v>
+        <v>1.240447740856416e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.240447740856417e-05</v>
+        <v>1.240447740856416e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.256743770093656e-05</v>
+        <v>1.256743770093653e-05</v>
       </c>
       <c r="H4" t="n">
         <v>1.282302135581588e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.247556185050785e-05</v>
+        <v>1.247556185050788e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.27968385012538e-05</v>
+        <v>1.279683850125375e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.232679459217736e-05</v>
+        <v>1.232679459217723e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.250684196150021e-05</v>
+        <v>1.250684196150016e-05</v>
       </c>
     </row>
     <row r="5">
@@ -4202,34 +4202,34 @@
         <v>2.518875779697165e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.794807225479044e-05</v>
+        <v>4.794807225479027e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.630517876134283e-05</v>
+        <v>5.630517876134281e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>4.966924860359429e-05</v>
+        <v>4.966924860359415e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.966924860359429e-05</v>
+        <v>4.966924860359415e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>5.081275627070956e-05</v>
+        <v>5.081275627070906e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>5.863445453685823e-05</v>
+        <v>5.863445453685809e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>4.966922428810622e-05</v>
+        <v>4.966922428810609e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>5.567599393550783e-05</v>
+        <v>5.567599393550755e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>4.616383665676966e-05</v>
+        <v>4.616383665676963e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.326562379996521e-05</v>
+        <v>5.326562379996504e-05</v>
       </c>
     </row>
     <row r="6">
@@ -4239,37 +4239,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.65784798041415e-05</v>
+        <v>1.657847980414151e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.357916199251001e-05</v>
+        <v>1.357916199250997e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.419470898620477e-05</v>
+        <v>1.41947089862047e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.368531589721021e-05</v>
+        <v>1.368531589721026e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.37315115275025e-05</v>
+        <v>1.373151152750251e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.382032611738053e-05</v>
+        <v>1.382032611738049e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.74121768595667e-05</v>
+        <v>1.741217685956675e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.676742322066665e-05</v>
+        <v>1.676742322066671e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.413540398486312e-05</v>
+        <v>1.413540398486308e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.35759406786378e-05</v>
+        <v>1.357594067863772e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.37625636431202e-05</v>
+        <v>1.376256364312012e-05</v>
       </c>
     </row>
     <row r="7">
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.034022294261082e-05</v>
+        <v>2.034022294261069e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>2.039826139749736e-05</v>
+        <v>2.039826139749735e-05</v>
       </c>
       <c r="D7" t="n">
         <v>2.098273020018544e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.053277087016693e-05</v>
+        <v>2.053277087016685e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.053277087016693e-05</v>
+        <v>2.053277087016685e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.062104220956467e-05</v>
+        <v>2.062104220956457e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.087662586444397e-05</v>
+        <v>2.087662586444387e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.052916635913599e-05</v>
+        <v>2.0529166359136e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.085044300988193e-05</v>
+        <v>2.08504430098819e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>2.038039910080547e-05</v>
+        <v>2.03803991008054e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>2.056044647012833e-05</v>
+        <v>2.056044647012828e-05</v>
       </c>
     </row>
     <row r="8">
@@ -4319,37 +4319,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.201831294652431e-05</v>
+        <v>5.201831294652436e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>7.75581405602782e-05</v>
+        <v>7.755814056027816e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>8.3416235907881e-05</v>
+        <v>8.341623590788093e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>7.072144133955651e-05</v>
+        <v>7.072144133955643e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>5.301688380022309e-05</v>
+        <v>5.301688380022296e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>7.777248058380398e-05</v>
+        <v>7.777248058380383e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>7.80280642387159e-05</v>
+        <v>7.802806423871568e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>7.768060473337542e-05</v>
+        <v>7.768060473337532e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>7.800688763142263e-05</v>
+        <v>7.80068876314225e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>5.158530858030692e-05</v>
+        <v>5.158530858030678e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001043209272681781</v>
+        <v>0.0001043209272681782</v>
       </c>
     </row>
     <row r="9">
@@ -4359,37 +4359,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.488095435166837e-05</v>
+        <v>3.488095435166831e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>4.128693430812904e-05</v>
+        <v>4.128693430812898e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.187140618768212e-05</v>
+        <v>4.187140618768203e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>4.874325228063064e-05</v>
+        <v>4.874325228063057e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>4.141786228460643e-05</v>
+        <v>4.141786228460632e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.150971512019633e-05</v>
+        <v>4.150971512019614e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>4.17652987750757e-05</v>
+        <v>4.176529877507557e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.141783926976763e-05</v>
+        <v>4.141783926976759e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.173911592051358e-05</v>
+        <v>4.173911592051354e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>3.327588043513166e-05</v>
+        <v>3.327588043513152e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>4.144911938076002e-05</v>
+        <v>4.144911938076001e-05</v>
       </c>
     </row>
   </sheetData>
@@ -4475,34 +4475,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.444359624974212e-05</v>
+        <v>1.44435962497421e-05</v>
       </c>
       <c r="C2" t="n">
         <v>1.43626522166187e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.449707084295116e-05</v>
+        <v>1.449707084295114e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.445296248455829e-05</v>
+        <v>1.445296248455828e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.445296100752458e-05</v>
+        <v>1.445296100752457e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.447069658021619e-05</v>
+        <v>1.447069658021621e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.448717812721466e-05</v>
+        <v>1.448717812721467e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.44645636176545e-05</v>
+        <v>1.446456361765447e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.462451770638922e-05</v>
+        <v>1.462451770638921e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.45809173379826e-05</v>
+        <v>1.458091733798259e-05</v>
       </c>
       <c r="L2" t="n">
         <v>1.446162050165742e-05</v>
@@ -4515,34 +4515,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.44467634988624e-05</v>
+        <v>1.444676349886244e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.443449474075198e-05</v>
+        <v>1.443449474075197e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.486657041854455e-05</v>
+        <v>1.486657041854456e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.461635986304047e-05</v>
+        <v>1.461635986304049e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.461635838600678e-05</v>
+        <v>1.461635838600679e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.467965912652267e-05</v>
+        <v>1.467965912652261e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.482353714725448e-05</v>
+        <v>1.48235371472545e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.463557449381881e-05</v>
+        <v>1.463557449381882e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.507167691796232e-05</v>
+        <v>1.507167691796224e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.472984363229004e-05</v>
+        <v>1.472984363229006e-05</v>
       </c>
       <c r="L3" t="n">
         <v>1.46482513261699e-05</v>
@@ -4558,34 +4558,34 @@
         <v>1.244562680315678e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.240802210299193e-05</v>
+        <v>1.240802210299192e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.304964693298115e-05</v>
+        <v>1.304964693298116e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.257422073733715e-05</v>
+        <v>1.257422073733718e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.257422073733714e-05</v>
+        <v>1.257422073733718e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.27396159712993e-05</v>
+        <v>1.273961597129931e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.297372029418227e-05</v>
+        <v>1.297372029418228e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.263039030108175e-05</v>
+        <v>1.263039030108176e-05</v>
       </c>
       <c r="J4" t="n">
         <v>1.303200343319549e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.248125704649977e-05</v>
+        <v>1.248125704649978e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.269708000448805e-05</v>
+        <v>1.269708000448806e-05</v>
       </c>
     </row>
     <row r="5">
@@ -4595,37 +4595,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.558748013281025e-05</v>
+        <v>2.558748013281029e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.920985231723962e-05</v>
+        <v>4.920985231723958e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.604399621610868e-05</v>
+        <v>5.604399621610887e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>5.002098008231519e-05</v>
+        <v>5.00209800823152e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>5.002098008231519e-05</v>
+        <v>5.00209800823152e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>5.144853650874668e-05</v>
+        <v>5.144853650874781e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>5.89048998954827e-05</v>
+        <v>5.890489989548273e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>5.00209515743407e-05</v>
+        <v>5.002095157434066e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>5.744302655353513e-05</v>
+        <v>5.744302655353523e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>4.648046140261786e-05</v>
+        <v>4.648046140261788e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.431056725379807e-05</v>
+        <v>5.431056725379813e-05</v>
       </c>
     </row>
     <row r="6">
@@ -4635,37 +4635,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.681933701992488e-05</v>
+        <v>1.681933701992491e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.380336667701242e-05</v>
+        <v>1.380336667701241e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.432827857577114e-05</v>
+        <v>1.432827857577116e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.385457991652805e-05</v>
+        <v>1.385457991652808e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.390494191208662e-05</v>
+        <v>1.390494191208664e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.401008054021977e-05</v>
+        <v>1.401008054021979e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.773655038138172e-05</v>
+        <v>1.773655038138173e-05</v>
       </c>
       <c r="I6" t="n">
         <v>1.390085487000223e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.748736422728016e-05</v>
+        <v>1.748736422728015e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.374613741421273e-05</v>
+        <v>1.374613741421274e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.397163930960231e-05</v>
+        <v>1.397163930960233e-05</v>
       </c>
     </row>
     <row r="7">
@@ -4675,37 +4675,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.054559485224661e-05</v>
+        <v>2.054559485224663e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>2.065292645574258e-05</v>
+        <v>2.065292645574261e-05</v>
       </c>
       <c r="D7" t="n">
         <v>2.114961183168459e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.073913384733328e-05</v>
+        <v>2.073913384733331e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.073913384733328e-05</v>
+        <v>2.073913384733331e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.083958402038914e-05</v>
+        <v>2.083958402038915e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.107368834327208e-05</v>
+        <v>2.107368834327211e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.073035835017158e-05</v>
+        <v>2.073035835017162e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.113197148228533e-05</v>
+        <v>2.113197148228534e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>2.05812250955896e-05</v>
+        <v>2.058122509558962e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>2.079704805357789e-05</v>
+        <v>2.07970480535779e-05</v>
       </c>
     </row>
     <row r="8">
@@ -4718,34 +4718,34 @@
         <v>5.230531043637238e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>7.800874284444569e-05</v>
+        <v>7.800874284444576e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>8.379676437330025e-05</v>
+        <v>8.379676437330038e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>7.10881407697997e-05</v>
+        <v>7.108814076979978e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>5.330625426099026e-05</v>
+        <v>5.330625426099029e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>7.818199488843612e-05</v>
+        <v>7.818199488843616e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>7.84160992113671e-05</v>
+        <v>7.841609921136712e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>7.80727692182186e-05</v>
+        <v>7.807276921821867e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>7.84794100870076e-05</v>
+        <v>7.847941008700762e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>5.186572898026107e-05</v>
+        <v>5.186572898026106e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001048627233398041</v>
+        <v>0.0001048627233398042</v>
       </c>
     </row>
     <row r="9">
@@ -4755,37 +4755,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.400232647151434e-05</v>
+        <v>3.40023264715144e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>4.018283353101793e-05</v>
+        <v>4.018283353101802e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.067952259414712e-05</v>
+        <v>4.067952259414729e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>4.726860850853339e-05</v>
+        <v>4.726860850853354e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>4.026029264201732e-05</v>
+        <v>4.026029264201743e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.036949109566451e-05</v>
+        <v>4.036949109566452e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>4.060359541854742e-05</v>
+        <v>4.060359541854755e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.02602654254469e-05</v>
+        <v>4.026026542544701e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.066187855756061e-05</v>
+        <v>4.066187855756074e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>3.644954763188232e-05</v>
+        <v>3.644954763188242e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>4.032695512885319e-05</v>
+        <v>4.032695512885333e-05</v>
       </c>
     </row>
   </sheetData>
@@ -4871,19 +4871,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.340809496977704e-05</v>
+        <v>1.340809496977702e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.37000719688475e-05</v>
+        <v>1.370007196884752e-05</v>
       </c>
       <c r="D2" t="n">
         <v>1.342049548433669e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.377773983078341e-05</v>
+        <v>1.377773983078343e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.356720089096345e-05</v>
+        <v>1.356720089096348e-05</v>
       </c>
       <c r="G2" t="n">
         <v>1.341165910173797e-05</v>
@@ -4892,16 +4892,16 @@
         <v>1.341086001557462e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.340786338513155e-05</v>
+        <v>1.340786338513157e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.398185748965487e-05</v>
+        <v>1.398185748965489e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.374683299684121e-05</v>
+        <v>1.374683299684122e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.341348375212394e-05</v>
+        <v>1.341348375212393e-05</v>
       </c>
     </row>
     <row r="3">
@@ -4911,10 +4911,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.346482434893004e-05</v>
+        <v>1.346482434893003e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.395526283060961e-05</v>
+        <v>1.395526283060962e-05</v>
       </c>
       <c r="D3" t="n">
         <v>1.355144970294389e-05</v>
@@ -4926,13 +4926,13 @@
         <v>1.373248973435774e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.348913280688489e-05</v>
+        <v>1.348913280688492e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.350567101409166e-05</v>
+        <v>1.350567101409167e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.34695004821965e-05</v>
+        <v>1.346950048219654e-05</v>
       </c>
       <c r="J3" t="n">
         <v>1.448641778228256e-05</v>
@@ -4941,7 +4941,7 @@
         <v>1.403199892065558e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.353028462808845e-05</v>
+        <v>1.353028462808847e-05</v>
       </c>
     </row>
     <row r="4">
@@ -4951,13 +4951,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.167259465719147e-05</v>
+        <v>1.16725946571914e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.154045326275942e-05</v>
+        <v>1.154045326275944e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.181266417366145e-05</v>
+        <v>1.181266417366148e-05</v>
       </c>
       <c r="E4" t="n">
         <v>1.154893434924221e-05</v>
@@ -4966,22 +4966,22 @@
         <v>1.154893434924221e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.170137905639777e-05</v>
+        <v>1.170137905639767e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.173749695274959e-05</v>
+        <v>1.17374969527496e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.162195969748507e-05</v>
+        <v>1.162195969748511e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.183054544676925e-05</v>
+        <v>1.183054544676929e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.16937369829653e-05</v>
+        <v>1.169373698296533e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.177637373391141e-05</v>
+        <v>1.177637373391145e-05</v>
       </c>
     </row>
     <row r="5">
@@ -4991,34 +4991,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.358690677495288e-05</v>
+        <v>4.358690677495375e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.700931262133352e-05</v>
+        <v>4.700931262133355e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>4.519102038475808e-05</v>
+        <v>4.519102038475827e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>4.700931296290982e-05</v>
+        <v>4.700931296290988e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.700931296290982e-05</v>
+        <v>4.700931296290987e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>4.370878002843272e-05</v>
+        <v>4.370878002843303e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>4.638181143001845e-05</v>
+        <v>4.638181143001804e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>4.700929515293758e-05</v>
+        <v>4.700929515293756e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>4.53356493558505e-05</v>
+        <v>4.533564935585063e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>4.273883322694571e-05</v>
+        <v>4.273883322694607e-05</v>
       </c>
       <c r="L5" t="n">
         <v>4.434047599432954e-05</v>
@@ -5031,37 +5031,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.29887540302997e-05</v>
+        <v>1.29887540302996e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.293367885405009e-05</v>
+        <v>1.293367885405012e-05</v>
       </c>
       <c r="D6" t="n">
         <v>1.313684213266226e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.289680413272748e-05</v>
+        <v>1.289680413272749e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.29397460100933e-05</v>
+        <v>1.293974601009329e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.301753842950582e-05</v>
+        <v>1.301753842950587e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.618178920262179e-05</v>
+        <v>1.618178920262174e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.605225051743379e-05</v>
+        <v>1.605225051743382e-05</v>
       </c>
       <c r="J6" t="n">
         <v>1.323178165959342e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.301488732999545e-05</v>
+        <v>1.301488732999549e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.309522333114446e-05</v>
+        <v>1.309522333114445e-05</v>
       </c>
     </row>
     <row r="7">
@@ -5071,37 +5071,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.018987848283668e-05</v>
+        <v>2.018987848283657e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>2.013926099152625e-05</v>
+        <v>2.013926099152626e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.032991799509244e-05</v>
+        <v>2.032991799509245e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.013905355553481e-05</v>
+        <v>2.013905355553483e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.013905355553481e-05</v>
+        <v>2.013905355553483e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.021866288204292e-05</v>
+        <v>2.021866288204289e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.025478077839481e-05</v>
+        <v>2.025478077839482e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.013924352313029e-05</v>
+        <v>2.01392435231303e-05</v>
       </c>
       <c r="J7" t="n">
         <v>2.034782927241449e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>2.021102080861052e-05</v>
+        <v>2.021102080861054e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>2.029365755955661e-05</v>
+        <v>2.029365755955663e-05</v>
       </c>
     </row>
     <row r="8">
@@ -5111,34 +5111,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.394576822844576e-05</v>
+        <v>5.394576822844585e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>8.0953543812442e-05</v>
+        <v>8.095354381244196e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>8.674873730076447e-05</v>
+        <v>8.674873730076431e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>7.355417711220088e-05</v>
+        <v>7.355417711220067e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>5.475259080307028e-05</v>
+        <v>5.475259080307019e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>8.102778766311348e-05</v>
+        <v>8.102778766311329e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>8.10639055594645e-05</v>
+        <v>8.106390555946447e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>8.094836830420096e-05</v>
+        <v>8.094836830420068e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>8.116227079424877e-05</v>
+        <v>8.116227079424878e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>5.346438282389771e-05</v>
+        <v>5.346438282389762e-05</v>
       </c>
       <c r="L8" t="n">
         <v>0.0001093621484944028</v>
@@ -5151,37 +5151,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.696891657371908e-05</v>
+        <v>3.696891657371923e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>4.399828113752794e-05</v>
+        <v>4.399828113752802e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.418896836378638e-05</v>
+        <v>4.418896836378627e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>5.216842913110641e-05</v>
+        <v>5.216842913110637e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>4.399828010531713e-05</v>
+        <v>4.399828010531718e-05</v>
       </c>
       <c r="G9" t="n">
         <v>4.40776830280446e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>4.411380092439664e-05</v>
+        <v>4.411380092439658e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.399826366913205e-05</v>
+        <v>4.399826366913199e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.420684941841622e-05</v>
+        <v>4.420684941841624e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>3.996787163853142e-05</v>
+        <v>3.996787163853128e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>4.415267770555838e-05</v>
+        <v>4.415267770555833e-05</v>
       </c>
     </row>
   </sheetData>
@@ -5267,37 +5267,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.344329406688571e-05</v>
+        <v>1.344329406688573e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.374566656205533e-05</v>
+        <v>1.374566656205534e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.345234122888572e-05</v>
+        <v>1.345234122888574e-05</v>
       </c>
       <c r="E2" t="n">
         <v>1.382760979700979e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.360495037647834e-05</v>
+        <v>1.360495037647838e-05</v>
       </c>
       <c r="G2" t="n">
         <v>1.344516598125385e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.344629871906959e-05</v>
+        <v>1.34462987190696e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.344097057537432e-05</v>
+        <v>1.344097057537435e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.4049726529718e-05</v>
+        <v>1.404972652971804e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.379818511271987e-05</v>
+        <v>1.379818511271989e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.344629566188551e-05</v>
+        <v>1.344629566188554e-05</v>
       </c>
     </row>
     <row r="3">
@@ -5307,37 +5307,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.353051890729523e-05</v>
+        <v>1.353051890729525e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.403019417905579e-05</v>
+        <v>1.403019417905583e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.359733805098774e-05</v>
+        <v>1.359733805098779e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.416192793265961e-05</v>
+        <v>1.416192793265963e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.379438978364911e-05</v>
+        <v>1.379438978364912e-05</v>
       </c>
       <c r="G3" t="n">
         <v>1.354618486636492e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.357509696844373e-05</v>
+        <v>1.357509696844376e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.352374421712999e-05</v>
+        <v>1.352374421713e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.461944996066752e-05</v>
+        <v>1.461944996066755e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.413391179907228e-05</v>
+        <v>1.413391179907231e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.35810770844702e-05</v>
+        <v>1.358107708447022e-05</v>
       </c>
     </row>
     <row r="4">
@@ -5350,31 +5350,31 @@
         <v>1.177895207722745e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.162898363555495e-05</v>
+        <v>1.162898363555497e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.188114393391759e-05</v>
+        <v>1.188114393391774e-05</v>
       </c>
       <c r="E4" t="n">
         <v>1.163831390670501e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1638313906705e-05</v>
+        <v>1.163831390670501e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.178862132927875e-05</v>
+        <v>1.178862132927882e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.184677490694782e-05</v>
+        <v>1.184677490694784e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.170469443895761e-05</v>
+        <v>1.170469443895759e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.196042199136879e-05</v>
+        <v>1.19604219913688e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.180472027848717e-05</v>
+        <v>1.180472027848716e-05</v>
       </c>
       <c r="L4" t="n">
         <v>1.185621076515339e-05</v>
@@ -5387,37 +5387,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.166759885184889e-05</v>
+        <v>4.16675988518488e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.623826373128247e-05</v>
+        <v>4.623826373128251e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>4.464056828434178e-05</v>
+        <v>4.464056828434399e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>4.623826409012581e-05</v>
+        <v>4.623826409012589e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.623826409012583e-05</v>
+        <v>4.623826409012588e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>4.322512566413424e-05</v>
+        <v>4.322512566413457e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>4.531520220022389e-05</v>
+        <v>4.531520220022374e-05</v>
       </c>
       <c r="I5" t="n">
         <v>4.623824495835164e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>4.47531910403311e-05</v>
+        <v>4.475319104033112e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>4.474777970390278e-05</v>
+        <v>4.47477797039028e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>4.470179056998568e-05</v>
+        <v>4.470179056998563e-05</v>
       </c>
     </row>
     <row r="6">
@@ -5427,37 +5427,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.301015473760229e-05</v>
+        <v>1.301015473760235e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.293068503627033e-05</v>
+        <v>1.293068503627034e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.311855953160823e-05</v>
+        <v>1.311855953160836e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.289613366728721e-05</v>
+        <v>1.289613366728724e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.293724609666414e-05</v>
+        <v>1.293724609666415e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.301982398965367e-05</v>
+        <v>1.301982398965371e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.603486966839064e-05</v>
+        <v>1.603486966839074e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.586509485000602e-05</v>
+        <v>1.586509485000607e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.327148892635924e-05</v>
+        <v>1.327148892635927e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.304031577768085e-05</v>
+        <v>1.30403157776809e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.308955119244874e-05</v>
+        <v>1.308955119244876e-05</v>
       </c>
     </row>
     <row r="7">
@@ -5467,37 +5467,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.972744891198326e-05</v>
+        <v>1.97274489119833e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>1.965321004664426e-05</v>
+        <v>1.965321004664428e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>1.982961010549117e-05</v>
+        <v>1.982961010549134e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>1.965361555148775e-05</v>
+        <v>1.965361555148781e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>1.965361555148775e-05</v>
+        <v>1.965361555148781e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>1.973711816403461e-05</v>
+        <v>1.973711816403469e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>1.979527174170367e-05</v>
+        <v>1.979527174170369e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>1.965319127371339e-05</v>
+        <v>1.965319127371346e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>1.990891882612462e-05</v>
+        <v>1.990891882612465e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>1.975321711324298e-05</v>
+        <v>1.975321711324303e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>1.980470759990923e-05</v>
+        <v>1.980470759990924e-05</v>
       </c>
     </row>
     <row r="8">
@@ -5507,37 +5507,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.12079747089063e-05</v>
+        <v>5.120797470890638e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>7.637837762793336e-05</v>
+        <v>7.637837762793338e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>8.178294171492247e-05</v>
+        <v>8.178294171492266e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>6.947509248721748e-05</v>
+        <v>6.947509248721757e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>5.193404149298753e-05</v>
+        <v>5.193404149298757e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>7.645689581880149e-05</v>
+        <v>7.645689581880156e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>7.651504939646982e-05</v>
+        <v>7.651504939646989e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>7.637296892848029e-05</v>
+        <v>7.637296892848038e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>7.663365672160152e-05</v>
+        <v>7.66336567216016e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>5.076491084868662e-05</v>
+        <v>5.076491084868673e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001028889942962931</v>
+        <v>0.0001028889942962932</v>
       </c>
     </row>
     <row r="9">
@@ -5547,37 +5547,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.40397685585785e-05</v>
+        <v>3.403976855857857e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>4.020304905669242e-05</v>
+        <v>4.020304905669236e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.037948000072946e-05</v>
+        <v>4.037948000072978e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>4.740101308810624e-05</v>
+        <v>4.740101308810628e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>4.020304812212085e-05</v>
+        <v>4.020304812212093e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.02869571740827e-05</v>
+        <v>4.028695717408287e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>4.034511075175175e-05</v>
+        <v>4.034511075175184e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.020303028376148e-05</v>
+        <v>4.020303028376159e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.045875783617273e-05</v>
+        <v>4.045875783617287e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>3.668901300085284e-05</v>
+        <v>3.668901300085294e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>4.03545466099573e-05</v>
+        <v>4.035454660995747e-05</v>
       </c>
     </row>
   </sheetData>
@@ -5663,37 +5663,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.346248400221177e-05</v>
+        <v>1.346248400221196e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.377544803180634e-05</v>
+        <v>1.377544803180635e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.347383087114289e-05</v>
+        <v>1.347383087114315e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.385960722293926e-05</v>
+        <v>1.385960722293946e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.363084109382692e-05</v>
+        <v>1.36308410938269e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.346641644945872e-05</v>
+        <v>1.3466416449459e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.34670853738192e-05</v>
+        <v>1.346708537381922e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.346353266135915e-05</v>
+        <v>1.346353266135939e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.409368557654275e-05</v>
+        <v>1.40936855765428e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.382657878895346e-05</v>
+        <v>1.382657878895338e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.346878161245931e-05</v>
+        <v>1.346878161245932e-05</v>
       </c>
     </row>
     <row r="3">
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.355383247525582e-05</v>
+        <v>1.355383247525581e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.408718019852926e-05</v>
+        <v>1.408718019852928e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.363816116220566e-05</v>
+        <v>1.363816116220579e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.422253525718645e-05</v>
+        <v>1.422253525718644e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.384491675515303e-05</v>
+        <v>1.384491675515306e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.358369140022044e-05</v>
+        <v>1.358369140022054e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.361248967760656e-05</v>
+        <v>1.361248967760655e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.356877912776704e-05</v>
+        <v>1.356877912776685e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.472673826910119e-05</v>
+        <v>1.472673826910095e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.41791669534332e-05</v>
+        <v>1.417916695343321e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.362596647623892e-05</v>
+        <v>1.362596647623893e-05</v>
       </c>
     </row>
     <row r="4">
@@ -5743,37 +5743,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.181772667121064e-05</v>
+        <v>1.181772667121065e-05</v>
       </c>
       <c r="C4" t="n">
         <v>1.17080294094418e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.19458947756054e-05</v>
+        <v>1.194589477560544e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.171792680649411e-05</v>
+        <v>1.17179268064941e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.171792680649411e-05</v>
+        <v>1.17179268064941e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.185068401485317e-05</v>
+        <v>1.185068401485326e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.190395186587263e-05</v>
+        <v>1.190395186587264e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.178165550759422e-05</v>
+        <v>1.178165550759421e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.209481557978154e-05</v>
+        <v>1.209481557978158e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.185516497680729e-05</v>
+        <v>1.18551649768073e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.193225463519431e-05</v>
+        <v>1.193225463519433e-05</v>
       </c>
     </row>
     <row r="5">
@@ -5783,37 +5783,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.354006972922754e-05</v>
+        <v>4.354006972922749e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.756882711606211e-05</v>
+        <v>4.756882711606203e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>4.754066399493532e-05</v>
+        <v>4.754066399493518e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>4.756882742069525e-05</v>
+        <v>4.756882742069515e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.756882742069525e-05</v>
+        <v>4.756882742069515e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>4.524332868734805e-05</v>
+        <v>4.524332868734932e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>4.880044425505231e-05</v>
+        <v>4.880044425505236e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>4.75688117264464e-05</v>
+        <v>4.756881172644628e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>4.657833866451868e-05</v>
+        <v>4.657833866451876e-05</v>
       </c>
       <c r="K5" t="n">
         <v>4.738674779241036e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.000695410972332e-05</v>
+        <v>5.000695410972341e-05</v>
       </c>
     </row>
     <row r="6">
@@ -5826,34 +5826,34 @@
         <v>1.305327844313796e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.301257831490944e-05</v>
+        <v>1.301257831490945e-05</v>
       </c>
       <c r="D6" t="n">
         <v>1.318758745163166e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.297768976629063e-05</v>
+        <v>1.29776897662906e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.301890033371036e-05</v>
+        <v>1.301890033371037e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.602739839948247e-05</v>
+        <v>1.602739839948266e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.611513863666513e-05</v>
+        <v>1.611513863666515e-05</v>
       </c>
       <c r="I6" t="n">
         <v>1.301720727952155e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.628111439431847e-05</v>
+        <v>1.628111439431848e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.309450928687728e-05</v>
+        <v>1.309450928687729e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.317002473621902e-05</v>
+        <v>1.317002473621904e-05</v>
       </c>
     </row>
     <row r="7">
@@ -5863,37 +5863,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.977298462188091e-05</v>
+        <v>1.977298462188089e-05</v>
       </c>
       <c r="C7" t="n">
         <v>1.973692884788018e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>1.990112112593075e-05</v>
+        <v>1.990112112593079e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>1.97381536301952e-05</v>
+        <v>1.973815363019521e-05</v>
       </c>
       <c r="F7" t="n">
         <v>1.973815363019521e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>1.980594196552329e-05</v>
+        <v>1.980594196552353e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>1.985920981654288e-05</v>
+        <v>1.985920981654289e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>1.97369134582645e-05</v>
+        <v>1.973691345826452e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.005007353045179e-05</v>
+        <v>2.00500735304518e-05</v>
       </c>
       <c r="K7" t="n">
         <v>1.981042292747754e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>1.988751258586454e-05</v>
+        <v>1.988751258586459e-05</v>
       </c>
     </row>
     <row r="8">
@@ -5903,37 +5903,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.126407410771133e-05</v>
+        <v>5.12640741077114e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>7.648751980921083e-05</v>
+        <v>7.648751980921091e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>8.188200681941722e-05</v>
+        <v>8.188200681941736e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>6.95803017002526e-05</v>
+        <v>6.958030170025267e-05</v>
       </c>
       <c r="F8" t="n">
         <v>5.20292593076326e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>7.655035492581133e-05</v>
+        <v>7.655035492581136e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>7.660362277683025e-05</v>
+        <v>7.660362277683032e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>7.648132641855229e-05</v>
+        <v>7.648132641855236e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>7.679944949689546e-05</v>
+        <v>7.679944949689562e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>5.083241896432449e-05</v>
+        <v>5.083241896432451e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001030111335679501</v>
+        <v>0.0001030111335679502</v>
       </c>
     </row>
     <row r="9">
@@ -5943,37 +5943,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.302693726732069e-05</v>
+        <v>3.302693726732074e-05</v>
       </c>
       <c r="C9" t="n">
         <v>3.89389073510173e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>3.910313146936366e-05</v>
+        <v>3.910313146936362e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>4.580280198059776e-05</v>
+        <v>4.580280198059778e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>3.893890636507167e-05</v>
+        <v>3.893890636507162e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>3.900792046866056e-05</v>
+        <v>3.900792046866068e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>3.906118831968e-05</v>
+        <v>3.906118831968007e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>3.893889196140166e-05</v>
+        <v>3.893889196140161e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>3.925205203358894e-05</v>
+        <v>3.925205203358893e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>3.556609198988666e-05</v>
+        <v>3.556609198988663e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>3.908949108900168e-05</v>
+        <v>3.908949108900174e-05</v>
       </c>
     </row>
   </sheetData>
@@ -6062,31 +6062,31 @@
         <v>1.34389364931651e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.372553760668575e-05</v>
+        <v>1.372553760668576e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.34460853244988e-05</v>
+        <v>1.344608532449881e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.38039147427897e-05</v>
+        <v>1.380391474278971e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.359144647591967e-05</v>
+        <v>1.359144647591969e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.34326168106716e-05</v>
+        <v>1.343261681067156e-05</v>
       </c>
       <c r="H2" t="n">
         <v>1.342870685752953e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.343012240712042e-05</v>
+        <v>1.34301224071204e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.401107057235374e-05</v>
+        <v>1.401107057235387e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.377500720956788e-05</v>
+        <v>1.377500720956791e-05</v>
       </c>
       <c r="L2" t="n">
         <v>1.343296876909513e-05</v>
@@ -6099,37 +6099,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.356811305023892e-05</v>
+        <v>1.356811305023886e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.400235933089991e-05</v>
+        <v>1.400235933089994e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.362918077664748e-05</v>
+        <v>1.36291807766475e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.412825984918148e-05</v>
+        <v>1.412825984918155e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.377754398372713e-05</v>
+        <v>1.377754398372708e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.352818496297806e-05</v>
+        <v>1.352818496297804e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.352987376133135e-05</v>
+        <v>1.352987376133137e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.351127637988808e-05</v>
+        <v>1.351127637988805e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.454498541330388e-05</v>
+        <v>1.454498541330405e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.408966752188393e-05</v>
+        <v>1.408966752188395e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.355517697481364e-05</v>
+        <v>1.355517697481365e-05</v>
       </c>
     </row>
     <row r="4">
@@ -6139,37 +6139,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.183515064092607e-05</v>
+        <v>1.183515064092601e-05</v>
       </c>
       <c r="C4" t="n">
         <v>1.160843627650613e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.191589997946515e-05</v>
+        <v>1.191589997946517e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.161689604320028e-05</v>
+        <v>1.161689604320029e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.161689604320028e-05</v>
+        <v>1.161689604320029e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.175229232955651e-05</v>
+        <v>1.17522923295565e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.175404009435515e-05</v>
+        <v>1.175404009435514e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.168757269755417e-05</v>
+        <v>1.168757269755414e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.190796784902485e-05</v>
+        <v>1.190796784902486e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.176125178984977e-05</v>
+        <v>1.176125178984975e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.181120381219474e-05</v>
+        <v>1.181120381219473e-05</v>
       </c>
     </row>
     <row r="5">
@@ -6179,37 +6179,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.684133999923919e-05</v>
+        <v>4.684133999923784e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.828666953826425e-05</v>
+        <v>4.828666953826416e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.395533573030958e-05</v>
+        <v>5.395533573030942e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>4.828666981966795e-05</v>
+        <v>4.828666981966786e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.828666981966798e-05</v>
+        <v>4.828666981966786e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>4.835868262424861e-05</v>
+        <v>4.835868262424821e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>5.423914350157632e-05</v>
+        <v>5.423914350157608e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>4.828665538460588e-05</v>
+        <v>4.828665538460581e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660084972751486e-05</v>
+        <v>4.660084972751459e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>4.694676904812411e-05</v>
+        <v>4.694676904812353e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>4.974907265965199e-05</v>
+        <v>4.97490726596519e-05</v>
       </c>
     </row>
     <row r="6">
@@ -6219,37 +6219,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.627669836759641e-05</v>
+        <v>1.627669836759633e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.300533189855036e-05</v>
+        <v>1.300533189855037e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.64043643434065e-05</v>
+        <v>1.640436434340646e-05</v>
       </c>
       <c r="E6" t="n">
         <v>1.296800471292778e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.301091369554281e-05</v>
+        <v>1.301091369554283e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.619384005622691e-05</v>
+        <v>1.619384005622683e-05</v>
       </c>
       <c r="H6" t="n">
         <v>1.307777790076878e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.612912042422447e-05</v>
+        <v>1.612912042422445e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.63613087111453e-05</v>
+        <v>1.636130871114528e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.308825639523327e-05</v>
+        <v>1.308825639523323e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.31352080772005e-05</v>
+        <v>1.313520807720048e-05</v>
       </c>
     </row>
     <row r="7">
@@ -6262,34 +6262,34 @@
         <v>2.035529465341406e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>2.020773086370055e-05</v>
+        <v>2.020773086370056e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.04360133127796e-05</v>
+        <v>2.043601331277961e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.02081555674607e-05</v>
+        <v>2.020815556746069e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.020815556746071e-05</v>
+        <v>2.020815556746069e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.027243634204456e-05</v>
+        <v>2.027243634204454e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.027418410684318e-05</v>
+        <v>2.027418410684319e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.020771671004219e-05</v>
+        <v>2.020771671004218e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.042811186151286e-05</v>
+        <v>2.042811186151292e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>2.028139580233774e-05</v>
+        <v>2.028139580233778e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>2.033134782468278e-05</v>
+        <v>2.033134782468277e-05</v>
       </c>
     </row>
     <row r="8">
@@ -6299,37 +6299,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.41144387922641e-05</v>
+        <v>5.411443879226404e-05</v>
       </c>
       <c r="C8" t="n">
         <v>8.10310382420752e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>8.686432209138969e-05</v>
+        <v>8.686432209138975e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>7.363019465284529e-05</v>
+        <v>7.36301946528452e-05</v>
       </c>
       <c r="F8" t="n">
         <v>5.482485622965093e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>8.108997919805677e-05</v>
+        <v>8.108997919805662e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>8.109172696285433e-05</v>
+        <v>8.109172696285439e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>8.102525956605432e-05</v>
+        <v>8.102525956605426e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>8.12509724730767e-05</v>
+        <v>8.125097247307683e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>5.353791629282984e-05</v>
+        <v>5.35379162928297e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001094136507317642</v>
+        <v>0.0001094136507317643</v>
       </c>
     </row>
     <row r="9">
@@ -6339,37 +6339,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.7154585712087e-05</v>
+        <v>3.715458571208704e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>4.409395249103986e-05</v>
+        <v>4.409395249103987e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.432226587713831e-05</v>
+        <v>4.432226587713826e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>5.227211892804581e-05</v>
+        <v>5.22721189280457e-05</v>
       </c>
       <c r="F9" t="n">
         <v>4.409395142322552e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.415865796938385e-05</v>
+        <v>4.41586579693838e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>4.416040573418253e-05</v>
+        <v>4.416040573418247e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.409393833738152e-05</v>
+        <v>4.40939383373815e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.431433348885227e-05</v>
+        <v>4.431433348885219e-05</v>
       </c>
       <c r="K9" t="n">
         <v>4.006142213411607e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>4.42175694520221e-05</v>
+        <v>4.421756945202201e-05</v>
       </c>
     </row>
   </sheetData>
@@ -6455,34 +6455,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.350449014528646e-05</v>
+        <v>1.350449014528648e-05</v>
       </c>
       <c r="C2" t="n">
         <v>1.38079202442044e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.351768406776994e-05</v>
+        <v>1.351768406776992e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.389096178634386e-05</v>
+        <v>1.389096178634387e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.366545486017042e-05</v>
+        <v>1.36654548601704e-05</v>
       </c>
       <c r="G2" t="n">
         <v>1.350300300008106e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.351735368066333e-05</v>
+        <v>1.351735368066334e-05</v>
       </c>
       <c r="I2" t="n">
         <v>1.349802458592063e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.411123029399486e-05</v>
+        <v>1.411123029399485e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.386267221358542e-05</v>
+        <v>1.386267221358541e-05</v>
       </c>
       <c r="L2" t="n">
         <v>1.350716112999868e-05</v>
@@ -6495,37 +6495,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.368929154739665e-05</v>
+        <v>1.368929154739664e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.416889723684607e-05</v>
+        <v>1.416889723684605e-05</v>
       </c>
       <c r="D3" t="n">
         <v>1.379791833433739e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.43023109324209e-05</v>
+        <v>1.430231093242091e-05</v>
       </c>
       <c r="F3" t="n">
         <v>1.393007211823094e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.368821465898474e-05</v>
+        <v>1.368821465898475e-05</v>
       </c>
       <c r="H3" t="n">
         <v>1.382408649325131e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.365373168635191e-05</v>
+        <v>1.365373168635194e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.474369093031336e-05</v>
+        <v>1.47436909303133e-05</v>
       </c>
       <c r="K3" t="n">
         <v>1.426890428306254e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.37433254267468e-05</v>
+        <v>1.374332542674681e-05</v>
       </c>
     </row>
     <row r="4">
@@ -6538,16 +6538,16 @@
         <v>1.201890326519313e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.182169092584298e-05</v>
+        <v>1.182169092584299e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.216793468914792e-05</v>
+        <v>1.216793468914794e-05</v>
       </c>
       <c r="E4" t="n">
         <v>1.183138679921906e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.183138679921907e-05</v>
+        <v>1.183138679921906e-05</v>
       </c>
       <c r="G4" t="n">
         <v>1.199060944913815e-05</v>
@@ -6556,16 +6556,16 @@
         <v>1.219749700479554e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.189772571615242e-05</v>
+        <v>1.18977257161524e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.211370280570556e-05</v>
+        <v>1.211370280570557e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.198461985873289e-05</v>
+        <v>1.19846198587329e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.20927795806103e-05</v>
+        <v>1.209277958061031e-05</v>
       </c>
     </row>
     <row r="5">
@@ -6575,37 +6575,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.571756448997717e-05</v>
+        <v>4.571756448997731e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.986324777330755e-05</v>
+        <v>4.986324777330757e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>5.584753233118689e-05</v>
+        <v>5.584753233118691e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>4.986324814339112e-05</v>
+        <v>4.986324814339106e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.986324814339112e-05</v>
+        <v>4.986324814339106e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>5.035124671211445e-05</v>
+        <v>5.035124671211447e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>6.177897069471617e-05</v>
+        <v>6.177897069471626e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>4.986322674053457e-05</v>
+        <v>4.986322674053464e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>5.092760841390295e-05</v>
+        <v>5.092760841390291e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>4.771248714026378e-05</v>
+        <v>4.771248714026374e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.571113251835597e-05</v>
+        <v>5.571113251835599e-05</v>
       </c>
     </row>
     <row r="6">
@@ -6615,37 +6615,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.621095913906893e-05</v>
+        <v>1.621095913906892e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.313781992873012e-05</v>
+        <v>1.313781992873006e-05</v>
       </c>
       <c r="D6" t="n">
         <v>1.34223937293985e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.310238892041661e-05</v>
+        <v>1.31023889204166e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.314468816973996e-05</v>
+        <v>1.314468816973994e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.618266532301392e-05</v>
+        <v>1.618266532301388e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.642074931813738e-05</v>
+        <v>1.642074931813741e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.608978159002818e-05</v>
+        <v>1.608978159002816e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.34398630206409e-05</v>
+        <v>1.343986302064089e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.323462180813147e-05</v>
+        <v>1.323462180813148e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.334074009029091e-05</v>
+        <v>1.334074009029093e-05</v>
       </c>
     </row>
     <row r="7">
@@ -6655,37 +6655,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.997932443093548e-05</v>
+        <v>1.997932443093544e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>1.985816791466768e-05</v>
+        <v>1.98581679146677e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.012832497835376e-05</v>
+        <v>2.012832497835377e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>1.985859542002465e-05</v>
+        <v>1.985859542002464e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>1.985859542002465e-05</v>
+        <v>1.985859542002464e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>1.995103061488049e-05</v>
+        <v>1.995103061488044e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.015791817053789e-05</v>
+        <v>2.015791817053785e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>1.985814688189475e-05</v>
+        <v>1.985814688189473e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.007412397144789e-05</v>
+        <v>2.00741239714479e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>1.994504102447522e-05</v>
+        <v>1.994504102447524e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>2.005320074635267e-05</v>
+        <v>2.005320074635266e-05</v>
       </c>
     </row>
     <row r="8">
@@ -6695,37 +6695,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.147008553022394e-05</v>
+        <v>5.1470085530224e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>7.661091643514251e-05</v>
+        <v>7.661091643514271e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>8.21128046372367e-05</v>
+        <v>8.211280463723681e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>6.970289150337766e-05</v>
+        <v>6.970289150337765e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>5.214979696621315e-05</v>
+        <v>5.214979696621323e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>7.669836449875234e-05</v>
+        <v>7.669836449875243e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>7.690525205440945e-05</v>
+        <v>7.690525205440947e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>7.660548076576654e-05</v>
+        <v>7.660548076576662e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>7.682642150005602e-05</v>
+        <v>7.682642150005604e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>5.096664831718081e-05</v>
+        <v>5.096664831718085e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001031831368281427</v>
+        <v>0.0001031831368281428</v>
       </c>
     </row>
     <row r="9">
@@ -6735,37 +6735,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.435189263887485e-05</v>
+        <v>3.43518926388748e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>4.048962587930552e-05</v>
+        <v>4.048962587930548e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.075981406393997e-05</v>
+        <v>4.075981406393987e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>4.771225087287334e-05</v>
+        <v>4.771225087287332e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>4.048962491595939e-05</v>
+        <v>4.048962491595936e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.058248857951836e-05</v>
+        <v>4.058248857951818e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>4.078937613517577e-05</v>
+        <v>4.078937613517566e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.048960484653248e-05</v>
+        <v>4.048960484653251e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.070558193608576e-05</v>
+        <v>4.070558193608562e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>3.695007378632329e-05</v>
+        <v>3.695007378632322e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>4.068465871099053e-05</v>
+        <v>4.068465871099044e-05</v>
       </c>
     </row>
   </sheetData>
@@ -6851,34 +6851,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.354456429338381e-05</v>
+        <v>1.354456429338385e-05</v>
       </c>
       <c r="C2" t="n">
         <v>1.385885927889388e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.35972285892425e-05</v>
+        <v>1.359722858924255e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.394574298114687e-05</v>
+        <v>1.394574298114692e-05</v>
       </c>
       <c r="F2" t="n">
         <v>1.371008803588781e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.35463454540735e-05</v>
+        <v>1.354634545407349e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.356428401557195e-05</v>
+        <v>1.356428401557191e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.353913805844664e-05</v>
+        <v>1.353913805844665e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.423152484528236e-05</v>
+        <v>1.423152484528238e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.390350049525481e-05</v>
+        <v>1.390350049525491e-05</v>
       </c>
       <c r="L2" t="n">
         <v>1.354689423442057e-05</v>
@@ -6891,37 +6891,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.378713712291793e-05</v>
+        <v>1.378713712291795e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.428617563087724e-05</v>
+        <v>1.428617563087725e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.416802068214501e-05</v>
+        <v>1.416802068214502e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.442580708704496e-05</v>
+        <v>1.442580708704502e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.403681706086922e-05</v>
+        <v>1.403681706086925e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.38050276610225e-05</v>
+        <v>1.380502766102249e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.395983228450703e-05</v>
+        <v>1.395983228450707e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.375466868365273e-05</v>
+        <v>1.375466868365276e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.525776304229822e-05</v>
+        <v>1.525776304229827e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.434165022757549e-05</v>
+        <v>1.434165022757556e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.383626111080694e-05</v>
+        <v>1.383626111080696e-05</v>
       </c>
     </row>
     <row r="4">
@@ -6934,31 +6934,31 @@
         <v>1.216184031534619e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.19743407474552e-05</v>
+        <v>1.197434074745521e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.275670776384301e-05</v>
+        <v>1.275670776384303e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.198490825997571e-05</v>
+        <v>1.198490825997568e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.198490825997571e-05</v>
+        <v>1.198490825997568e-05</v>
       </c>
       <c r="G4" t="n">
         <v>1.217044093513221e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.241819657668815e-05</v>
+        <v>1.241819657668816e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.205226104456983e-05</v>
+        <v>1.205226104456986e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.28490565832461e-05</v>
+        <v>1.284905658324612e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.207190281540013e-05</v>
+        <v>1.207190281540015e-05</v>
       </c>
       <c r="L4" t="n">
         <v>1.223297675399751e-05</v>
@@ -6971,37 +6971,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.798632465144233e-05</v>
+        <v>4.79863246514424e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>5.009751823353501e-05</v>
+        <v>5.009751823353507e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>6.110687654825368e-05</v>
+        <v>6.110687654825354e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>5.00975186583549e-05</v>
+        <v>5.009751865835498e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>5.00975186583549e-05</v>
+        <v>5.009751865835498e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>5.101417015844216e-05</v>
+        <v>5.101417015844301e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>5.961591135102159e-05</v>
+        <v>5.961591135102169e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>5.009749111743623e-05</v>
+        <v>5.009749111743642e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>6.163387244100847e-05</v>
+        <v>6.163387244100877e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>4.935320479113144e-05</v>
+        <v>4.935320479113157e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.434060621073016e-05</v>
+        <v>5.434060621073003e-05</v>
       </c>
     </row>
     <row r="6">
@@ -7011,37 +7011,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.342136611960255e-05</v>
+        <v>1.342136611960256e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.330544021252435e-05</v>
+        <v>1.330544021252438e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.403834191655436e-05</v>
+        <v>1.403834191655435e-05</v>
       </c>
       <c r="E6" t="n">
         <v>1.326910297537549e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.331318703065079e-05</v>
+        <v>1.331318703065083e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.342996673938861e-05</v>
+        <v>1.342996673938859e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.668106239240841e-05</v>
+        <v>1.668106239240844e-05</v>
       </c>
       <c r="I6" t="n">
         <v>1.331178684882619e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.419342764466885e-05</v>
+        <v>1.419342764466886e-05</v>
       </c>
       <c r="K6" t="n">
         <v>1.333327883319014e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.349489489629688e-05</v>
+        <v>1.349489489629687e-05</v>
       </c>
     </row>
     <row r="7">
@@ -7051,37 +7051,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.013630795880162e-05</v>
+        <v>2.013630795880163e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>2.002675580412411e-05</v>
+        <v>2.002675580412412e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.073114420550095e-05</v>
+        <v>2.073114420550093e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.002704544366042e-05</v>
+        <v>2.002704544366043e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.002704544366042e-05</v>
+        <v>2.002704544366043e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.014490857858768e-05</v>
+        <v>2.014490857858771e-05</v>
       </c>
       <c r="H7" t="n">
         <v>2.03926642201436e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.002672868802529e-05</v>
+        <v>2.002672868802531e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.082352422670153e-05</v>
+        <v>2.082352422670155e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>2.004637045885557e-05</v>
+        <v>2.004637045885562e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>2.020744439745293e-05</v>
+        <v>2.020744439745295e-05</v>
       </c>
     </row>
     <row r="8">
@@ -7091,34 +7091,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.164387378103595e-05</v>
+        <v>5.164387378103611e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>7.682011319377171e-05</v>
+        <v>7.682011319377182e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>8.276132143260688e-05</v>
+        <v>8.276132143260674e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>6.990555641570373e-05</v>
+        <v>6.990555641570376e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>5.233586610770585e-05</v>
+        <v>5.233586610770589e-05</v>
       </c>
       <c r="G8" t="n">
         <v>7.693297758183149e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>7.718073322338772e-05</v>
+        <v>7.718073322338763e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>7.681479769126915e-05</v>
+        <v>7.68147976912691e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>7.761656157766239e-05</v>
+        <v>7.761656157766254e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>5.108433795510593e-05</v>
+        <v>5.1084337955106e-05</v>
       </c>
       <c r="L8" t="n">
         <v>0.0001034031128986903</v>
@@ -7131,37 +7131,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.347806137451573e-05</v>
+        <v>3.34780613745158e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>3.934809024467653e-05</v>
+        <v>3.934809024467658e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.005251011890134e-05</v>
+        <v>4.005251011890133e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>4.624839892632032e-05</v>
+        <v>4.624839892632033e-05</v>
       </c>
       <c r="F9" t="n">
         <v>3.934808930688551e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>3.946624301914011e-05</v>
+        <v>3.946624301914022e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>3.971399866069603e-05</v>
+        <v>3.971399866069607e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>3.934806312857772e-05</v>
+        <v>3.934806312857781e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.0144858667254e-05</v>
+        <v>4.014485866725406e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>3.576254937415241e-05</v>
+        <v>3.576254937415243e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>3.95287788380054e-05</v>
+        <v>3.952877883800546e-05</v>
       </c>
     </row>
   </sheetData>
@@ -7247,37 +7247,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.341258106764223e-05</v>
+        <v>1.341258106764228e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.370143060846467e-05</v>
+        <v>1.370143060846475e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.342251804266879e-05</v>
+        <v>1.34225180426689e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.377908062404276e-05</v>
+        <v>1.377908062404269e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.356862460606136e-05</v>
+        <v>1.356862460606129e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.341132665965607e-05</v>
+        <v>1.341132665965614e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.341127180908885e-05</v>
+        <v>1.341127180908889e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.340887094210853e-05</v>
+        <v>1.340887094210862e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.398272558435653e-05</v>
+        <v>1.398272558435637e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.374162229292382e-05</v>
+        <v>1.374162229292385e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.341395393638197e-05</v>
+        <v>1.341395393638198e-05</v>
       </c>
     </row>
     <row r="3">
@@ -7287,37 +7287,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.348803323161743e-05</v>
+        <v>1.348803323161747e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.395417632193159e-05</v>
+        <v>1.395417632193163e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.35626048278416e-05</v>
+        <v>1.356260482784171e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.407892021205907e-05</v>
+        <v>1.407892021205918e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.37315260654947e-05</v>
+        <v>1.373152606549493e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.348091828921763e-05</v>
+        <v>1.348091828921784e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.351035614358085e-05</v>
+        <v>1.351035614358102e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.346785015749652e-05</v>
+        <v>1.34678501574965e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.448190179822058e-05</v>
+        <v>1.448190179822035e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.399756173448356e-05</v>
+        <v>1.399756173448328e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.352445207058332e-05</v>
+        <v>1.352445207058336e-05</v>
       </c>
     </row>
     <row r="4">
@@ -7330,34 +7330,34 @@
         <v>1.171165935613759e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.154155010869259e-05</v>
+        <v>1.154155010869261e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.182390206029754e-05</v>
+        <v>1.182390206029757e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.154995607673572e-05</v>
+        <v>1.154995607673573e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.15499560767357e-05</v>
+        <v>1.154995607673573e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.168602198532032e-05</v>
+        <v>1.168602198532039e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.173042444662753e-05</v>
+        <v>1.17304244466278e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.162177305124714e-05</v>
+        <v>1.162177305124708e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.182595501332133e-05</v>
+        <v>1.182595501332132e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.164319595306337e-05</v>
+        <v>1.164319595306332e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.176996960384439e-05</v>
+        <v>1.176996960384441e-05</v>
       </c>
     </row>
     <row r="5">
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.464814139884309e-05</v>
+        <v>4.464814139884315e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.730948073675125e-05</v>
+        <v>4.730948073674987e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>4.880087759365758e-05</v>
+        <v>4.880087759365841e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>4.730948104770646e-05</v>
+        <v>4.730948104770606e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.730948104770646e-05</v>
+        <v>4.730948104770605e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>4.539087812015523e-05</v>
+        <v>4.539087812015744e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>5.247581241222421e-05</v>
+        <v>5.247581241222829e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>4.730946675673818e-05</v>
+        <v>4.730946675673792e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>4.526625898246877e-05</v>
+        <v>4.526625898246827e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>4.315308163081903e-05</v>
+        <v>4.315308163081915e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>4.537205260771136e-05</v>
+        <v>4.537205260771538e-05</v>
       </c>
     </row>
     <row r="6">
@@ -7410,34 +7410,34 @@
         <v>1.302764290735075e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.293396625515328e-05</v>
+        <v>1.293396625515337e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.314874018783065e-05</v>
+        <v>1.314874018783077e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.289703975068991e-05</v>
+        <v>1.289703975068995e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.293949257877045e-05</v>
+        <v>1.293949257877044e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.611507579717371e-05</v>
+        <v>1.611507579717378e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.617396069139492e-05</v>
+        <v>1.617396069139508e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.605082686310028e-05</v>
+        <v>1.605082686310048e-05</v>
       </c>
       <c r="J6" t="n">
         <v>1.626733762188827e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.296290090344518e-05</v>
+        <v>1.296290090344519e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.308860463129555e-05</v>
+        <v>1.308860463129559e-05</v>
       </c>
     </row>
     <row r="7">
@@ -7447,37 +7447,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.022697416833657e-05</v>
+        <v>2.022697416833666e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>2.013710184345956e-05</v>
+        <v>2.013710184345957e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.033918660085999e-05</v>
+        <v>2.033918660086012e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.013719899449477e-05</v>
+        <v>2.013719899449487e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.013719899449477e-05</v>
+        <v>2.013719899449487e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.020133679751943e-05</v>
+        <v>2.020133679751945e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.024573925882672e-05</v>
+        <v>2.024573925882691e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.013708786344613e-05</v>
+        <v>2.013708786344614e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.034126982552024e-05</v>
+        <v>2.034126982552039e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>2.015851076526236e-05</v>
+        <v>2.015851076526245e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>2.028528441604338e-05</v>
+        <v>2.028528441604349e-05</v>
       </c>
     </row>
     <row r="8">
@@ -7487,37 +7487,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.398173369330096e-05</v>
+        <v>5.398173369330106e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>8.094836698359381e-05</v>
+        <v>8.094836698359373e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>8.675424549034579e-05</v>
+        <v>8.675424549034568e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>7.354956509544977e-05</v>
+        <v>7.354956509545e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>5.474941422118035e-05</v>
+        <v>5.47494142211805e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>8.100715266181675e-05</v>
+        <v>8.100715266181683e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>8.105155512312312e-05</v>
+        <v>8.105155512312345e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>8.094290372774365e-05</v>
+        <v>8.094290372774369e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>8.115240200240075e-05</v>
+        <v>8.115240200240086e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>5.34107830303044e-05</v>
+        <v>5.341078303030462e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001093481906038262</v>
+        <v>0.0001093481906038264</v>
       </c>
     </row>
     <row r="9">
@@ -7527,37 +7527,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.700203263085771e-05</v>
+        <v>3.700203263085793e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>4.399040605501001e-05</v>
+        <v>4.399040605501042e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.41925213052044e-05</v>
+        <v>4.419252130520475e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>5.215855037226565e-05</v>
+        <v>5.215855037226583e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>4.39904050020085e-05</v>
+        <v>4.399040500200865e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.405464100907013e-05</v>
+        <v>4.40546410090704e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>4.409904347037764e-05</v>
+        <v>4.409904347037778e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.399039207499692e-05</v>
+        <v>4.399039207499698e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.419457403707103e-05</v>
+        <v>4.419457403707112e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>3.99106516844266e-05</v>
+        <v>3.991065168442669e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>4.413858862759415e-05</v>
+        <v>4.413858862759429e-05</v>
       </c>
     </row>
   </sheetData>
@@ -7643,19 +7643,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.348134083948757e-05</v>
+        <v>1.348134083948755e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.378384604597132e-05</v>
+        <v>1.378384604597134e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.347390027746435e-05</v>
+        <v>1.347390027746436e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.386606172726156e-05</v>
+        <v>1.386606172726158e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.364280396830358e-05</v>
+        <v>1.364280396830359e-05</v>
       </c>
       <c r="G2" t="n">
         <v>1.347788259665816e-05</v>
@@ -7667,10 +7667,10 @@
         <v>1.347576403638333e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.407924169708051e-05</v>
+        <v>1.407924169708053e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.383041757247906e-05</v>
+        <v>1.383041757247908e-05</v>
       </c>
       <c r="L2" t="n">
         <v>1.347552298502668e-05</v>
@@ -7683,37 +7683,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.364441085625457e-05</v>
+        <v>1.364441085625458e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.41260570641428e-05</v>
+        <v>1.412605706414284e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.360206188421917e-05</v>
+        <v>1.360206188421918e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.425817781626092e-05</v>
+        <v>1.425817781626095e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.388965181106658e-05</v>
+        <v>1.38896518110666e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.362628727484777e-05</v>
+        <v>1.362628727484779e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.372043274821948e-05</v>
+        <v>1.372043274821949e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.361395536287598e-05</v>
+        <v>1.361395536287599e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.465571366511844e-05</v>
+        <v>1.465571366511849e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.418924965205856e-05</v>
+        <v>1.418924965205857e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.363420938925363e-05</v>
+        <v>1.363420938925364e-05</v>
       </c>
     </row>
     <row r="4">
@@ -7723,31 +7723,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.195264506510807e-05</v>
+        <v>1.195264506510808e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.176614468035831e-05</v>
+        <v>1.176614468035834e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.186860049422828e-05</v>
+        <v>1.186860049422827e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.177562951273453e-05</v>
+        <v>1.177562951273456e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.177562951273452e-05</v>
+        <v>1.177562951273455e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.190211450602067e-05</v>
+        <v>1.190211450602062e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.205005313007828e-05</v>
+        <v>1.20500531300783e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.184169031559323e-05</v>
+        <v>1.184169031559324e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.200484724140322e-05</v>
+        <v>1.200484724140321e-05</v>
       </c>
       <c r="K4" t="n">
         <v>1.187761390437988e-05</v>
@@ -7763,37 +7763,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.481833024210802e-05</v>
+        <v>4.481833024210798e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.849980407713913e-05</v>
+        <v>4.849980407713928e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>4.890520910919121e-05</v>
+        <v>4.890520910919126e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>4.849980443901971e-05</v>
+        <v>4.84998044390198e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.849980443901971e-05</v>
+        <v>4.84998044390198e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>4.751453210105189e-05</v>
+        <v>4.751453210105137e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>5.557854926853048e-05</v>
+        <v>5.557854926853058e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>4.849979058819334e-05</v>
+        <v>4.849979058819342e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>4.522475565652914e-05</v>
+        <v>4.522475565652886e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>4.611735923259381e-05</v>
+        <v>4.611735923259374e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>4.817407968987906e-05</v>
+        <v>4.817407968987904e-05</v>
       </c>
     </row>
     <row r="6">
@@ -7803,37 +7803,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.613017561371935e-05</v>
+        <v>1.613017561371938e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.307652648707906e-05</v>
+        <v>1.307652648707907e-05</v>
       </c>
       <c r="D6" t="n">
         <v>1.311006873898244e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.304153599228152e-05</v>
+        <v>1.304153599228155e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.308257044860917e-05</v>
+        <v>1.30825704486092e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.607964505463195e-05</v>
+        <v>1.607964505463189e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.625680809293764e-05</v>
+        <v>1.625680809293777e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.60192208642045e-05</v>
+        <v>1.601922086420453e-05</v>
       </c>
       <c r="J6" t="n">
         <v>1.332416552491936e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.31202393586577e-05</v>
+        <v>1.312023935865771e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.317257867064537e-05</v>
+        <v>1.317257867064539e-05</v>
       </c>
     </row>
     <row r="7">
@@ -7843,37 +7843,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.990714241568655e-05</v>
+        <v>1.990714241568658e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>1.979620115511747e-05</v>
+        <v>1.979620115511751e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>1.982306702768451e-05</v>
+        <v>1.982306702768455e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>1.979662320018802e-05</v>
+        <v>1.979662320018808e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>1.979662320018802e-05</v>
+        <v>1.979662320018808e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>1.985661185659917e-05</v>
+        <v>1.985661185659909e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.000455048065675e-05</v>
+        <v>2.000455048065678e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>1.979618766617171e-05</v>
+        <v>1.979618766617175e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>1.995934459198168e-05</v>
+        <v>1.995934459198173e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>1.983211125495837e-05</v>
+        <v>1.983211125495836e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>1.988581625267581e-05</v>
+        <v>1.988581625267583e-05</v>
       </c>
     </row>
     <row r="8">
@@ -7883,37 +7883,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.139315083927781e-05</v>
+        <v>5.139315083927807e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>7.653564811091767e-05</v>
+        <v>7.653564811091812e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>8.179248082490713e-05</v>
+        <v>8.179248082490759e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>6.962996007413404e-05</v>
+        <v>6.962996007413439e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>5.208280346962642e-05</v>
+        <v>5.208280346962671e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>7.659065115819752e-05</v>
+        <v>7.65906511581979e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>7.673858978225454e-05</v>
+        <v>7.673858978225496e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>7.653022696777006e-05</v>
+        <v>7.653022696777053e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>7.669834585960599e-05</v>
+        <v>7.669834585960641e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>5.084912454226481e-05</v>
+        <v>5.084912454226508e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001029935350165289</v>
+        <v>0.0001029935350165296</v>
       </c>
     </row>
     <row r="9">
@@ -7923,37 +7923,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.425452615998994e-05</v>
+        <v>3.425452615998999e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>4.039310625690024e-05</v>
+        <v>4.039310625690031e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.042000318031826e-05</v>
+        <v>4.042000318031827e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>4.760492032675375e-05</v>
+        <v>4.760492032675378e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>4.039310530791321e-05</v>
+        <v>4.039310530791323e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.045351695838193e-05</v>
+        <v>4.04535169583819e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>4.060145558243951e-05</v>
+        <v>4.060145558243952e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.039309276795449e-05</v>
+        <v>4.039309276795455e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.055624969376446e-05</v>
+        <v>4.055624969376445e-05</v>
       </c>
       <c r="K9" t="n">
         <v>3.680801923675819e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>4.048272135445857e-05</v>
+        <v>4.048272135445858e-05</v>
       </c>
     </row>
   </sheetData>
